--- a/30_table/01_테스트버전/Table_STR_String.xlsx
+++ b/30_table/01_테스트버전/Table_STR_String.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="14385" yWindow="165" windowWidth="14430" windowHeight="11880" activeTab="2"/>
+    <workbookView xWindow="14385" yWindow="225" windowWidth="14430" windowHeight="11820" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="DOC History" sheetId="6" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1583" uniqueCount="1545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1661" uniqueCount="1622">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5318,6 +5318,273 @@
   </si>
   <si>
     <t>가방에 빈 공간이 부족합니다.\n필요없는 아이템을 판매하거나, 가방을 확장한 후 다시 시도해 주세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_ERROR_2</t>
+  </si>
+  <si>
+    <t>인터넷이 연결되어 있지 않습니다.\n인터넷 연결을 확인해 주세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_NPC_N_0022</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20022_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>개발자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_MAP_S1_006</t>
+  </si>
+  <si>
+    <t>STR_MAP_S1_007</t>
+  </si>
+  <si>
+    <t>STR_MAP_S1_008</t>
+  </si>
+  <si>
+    <t>STR_MAP_S1_009</t>
+  </si>
+  <si>
+    <t>STR_MAP_S1_010</t>
+  </si>
+  <si>
+    <t>STR_MAP_S1_011</t>
+  </si>
+  <si>
+    <t>STR_MAP_S1_005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>개발자의 방으로</t>
+  </si>
+  <si>
+    <t>개발자와 대화 1</t>
+  </si>
+  <si>
+    <t>개발자와 대화 2</t>
+  </si>
+  <si>
+    <t>시험 1</t>
+  </si>
+  <si>
+    <t>시험 2</t>
+  </si>
+  <si>
+    <t>시험 3</t>
+  </si>
+  <si>
+    <t>개발자와 대화 3</t>
+  </si>
+  <si>
+    <t>STR_MAP_S1_005_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S1_006_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S1_007_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S1_008_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S1_009_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S1_010_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S1_011_DESC</t>
+  </si>
+  <si>
+    <t>개발자의 방으로 이동하세요. 계단을 내려가면 됩니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>개발자와 대화해 보세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>개발자와 대화해 보세요. 개발자 근처에 가서 개발자를 터치하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바닥의 아이콘 중 환전 아이콘으로 이동하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바닥의 아이콘 중 리뷰 아이콘으로 이동하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>어서 오세요. 저희 게임을 다운 받아 주셔서 감사합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임에 도움이 되는 내용을 설명해 드릴께요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그럼 다음 맵에서 계속해서 설명하겠습니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20022_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20022_03</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20022_04</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20023_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메뉴 버튼에 대해 설명 드리겠습니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임화면 아래 쪽에 동그란 모양의 버튼이 메뉴 버튼입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메뉴 버튼은 좌우로 드레그 하거나,</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좌우 화살표를 눌러서 다음으로 이동시킬 수 있습니다.</t>
+  </si>
+  <si>
+    <t>메뉴는 순서대로 영웅정보, 맵선택, 소지품, 상점, 보석구입, 환전,</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>출석보상, 리뷰, 버그 신고, 설정, 나가기 버튼으로 구성되어 있습니다.</t>
+  </si>
+  <si>
+    <t>시간이 되시면 각 버튼들을 하나씩 눌러 보세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20023_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20023_03</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20023_04</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20023_05</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20023_06</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20023_07</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20024_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자 그럼 시험을 볼까요?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>준비가 되셨으면 다음 맵으로 이동해서 시험을 시작해 주세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 시험을 통과하시면 모험에 도움이 되는 아이템을 드리겠습니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그럼 좋은 결과가 있길 바랍니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20024_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20024_03</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20024_04</t>
+  </si>
+  <si>
+    <t>STR_MAP_S1_012</t>
+  </si>
+  <si>
+    <t>개발자와 대화 4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_MAP_S1_012_DESC</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20025_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수고하셨습니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그럼 이제부터 모험을 시작해 볼까요?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체 지도가 나오면 &lt;숲 속 마을&gt;을 선택해 주세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그럼 행운이 있길 바랍니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20025_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20025_03</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20025_04</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20025_05</t>
+  </si>
+  <si>
+    <t>개발자에게 메뉴에 대한 설명을 이어서 들어 보세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바닥의 아이콘 중 맵선택 아이콘으로 이동하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>설명이 필요 없으시면 이번 맵 완료 후 &lt;지역변경&gt;을 눌러서 숲속 마을로 이동하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>맵 아이콘을 눌러서 &lt;지역변경&gt;을 눌러 주세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_REGION_99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>개발실</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8505,7 +8772,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E771"/>
+  <dimension ref="A1:E810"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="33" bestFit="1" customWidth="1"/>
@@ -12881,10 +13148,10 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>1411</v>
+        <v>1545</v>
       </c>
       <c r="C397" t="s">
-        <v>1414</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.3">
@@ -12892,10 +13159,10 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="C398" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.3">
@@ -12903,10 +13170,10 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>257</v>
+        <v>1412</v>
       </c>
       <c r="C399" t="s">
-        <v>287</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.3">
@@ -12914,10 +13181,10 @@
         <v>399</v>
       </c>
       <c r="B400" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C400" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.3">
@@ -12925,10 +13192,10 @@
         <v>400</v>
       </c>
       <c r="B401" t="s">
-        <v>994</v>
+        <v>258</v>
       </c>
       <c r="C401" t="s">
-        <v>997</v>
+        <v>286</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.3">
@@ -12936,7 +13203,7 @@
         <v>401</v>
       </c>
       <c r="B402" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="C402" t="s">
         <v>997</v>
@@ -12947,7 +13214,7 @@
         <v>402</v>
       </c>
       <c r="B403" t="s">
-        <v>1393</v>
+        <v>995</v>
       </c>
       <c r="C403" t="s">
         <v>997</v>
@@ -12958,10 +13225,10 @@
         <v>403</v>
       </c>
       <c r="B404" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="C404" t="s">
-        <v>1395</v>
+        <v>997</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.3">
@@ -12969,10 +13236,10 @@
         <v>404</v>
       </c>
       <c r="B405" t="s">
-        <v>1516</v>
+        <v>1394</v>
       </c>
       <c r="C405" t="s">
-        <v>1517</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.3">
@@ -12980,10 +13247,10 @@
         <v>405</v>
       </c>
       <c r="B406" t="s">
-        <v>259</v>
+        <v>1516</v>
       </c>
       <c r="C406" t="s">
-        <v>1531</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.3">
@@ -12991,10 +13258,10 @@
         <v>406</v>
       </c>
       <c r="B407" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C407" t="s">
-        <v>288</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.3">
@@ -13002,10 +13269,10 @@
         <v>407</v>
       </c>
       <c r="B408" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C408" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.3">
@@ -13013,10 +13280,10 @@
         <v>408</v>
       </c>
       <c r="B409" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C409" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.3">
@@ -13024,10 +13291,10 @@
         <v>409</v>
       </c>
       <c r="B410" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C410" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.3">
@@ -13035,10 +13302,10 @@
         <v>410</v>
       </c>
       <c r="B411" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C411" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.3">
@@ -13046,10 +13313,10 @@
         <v>411</v>
       </c>
       <c r="B412" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C412" t="s">
-        <v>289</v>
+        <v>361</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.3">
@@ -13057,10 +13324,10 @@
         <v>412</v>
       </c>
       <c r="B413" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C413" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.3">
@@ -13068,10 +13335,10 @@
         <v>413</v>
       </c>
       <c r="B414" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C414" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.3">
@@ -13079,10 +13346,10 @@
         <v>414</v>
       </c>
       <c r="B415" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C415" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.3">
@@ -13090,10 +13357,10 @@
         <v>415</v>
       </c>
       <c r="B416" t="s">
-        <v>362</v>
+        <v>268</v>
       </c>
       <c r="C416" t="s">
-        <v>364</v>
+        <v>292</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.3">
@@ -13101,10 +13368,10 @@
         <v>416</v>
       </c>
       <c r="B417" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C417" t="s">
-        <v>1532</v>
+        <v>364</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.3">
@@ -13112,10 +13379,10 @@
         <v>417</v>
       </c>
       <c r="B418" t="s">
-        <v>269</v>
+        <v>363</v>
       </c>
       <c r="C418" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.3">
@@ -13123,10 +13390,10 @@
         <v>418</v>
       </c>
       <c r="B419" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C419" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.3">
@@ -13134,10 +13401,10 @@
         <v>419</v>
       </c>
       <c r="B420" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C420" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.3">
@@ -13145,10 +13412,10 @@
         <v>420</v>
       </c>
       <c r="B421" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C421" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.3">
@@ -13156,10 +13423,10 @@
         <v>421</v>
       </c>
       <c r="B422" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C422" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.3">
@@ -13167,10 +13434,10 @@
         <v>422</v>
       </c>
       <c r="B423" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C423" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.3">
@@ -13178,10 +13445,10 @@
         <v>423</v>
       </c>
       <c r="B424" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C424" t="s">
-        <v>1543</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.3">
@@ -13189,10 +13456,10 @@
         <v>424</v>
       </c>
       <c r="B425" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C425" t="s">
-        <v>386</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.3">
@@ -13200,10 +13467,10 @@
         <v>425</v>
       </c>
       <c r="B426" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C426" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.3">
@@ -13211,10 +13478,10 @@
         <v>426</v>
       </c>
       <c r="B427" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C427" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.3">
@@ -13222,10 +13489,10 @@
         <v>427</v>
       </c>
       <c r="B428" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C428" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.3">
@@ -13233,10 +13500,10 @@
         <v>428</v>
       </c>
       <c r="B429" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C429" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.3">
@@ -13244,10 +13511,10 @@
         <v>429</v>
       </c>
       <c r="B430" t="s">
-        <v>381</v>
+        <v>280</v>
       </c>
       <c r="C430" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.3">
@@ -13255,10 +13522,10 @@
         <v>430</v>
       </c>
       <c r="B431" t="s">
-        <v>1157</v>
+        <v>381</v>
       </c>
       <c r="C431" t="s">
-        <v>1162</v>
+        <v>382</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.3">
@@ -13266,10 +13533,10 @@
         <v>431</v>
       </c>
       <c r="B432" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="C432" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.3">
@@ -13277,10 +13544,10 @@
         <v>432</v>
       </c>
       <c r="B433" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="C433" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.3">
@@ -13288,10 +13555,10 @@
         <v>433</v>
       </c>
       <c r="B434" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="C434" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.3">
@@ -13299,10 +13566,10 @@
         <v>434</v>
       </c>
       <c r="B435" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="C435" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.3">
@@ -13310,10 +13577,10 @@
         <v>435</v>
       </c>
       <c r="B436" t="s">
-        <v>1409</v>
+        <v>1161</v>
       </c>
       <c r="C436" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.3">
@@ -13321,10 +13588,10 @@
         <v>436</v>
       </c>
       <c r="B437" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="C437" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.3">
@@ -13332,10 +13599,10 @@
         <v>437</v>
       </c>
       <c r="B438" t="s">
-        <v>1407</v>
+        <v>1410</v>
       </c>
       <c r="C438" t="s">
-        <v>1408</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.3">
@@ -13343,10 +13610,10 @@
         <v>438</v>
       </c>
       <c r="B439" t="s">
-        <v>281</v>
+        <v>1407</v>
       </c>
       <c r="C439" t="s">
-        <v>293</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.3">
@@ -13354,10 +13621,10 @@
         <v>439</v>
       </c>
       <c r="B440" t="s">
-        <v>365</v>
+        <v>281</v>
       </c>
       <c r="C440" t="s">
-        <v>1540</v>
+        <v>293</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.3">
@@ -13365,10 +13632,10 @@
         <v>440</v>
       </c>
       <c r="B441" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C441" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.3">
@@ -13376,10 +13643,10 @@
         <v>441</v>
       </c>
       <c r="B442" t="s">
-        <v>388</v>
+        <v>366</v>
       </c>
       <c r="C442" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.3">
@@ -13387,10 +13654,10 @@
         <v>442</v>
       </c>
       <c r="B443" t="s">
-        <v>282</v>
+        <v>388</v>
       </c>
       <c r="C443" t="s">
-        <v>294</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.3">
@@ -13398,10 +13665,10 @@
         <v>443</v>
       </c>
       <c r="B444" t="s">
-        <v>367</v>
+        <v>282</v>
       </c>
       <c r="C444" t="s">
-        <v>369</v>
+        <v>294</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.3">
@@ -13409,10 +13676,10 @@
         <v>444</v>
       </c>
       <c r="B445" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C445" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.3">
@@ -13420,10 +13687,10 @@
         <v>445</v>
       </c>
       <c r="B446" t="s">
-        <v>1169</v>
+        <v>368</v>
       </c>
       <c r="C446" t="s">
-        <v>1173</v>
+        <v>370</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.3">
@@ -13431,10 +13698,10 @@
         <v>446</v>
       </c>
       <c r="B447" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="C447" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.3">
@@ -13442,10 +13709,10 @@
         <v>447</v>
       </c>
       <c r="B448" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="C448" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.3">
@@ -13453,10 +13720,10 @@
         <v>448</v>
       </c>
       <c r="B449" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C449" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.3">
@@ -13464,10 +13731,10 @@
         <v>449</v>
       </c>
       <c r="B450" t="s">
-        <v>983</v>
+        <v>1172</v>
       </c>
       <c r="C450" t="s">
-        <v>984</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.3">
@@ -13475,10 +13742,10 @@
         <v>450</v>
       </c>
       <c r="B451" t="s">
-        <v>992</v>
+        <v>983</v>
       </c>
       <c r="C451" t="s">
-        <v>993</v>
+        <v>984</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.3">
@@ -13486,10 +13753,10 @@
         <v>451</v>
       </c>
       <c r="B452" t="s">
-        <v>1424</v>
+        <v>992</v>
       </c>
       <c r="C452" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.3">
@@ -13497,10 +13764,10 @@
         <v>452</v>
       </c>
       <c r="B453" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="C453" t="s">
-        <v>1427</v>
+        <v>997</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.3">
@@ -13508,10 +13775,10 @@
         <v>453</v>
       </c>
       <c r="B454" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="C454" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.3">
@@ -13519,10 +13786,10 @@
         <v>454</v>
       </c>
       <c r="B455" t="s">
-        <v>283</v>
+        <v>1426</v>
       </c>
       <c r="C455" t="s">
-        <v>295</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.3">
@@ -13530,10 +13797,10 @@
         <v>455</v>
       </c>
       <c r="B456" t="s">
-        <v>985</v>
+        <v>283</v>
       </c>
       <c r="C456" t="s">
-        <v>989</v>
+        <v>295</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.3">
@@ -13541,10 +13808,10 @@
         <v>456</v>
       </c>
       <c r="B457" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="C457" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.3">
@@ -13552,10 +13819,10 @@
         <v>457</v>
       </c>
       <c r="B458" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="C458" t="s">
-        <v>1396</v>
+        <v>990</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.3">
@@ -13563,10 +13830,10 @@
         <v>458</v>
       </c>
       <c r="B459" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="C459" t="s">
-        <v>991</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.3">
@@ -13574,10 +13841,10 @@
         <v>459</v>
       </c>
       <c r="B460" t="s">
-        <v>1177</v>
+        <v>988</v>
       </c>
       <c r="C460" t="s">
-        <v>1178</v>
+        <v>991</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.3">
@@ -13585,10 +13852,10 @@
         <v>460</v>
       </c>
       <c r="B461" t="s">
-        <v>1371</v>
+        <v>1177</v>
       </c>
       <c r="C461" t="s">
-        <v>1378</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.3">
@@ -13596,10 +13863,10 @@
         <v>461</v>
       </c>
       <c r="B462" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="C462" t="s">
-        <v>1399</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.3">
@@ -13607,10 +13874,10 @@
         <v>462</v>
       </c>
       <c r="B463" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="C463" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.3">
@@ -13618,10 +13885,10 @@
         <v>463</v>
       </c>
       <c r="B464" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="C464" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.3">
@@ -13629,10 +13896,10 @@
         <v>464</v>
       </c>
       <c r="B465" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="C465" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.3">
@@ -13640,10 +13907,10 @@
         <v>465</v>
       </c>
       <c r="B466" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="C466" t="s">
-        <v>1397</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.3">
@@ -13651,10 +13918,10 @@
         <v>466</v>
       </c>
       <c r="B467" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="C467" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.3">
@@ -13662,10 +13929,10 @@
         <v>467</v>
       </c>
       <c r="B468" t="s">
-        <v>297</v>
+        <v>1377</v>
       </c>
       <c r="C468" t="s">
-        <v>298</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.3">
@@ -13673,10 +13940,10 @@
         <v>468</v>
       </c>
       <c r="B469" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C469" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.3">
@@ -13684,10 +13951,10 @@
         <v>469</v>
       </c>
       <c r="B470" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C470" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.3">
@@ -13695,10 +13962,10 @@
         <v>470</v>
       </c>
       <c r="B471" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C471" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.3">
@@ -13706,10 +13973,10 @@
         <v>471</v>
       </c>
       <c r="B472" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C472" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.3">
@@ -13717,10 +13984,10 @@
         <v>472</v>
       </c>
       <c r="B473" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C473" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.3">
@@ -13728,10 +13995,10 @@
         <v>473</v>
       </c>
       <c r="B474" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C474" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.3">
@@ -13739,10 +14006,10 @@
         <v>474</v>
       </c>
       <c r="B475" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C475" t="s">
-        <v>864</v>
+        <v>310</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.3">
@@ -13750,10 +14017,10 @@
         <v>475</v>
       </c>
       <c r="B476" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C476" t="s">
-        <v>313</v>
+        <v>864</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.3">
@@ -13761,10 +14028,10 @@
         <v>476</v>
       </c>
       <c r="B477" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C477" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.3">
@@ -13772,10 +14039,10 @@
         <v>477</v>
       </c>
       <c r="B478" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C478" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.3">
@@ -13783,10 +14050,10 @@
         <v>478</v>
       </c>
       <c r="B479" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C479" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.3">
@@ -13794,10 +14061,10 @@
         <v>479</v>
       </c>
       <c r="B480" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C480" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.3">
@@ -13805,10 +14072,10 @@
         <v>480</v>
       </c>
       <c r="B481" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C481" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.3">
@@ -13816,10 +14083,10 @@
         <v>481</v>
       </c>
       <c r="B482" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C482" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.3">
@@ -13827,10 +14094,10 @@
         <v>482</v>
       </c>
       <c r="B483" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C483" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.3">
@@ -13838,10 +14105,10 @@
         <v>483</v>
       </c>
       <c r="B484" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C484" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.3">
@@ -13849,10 +14116,10 @@
         <v>484</v>
       </c>
       <c r="B485" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C485" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.3">
@@ -13860,10 +14127,10 @@
         <v>485</v>
       </c>
       <c r="B486" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C486" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.3">
@@ -13871,10 +14138,10 @@
         <v>486</v>
       </c>
       <c r="B487" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C487" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.3">
@@ -13882,10 +14149,10 @@
         <v>487</v>
       </c>
       <c r="B488" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C488" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.3">
@@ -13893,10 +14160,10 @@
         <v>488</v>
       </c>
       <c r="B489" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C489" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.3">
@@ -13904,10 +14171,10 @@
         <v>489</v>
       </c>
       <c r="B490" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="C490" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.3">
@@ -13915,10 +14182,10 @@
         <v>490</v>
       </c>
       <c r="B491" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C491" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.3">
@@ -13926,10 +14193,10 @@
         <v>491</v>
       </c>
       <c r="B492" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C492" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.3">
@@ -13937,10 +14204,10 @@
         <v>492</v>
       </c>
       <c r="B493" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C493" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.3">
@@ -13948,10 +14215,10 @@
         <v>493</v>
       </c>
       <c r="B494" t="s">
-        <v>833</v>
+        <v>353</v>
       </c>
       <c r="C494" t="s">
-        <v>835</v>
+        <v>354</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.3">
@@ -13959,10 +14226,10 @@
         <v>494</v>
       </c>
       <c r="B495" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C495" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.3">
@@ -13970,10 +14237,10 @@
         <v>495</v>
       </c>
       <c r="B496" t="s">
-        <v>977</v>
+        <v>834</v>
       </c>
       <c r="C496" t="s">
-        <v>979</v>
+        <v>836</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.3">
@@ -13981,10 +14248,10 @@
         <v>496</v>
       </c>
       <c r="B497" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="C497" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.3">
@@ -13992,10 +14259,10 @@
         <v>497</v>
       </c>
       <c r="B498" t="s">
-        <v>1132</v>
+        <v>978</v>
       </c>
       <c r="C498" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.3">
@@ -14003,10 +14270,10 @@
         <v>498</v>
       </c>
       <c r="B499" t="s">
-        <v>981</v>
+        <v>1132</v>
       </c>
       <c r="C499" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.3">
@@ -14014,10 +14281,10 @@
         <v>499</v>
       </c>
       <c r="B500" t="s">
-        <v>998</v>
+        <v>981</v>
       </c>
       <c r="C500" t="s">
-        <v>1008</v>
+        <v>982</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.3">
@@ -14025,10 +14292,10 @@
         <v>500</v>
       </c>
       <c r="B501" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="C501" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.3">
@@ -14036,10 +14303,10 @@
         <v>501</v>
       </c>
       <c r="B502" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="C502" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.3">
@@ -14047,10 +14314,10 @@
         <v>502</v>
       </c>
       <c r="B503" t="s">
-        <v>1010</v>
+        <v>1000</v>
       </c>
       <c r="C503" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.3">
@@ -14058,10 +14325,10 @@
         <v>503</v>
       </c>
       <c r="B504" t="s">
-        <v>1024</v>
+        <v>1010</v>
       </c>
       <c r="C504" t="s">
-        <v>1025</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.3">
@@ -14069,10 +14336,10 @@
         <v>504</v>
       </c>
       <c r="B505" t="s">
-        <v>1001</v>
+        <v>1024</v>
       </c>
       <c r="C505" t="s">
-        <v>1004</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.3">
@@ -14080,10 +14347,10 @@
         <v>505</v>
       </c>
       <c r="B506" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C506" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.3">
@@ -14091,10 +14358,10 @@
         <v>506</v>
       </c>
       <c r="B507" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="C507" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.3">
@@ -14102,10 +14369,10 @@
         <v>507</v>
       </c>
       <c r="B508" t="s">
-        <v>1012</v>
+        <v>1003</v>
       </c>
       <c r="C508" t="s">
-        <v>1523</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.3">
@@ -14113,10 +14380,10 @@
         <v>508</v>
       </c>
       <c r="B509" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="C509" t="s">
-        <v>1014</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.3">
@@ -14124,10 +14391,10 @@
         <v>509</v>
       </c>
       <c r="B510" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="C510" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.3">
@@ -14135,10 +14402,10 @@
         <v>510</v>
       </c>
       <c r="B511" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="C511" t="s">
-        <v>1524</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.3">
@@ -14146,10 +14413,10 @@
         <v>511</v>
       </c>
       <c r="B512" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="C512" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.3">
@@ -14157,10 +14424,10 @@
         <v>512</v>
       </c>
       <c r="B513" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="C513" t="s">
-        <v>1021</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.3">
@@ -14168,10 +14435,10 @@
         <v>513</v>
       </c>
       <c r="B514" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="C514" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.3">
@@ -14179,10 +14446,10 @@
         <v>514</v>
       </c>
       <c r="B515" t="s">
-        <v>852</v>
+        <v>1022</v>
       </c>
       <c r="C515" t="s">
-        <v>858</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.3">
@@ -14190,10 +14457,10 @@
         <v>515</v>
       </c>
       <c r="B516" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C516" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.3">
@@ -14201,10 +14468,10 @@
         <v>516</v>
       </c>
       <c r="B517" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="C517" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.3">
@@ -14212,10 +14479,10 @@
         <v>517</v>
       </c>
       <c r="B518" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C518" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.3">
@@ -14223,10 +14490,10 @@
         <v>518</v>
       </c>
       <c r="B519" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C519" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.3">
@@ -14234,10 +14501,10 @@
         <v>519</v>
       </c>
       <c r="B520" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="C520" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.3">
@@ -14245,10 +14512,10 @@
         <v>520</v>
       </c>
       <c r="B521" t="s">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="C521" t="s">
-        <v>1062</v>
+        <v>863</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.3">
@@ -14256,10 +14523,10 @@
         <v>521</v>
       </c>
       <c r="B522" t="s">
-        <v>1068</v>
+        <v>865</v>
       </c>
       <c r="C522" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.3">
@@ -14267,10 +14534,10 @@
         <v>522</v>
       </c>
       <c r="B523" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="C523" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.3">
@@ -14278,10 +14545,10 @@
         <v>523</v>
       </c>
       <c r="B524" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C524" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.3">
@@ -14289,10 +14556,10 @@
         <v>524</v>
       </c>
       <c r="B525" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C525" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.3">
@@ -14300,10 +14567,10 @@
         <v>525</v>
       </c>
       <c r="B526" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="C526" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.3">
@@ -14311,10 +14578,10 @@
         <v>526</v>
       </c>
       <c r="B527" t="s">
-        <v>866</v>
+        <v>1072</v>
       </c>
       <c r="C527" t="s">
-        <v>871</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.3">
@@ -14322,10 +14589,10 @@
         <v>527</v>
       </c>
       <c r="B528" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C528" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.3">
@@ -14333,10 +14600,10 @@
         <v>528</v>
       </c>
       <c r="B529" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="C529" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.3">
@@ -14344,10 +14611,10 @@
         <v>529</v>
       </c>
       <c r="B530" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="C530" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.3">
@@ -14355,10 +14622,10 @@
         <v>530</v>
       </c>
       <c r="B531" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C531" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.3">
@@ -14366,10 +14633,10 @@
         <v>531</v>
       </c>
       <c r="B532" t="s">
-        <v>1245</v>
+        <v>870</v>
       </c>
       <c r="C532" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.3">
@@ -14377,10 +14644,10 @@
         <v>532</v>
       </c>
       <c r="B533" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="C533" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.3">
@@ -14388,10 +14655,10 @@
         <v>533</v>
       </c>
       <c r="B534" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="C534" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.3">
@@ -14399,10 +14666,10 @@
         <v>534</v>
       </c>
       <c r="B535" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="C535" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.3">
@@ -14410,10 +14677,10 @@
         <v>535</v>
       </c>
       <c r="B536" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="C536" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.3">
@@ -14421,10 +14688,10 @@
         <v>536</v>
       </c>
       <c r="B537" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="C537" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.3">
@@ -14432,10 +14699,10 @@
         <v>537</v>
       </c>
       <c r="B538" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="C538" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.3">
@@ -14443,10 +14710,10 @@
         <v>538</v>
       </c>
       <c r="B539" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="C539" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.3">
@@ -14454,10 +14721,10 @@
         <v>539</v>
       </c>
       <c r="B540" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="C540" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.3">
@@ -14465,10 +14732,10 @@
         <v>540</v>
       </c>
       <c r="B541" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="C541" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.3">
@@ -14476,10 +14743,10 @@
         <v>541</v>
       </c>
       <c r="B542" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="C542" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.3">
@@ -14487,10 +14754,10 @@
         <v>542</v>
       </c>
       <c r="B543" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="C543" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.3">
@@ -14498,10 +14765,10 @@
         <v>543</v>
       </c>
       <c r="B544" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="C544" t="s">
-        <v>1526</v>
+        <v>887</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.3">
@@ -14509,10 +14776,10 @@
         <v>544</v>
       </c>
       <c r="B545" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="C545" t="s">
-        <v>888</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.3">
@@ -14520,10 +14787,10 @@
         <v>545</v>
       </c>
       <c r="B546" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="C546" t="s">
-        <v>1118</v>
+        <v>888</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.3">
@@ -14531,10 +14798,10 @@
         <v>546</v>
       </c>
       <c r="B547" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="C547" t="s">
-        <v>892</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.3">
@@ -14542,10 +14809,10 @@
         <v>547</v>
       </c>
       <c r="B548" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="C548" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.3">
@@ -14553,10 +14820,10 @@
         <v>548</v>
       </c>
       <c r="B549" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="C549" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.3">
@@ -14564,10 +14831,10 @@
         <v>549</v>
       </c>
       <c r="B550" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="C550" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.3">
@@ -14575,10 +14842,10 @@
         <v>550</v>
       </c>
       <c r="B551" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="C551" t="s">
-        <v>1041</v>
+        <v>891</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.3">
@@ -14586,10 +14853,10 @@
         <v>551</v>
       </c>
       <c r="B552" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="C552" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.3">
@@ -14597,10 +14864,10 @@
         <v>552</v>
       </c>
       <c r="B553" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="C553" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.3">
@@ -14608,10 +14875,10 @@
         <v>553</v>
       </c>
       <c r="B554" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="C554" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.3">
@@ -14619,10 +14886,10 @@
         <v>554</v>
       </c>
       <c r="B555" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="C555" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.3">
@@ -14630,10 +14897,10 @@
         <v>555</v>
       </c>
       <c r="B556" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="C556" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.3">
@@ -14641,10 +14908,10 @@
         <v>556</v>
       </c>
       <c r="B557" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="C557" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.3">
@@ -14652,10 +14919,10 @@
         <v>557</v>
       </c>
       <c r="B558" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="C558" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.3">
@@ -14663,10 +14930,10 @@
         <v>558</v>
       </c>
       <c r="B559" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="C559" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.3">
@@ -14674,10 +14941,10 @@
         <v>559</v>
       </c>
       <c r="B560" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C560" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.3">
@@ -14685,10 +14952,10 @@
         <v>560</v>
       </c>
       <c r="B561" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="C561" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.3">
@@ -14696,10 +14963,10 @@
         <v>561</v>
       </c>
       <c r="B562" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="C562" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.3">
@@ -14707,10 +14974,10 @@
         <v>562</v>
       </c>
       <c r="B563" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="C563" t="s">
-        <v>1527</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.3">
@@ -14718,10 +14985,10 @@
         <v>563</v>
       </c>
       <c r="B564" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="C564" t="s">
-        <v>1075</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.3">
@@ -14729,10 +14996,10 @@
         <v>564</v>
       </c>
       <c r="B565" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="C565" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.3">
@@ -14740,10 +15007,10 @@
         <v>565</v>
       </c>
       <c r="B566" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="C566" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.3">
@@ -14751,10 +15018,10 @@
         <v>566</v>
       </c>
       <c r="B567" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C567" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.3">
@@ -14762,10 +15029,10 @@
         <v>567</v>
       </c>
       <c r="B568" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="C568" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.3">
@@ -14773,10 +15040,10 @@
         <v>568</v>
       </c>
       <c r="B569" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="C569" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.3">
@@ -14784,10 +15051,10 @@
         <v>569</v>
       </c>
       <c r="B570" t="s">
-        <v>893</v>
+        <v>1282</v>
       </c>
       <c r="C570" t="s">
-        <v>894</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.3">
@@ -14795,10 +15062,10 @@
         <v>570</v>
       </c>
       <c r="B571" t="s">
-        <v>899</v>
+        <v>893</v>
       </c>
       <c r="C571" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.3">
@@ -14806,10 +15073,10 @@
         <v>571</v>
       </c>
       <c r="B572" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C572" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.3">
@@ -14817,10 +15084,10 @@
         <v>572</v>
       </c>
       <c r="B573" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="C573" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.3">
@@ -14828,10 +15095,10 @@
         <v>573</v>
       </c>
       <c r="B574" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C574" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.3">
@@ -14839,10 +15106,10 @@
         <v>574</v>
       </c>
       <c r="B575" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="C575" t="s">
-        <v>904</v>
+        <v>898</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.3">
@@ -14850,10 +15117,10 @@
         <v>575</v>
       </c>
       <c r="B576" t="s">
-        <v>909</v>
+        <v>903</v>
       </c>
       <c r="C576" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.3">
@@ -14861,10 +15128,10 @@
         <v>576</v>
       </c>
       <c r="B577" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="C577" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.3">
@@ -14872,10 +15139,10 @@
         <v>577</v>
       </c>
       <c r="B578" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C578" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.3">
@@ -14883,10 +15150,10 @@
         <v>578</v>
       </c>
       <c r="B579" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C579" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.3">
@@ -14894,10 +15161,10 @@
         <v>579</v>
       </c>
       <c r="B580" t="s">
-        <v>918</v>
+        <v>912</v>
       </c>
       <c r="C580" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.3">
@@ -14905,10 +15172,10 @@
         <v>580</v>
       </c>
       <c r="B581" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
       <c r="C581" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.3">
@@ -14916,10 +15183,10 @@
         <v>581</v>
       </c>
       <c r="B582" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="C582" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.3">
@@ -14927,10 +15194,10 @@
         <v>582</v>
       </c>
       <c r="B583" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="C583" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.3">
@@ -14938,10 +15205,10 @@
         <v>583</v>
       </c>
       <c r="B584" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C584" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.3">
@@ -14949,10 +15216,10 @@
         <v>584</v>
       </c>
       <c r="B585" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="C585" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.3">
@@ -14960,10 +15227,10 @@
         <v>585</v>
       </c>
       <c r="B586" t="s">
-        <v>936</v>
+        <v>928</v>
       </c>
       <c r="C586" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.3">
@@ -14971,10 +15238,10 @@
         <v>586</v>
       </c>
       <c r="B587" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="C587" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.3">
@@ -14982,10 +15249,10 @@
         <v>587</v>
       </c>
       <c r="B588" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="C588" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.3">
@@ -14993,10 +15260,10 @@
         <v>588</v>
       </c>
       <c r="B589" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="C589" t="s">
-        <v>1038</v>
+        <v>922</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.3">
@@ -15004,10 +15271,10 @@
         <v>589</v>
       </c>
       <c r="B590" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="C590" t="s">
-        <v>923</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.3">
@@ -15015,10 +15282,10 @@
         <v>590</v>
       </c>
       <c r="B591" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="C591" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.3">
@@ -15026,10 +15293,10 @@
         <v>591</v>
       </c>
       <c r="B592" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C592" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.3">
@@ -15037,10 +15304,10 @@
         <v>592</v>
       </c>
       <c r="B593" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="C593" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.3">
@@ -15048,10 +15315,10 @@
         <v>593</v>
       </c>
       <c r="B594" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="C594" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.3">
@@ -15059,10 +15326,10 @@
         <v>594</v>
       </c>
       <c r="B595" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="C595" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.3">
@@ -15070,10 +15337,10 @@
         <v>595</v>
       </c>
       <c r="B596" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="C596" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.3">
@@ -15081,10 +15348,10 @@
         <v>596</v>
       </c>
       <c r="B597" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="C597" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.3">
@@ -15092,10 +15359,10 @@
         <v>597</v>
       </c>
       <c r="B598" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="C598" t="s">
-        <v>949</v>
+        <v>935</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.3">
@@ -15103,10 +15370,10 @@
         <v>598</v>
       </c>
       <c r="B599" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="C599" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.3">
@@ -15114,10 +15381,10 @@
         <v>599</v>
       </c>
       <c r="B600" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="C600" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.3">
@@ -15125,10 +15392,10 @@
         <v>600</v>
       </c>
       <c r="B601" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="C601" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.3">
@@ -15136,10 +15403,10 @@
         <v>601</v>
       </c>
       <c r="B602" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="C602" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.3">
@@ -15147,10 +15414,10 @@
         <v>602</v>
       </c>
       <c r="B603" t="s">
-        <v>962</v>
+        <v>956</v>
       </c>
       <c r="C603" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.3">
@@ -15158,10 +15425,10 @@
         <v>603</v>
       </c>
       <c r="B604" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="C604" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.3">
@@ -15169,10 +15436,10 @@
         <v>604</v>
       </c>
       <c r="B605" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="C605" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.3">
@@ -15180,10 +15447,10 @@
         <v>605</v>
       </c>
       <c r="B606" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="C606" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.3">
@@ -15191,10 +15458,10 @@
         <v>606</v>
       </c>
       <c r="B607" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="C607" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.3">
@@ -15202,10 +15469,10 @@
         <v>607</v>
       </c>
       <c r="B608" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="C608" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.3">
@@ -15213,10 +15480,10 @@
         <v>608</v>
       </c>
       <c r="B609" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="C609" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.3">
@@ -15224,10 +15491,10 @@
         <v>609</v>
       </c>
       <c r="B610" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="C610" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.3">
@@ -15235,10 +15502,10 @@
         <v>610</v>
       </c>
       <c r="B611" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C611" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.3">
@@ -15246,10 +15513,10 @@
         <v>611</v>
       </c>
       <c r="B612" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C612" t="s">
-        <v>923</v>
+        <v>971</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.3">
@@ -15257,10 +15524,10 @@
         <v>612</v>
       </c>
       <c r="B613" t="s">
-        <v>1073</v>
+        <v>976</v>
       </c>
       <c r="C613" t="s">
-        <v>1074</v>
+        <v>923</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.3">
@@ -15268,10 +15535,10 @@
         <v>613</v>
       </c>
       <c r="B614" t="s">
-        <v>1283</v>
+        <v>1073</v>
       </c>
       <c r="C614" t="s">
-        <v>1037</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.3">
@@ -15279,10 +15546,10 @@
         <v>614</v>
       </c>
       <c r="B615" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="C615" t="s">
-        <v>1031</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.3">
@@ -15290,10 +15557,10 @@
         <v>615</v>
       </c>
       <c r="B616" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="C616" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.3">
@@ -15301,10 +15568,10 @@
         <v>616</v>
       </c>
       <c r="B617" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="C617" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.3">
@@ -15312,10 +15579,10 @@
         <v>617</v>
       </c>
       <c r="B618" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="C618" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.3">
@@ -15323,10 +15590,10 @@
         <v>618</v>
       </c>
       <c r="B619" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="C619" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.3">
@@ -15334,10 +15601,10 @@
         <v>619</v>
       </c>
       <c r="B620" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="C620" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.3">
@@ -15345,10 +15612,10 @@
         <v>620</v>
       </c>
       <c r="B621" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="C621" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.3">
@@ -15356,10 +15623,10 @@
         <v>621</v>
       </c>
       <c r="B622" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="C622" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.3">
@@ -15367,10 +15634,10 @@
         <v>622</v>
       </c>
       <c r="B623" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="C623" t="s">
-        <v>1077</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.3">
@@ -15378,10 +15645,10 @@
         <v>623</v>
       </c>
       <c r="B624" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="C624" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.3">
@@ -15389,10 +15656,10 @@
         <v>624</v>
       </c>
       <c r="B625" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="C625" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.3">
@@ -15400,10 +15667,10 @@
         <v>625</v>
       </c>
       <c r="B626" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="C626" t="s">
-        <v>1058</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.3">
@@ -15411,7 +15678,7 @@
         <v>626</v>
       </c>
       <c r="B627" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="C627" t="s">
         <v>1058</v>
@@ -15422,7 +15689,7 @@
         <v>627</v>
       </c>
       <c r="B628" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="C628" t="s">
         <v>1058</v>
@@ -15433,7 +15700,7 @@
         <v>628</v>
       </c>
       <c r="B629" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="C629" t="s">
         <v>1058</v>
@@ -15444,7 +15711,7 @@
         <v>629</v>
       </c>
       <c r="B630" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="C630" t="s">
         <v>1058</v>
@@ -15455,7 +15722,7 @@
         <v>630</v>
       </c>
       <c r="B631" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="C631" t="s">
         <v>1058</v>
@@ -15466,7 +15733,7 @@
         <v>631</v>
       </c>
       <c r="B632" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="C632" t="s">
         <v>1058</v>
@@ -15477,10 +15744,10 @@
         <v>632</v>
       </c>
       <c r="B633" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="C633" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.3">
@@ -15488,10 +15755,10 @@
         <v>633</v>
       </c>
       <c r="B634" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="C634" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.3">
@@ -15499,10 +15766,10 @@
         <v>634</v>
       </c>
       <c r="B635" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="C635" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.3">
@@ -15510,10 +15777,10 @@
         <v>635</v>
       </c>
       <c r="B636" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="C636" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.3">
@@ -15521,10 +15788,10 @@
         <v>636</v>
       </c>
       <c r="B637" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="C637" t="s">
-        <v>1080</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.3">
@@ -15532,10 +15799,10 @@
         <v>637</v>
       </c>
       <c r="B638" t="s">
-        <v>1081</v>
+        <v>1306</v>
       </c>
       <c r="C638" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.3">
@@ -15543,10 +15810,10 @@
         <v>638</v>
       </c>
       <c r="B639" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="C639" t="s">
-        <v>1093</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.3">
@@ -15554,21 +15821,21 @@
         <v>639</v>
       </c>
       <c r="B640" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="C640" t="s">
-        <v>1085</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A641">
         <v>640</v>
       </c>
-      <c r="B641" s="28" t="s">
-        <v>1086</v>
+      <c r="B641" t="s">
+        <v>1084</v>
       </c>
       <c r="C641" t="s">
-        <v>1321</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.3">
@@ -15576,10 +15843,10 @@
         <v>641</v>
       </c>
       <c r="B642" s="28" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C642" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.3">
@@ -15587,10 +15854,10 @@
         <v>642</v>
       </c>
       <c r="B643" s="28" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="C643" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.3">
@@ -15598,10 +15865,10 @@
         <v>643</v>
       </c>
       <c r="B644" s="28" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="C644" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.3">
@@ -15609,10 +15876,10 @@
         <v>644</v>
       </c>
       <c r="B645" s="28" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="C645" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.3">
@@ -15620,21 +15887,21 @@
         <v>645</v>
       </c>
       <c r="B646" s="28" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="C646" t="s">
-        <v>1092</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A647">
         <v>646</v>
       </c>
-      <c r="B647" t="s">
-        <v>1094</v>
+      <c r="B647" s="28" t="s">
+        <v>1091</v>
       </c>
       <c r="C647" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.3">
@@ -15642,21 +15909,21 @@
         <v>647</v>
       </c>
       <c r="B648" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="C648" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A649">
         <v>648</v>
       </c>
-      <c r="B649" s="28" t="s">
-        <v>1114</v>
+      <c r="B649" t="s">
+        <v>1096</v>
       </c>
       <c r="C649" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.3">
@@ -15664,10 +15931,10 @@
         <v>649</v>
       </c>
       <c r="B650" s="28" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="C650" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.3">
@@ -15675,10 +15942,10 @@
         <v>650</v>
       </c>
       <c r="B651" s="28" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C651" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.3">
@@ -15686,10 +15953,10 @@
         <v>651</v>
       </c>
       <c r="B652" s="28" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C652" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.3">
@@ -15697,21 +15964,21 @@
         <v>652</v>
       </c>
       <c r="B653" s="28" t="s">
-        <v>1102</v>
+        <v>1117</v>
       </c>
       <c r="C653" t="s">
-        <v>1105</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A654">
         <v>653</v>
       </c>
-      <c r="B654" t="s">
-        <v>1103</v>
+      <c r="B654" s="28" t="s">
+        <v>1102</v>
       </c>
       <c r="C654" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.3">
@@ -15719,10 +15986,10 @@
         <v>654</v>
       </c>
       <c r="B655" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C655" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.3">
@@ -15730,10 +15997,10 @@
         <v>655</v>
       </c>
       <c r="B656" t="s">
-        <v>1108</v>
+        <v>1104</v>
       </c>
       <c r="C656" t="s">
-        <v>1113</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.3">
@@ -15741,10 +16008,10 @@
         <v>656</v>
       </c>
       <c r="B657" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C657" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.3">
@@ -15752,10 +16019,10 @@
         <v>657</v>
       </c>
       <c r="B658" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C658" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.3">
@@ -15763,10 +16030,10 @@
         <v>658</v>
       </c>
       <c r="B659" t="s">
-        <v>1125</v>
+        <v>1110</v>
       </c>
       <c r="C659" t="s">
-        <v>1430</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.3">
@@ -15774,10 +16041,10 @@
         <v>659</v>
       </c>
       <c r="B660" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="C660" t="s">
-        <v>1119</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.3">
@@ -15785,10 +16052,10 @@
         <v>660</v>
       </c>
       <c r="B661" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="C661" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.3">
@@ -15796,10 +16063,10 @@
         <v>661</v>
       </c>
       <c r="B662" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="C662" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.3">
@@ -15807,10 +16074,10 @@
         <v>662</v>
       </c>
       <c r="B663" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="C663" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.3">
@@ -15818,10 +16085,10 @@
         <v>663</v>
       </c>
       <c r="B664" t="s">
-        <v>1123</v>
+        <v>1129</v>
       </c>
       <c r="C664" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.3">
@@ -15829,10 +16096,10 @@
         <v>664</v>
       </c>
       <c r="B665" t="s">
-        <v>1133</v>
+        <v>1620</v>
       </c>
       <c r="C665" t="s">
-        <v>1134</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.3">
@@ -15840,10 +16107,10 @@
         <v>665</v>
       </c>
       <c r="B666" t="s">
-        <v>1135</v>
+        <v>1123</v>
       </c>
       <c r="C666" t="s">
-        <v>1136</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.3">
@@ -15851,10 +16118,10 @@
         <v>666</v>
       </c>
       <c r="B667" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
       <c r="C667" t="s">
-        <v>1140</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.3">
@@ -15862,10 +16129,10 @@
         <v>667</v>
       </c>
       <c r="B668" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="C668" t="s">
-        <v>1141</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.3">
@@ -15873,10 +16140,10 @@
         <v>668</v>
       </c>
       <c r="B669" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="C669" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.3">
@@ -15884,10 +16151,10 @@
         <v>669</v>
       </c>
       <c r="B670" t="s">
-        <v>1143</v>
+        <v>1138</v>
       </c>
       <c r="C670" t="s">
-        <v>1146</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.3">
@@ -15895,10 +16162,10 @@
         <v>670</v>
       </c>
       <c r="B671" t="s">
-        <v>1144</v>
+        <v>1139</v>
       </c>
       <c r="C671" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.3">
@@ -15906,10 +16173,10 @@
         <v>671</v>
       </c>
       <c r="B672" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="C672" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.3">
@@ -15917,10 +16184,10 @@
         <v>672</v>
       </c>
       <c r="B673" t="s">
-        <v>1149</v>
+        <v>1144</v>
       </c>
       <c r="C673" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="674" spans="1:3" x14ac:dyDescent="0.3">
@@ -15928,10 +16195,10 @@
         <v>673</v>
       </c>
       <c r="B674" t="s">
-        <v>1154</v>
+        <v>1145</v>
       </c>
       <c r="C674" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.3">
@@ -15939,10 +16206,10 @@
         <v>674</v>
       </c>
       <c r="B675" t="s">
-        <v>1179</v>
+        <v>1149</v>
       </c>
       <c r="C675" t="s">
-        <v>1180</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.3">
@@ -15950,10 +16217,10 @@
         <v>675</v>
       </c>
       <c r="B676" t="s">
-        <v>1181</v>
+        <v>1154</v>
       </c>
       <c r="C676" t="s">
-        <v>1184</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="677" spans="1:3" x14ac:dyDescent="0.3">
@@ -15961,10 +16228,10 @@
         <v>676</v>
       </c>
       <c r="B677" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="C677" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.3">
@@ -15972,10 +16239,10 @@
         <v>677</v>
       </c>
       <c r="B678" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="C678" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.3">
@@ -15983,10 +16250,10 @@
         <v>678</v>
       </c>
       <c r="B679" t="s">
-        <v>1187</v>
+        <v>1182</v>
       </c>
       <c r="C679" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.3">
@@ -15994,10 +16261,10 @@
         <v>679</v>
       </c>
       <c r="B680" t="s">
-        <v>1189</v>
+        <v>1183</v>
       </c>
       <c r="C680" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.3">
@@ -16005,10 +16272,10 @@
         <v>680</v>
       </c>
       <c r="B681" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="C681" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.3">
@@ -16016,10 +16283,10 @@
         <v>681</v>
       </c>
       <c r="B682" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="C682" t="s">
-        <v>1194</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.3">
@@ -16027,10 +16294,10 @@
         <v>682</v>
       </c>
       <c r="B683" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="C683" t="s">
-        <v>1196</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.3">
@@ -16038,10 +16305,10 @@
         <v>683</v>
       </c>
       <c r="B684" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="C684" t="s">
-        <v>1200</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.3">
@@ -16049,10 +16316,10 @@
         <v>684</v>
       </c>
       <c r="B685" t="s">
-        <v>1201</v>
+        <v>1195</v>
       </c>
       <c r="C685" t="s">
-        <v>1205</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.3">
@@ -16060,10 +16327,10 @@
         <v>685</v>
       </c>
       <c r="B686" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
       <c r="C686" t="s">
-        <v>1206</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.3">
@@ -16071,10 +16338,10 @@
         <v>686</v>
       </c>
       <c r="B687" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="C687" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="688" spans="1:3" x14ac:dyDescent="0.3">
@@ -16082,10 +16349,10 @@
         <v>687</v>
       </c>
       <c r="B688" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="C688" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="689" spans="1:3" x14ac:dyDescent="0.3">
@@ -16093,10 +16360,10 @@
         <v>688</v>
       </c>
       <c r="B689" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
       <c r="C689" t="s">
-        <v>1198</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="690" spans="1:3" x14ac:dyDescent="0.3">
@@ -16104,10 +16371,10 @@
         <v>689</v>
       </c>
       <c r="B690" t="s">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="C690" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="691" spans="1:3" x14ac:dyDescent="0.3">
@@ -16115,10 +16382,10 @@
         <v>690</v>
       </c>
       <c r="B691" t="s">
-        <v>1210</v>
+        <v>1197</v>
       </c>
       <c r="C691" t="s">
-        <v>1212</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="692" spans="1:3" x14ac:dyDescent="0.3">
@@ -16126,10 +16393,10 @@
         <v>691</v>
       </c>
       <c r="B692" t="s">
-        <v>1213</v>
+        <v>1209</v>
       </c>
       <c r="C692" t="s">
-        <v>1222</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="693" spans="1:3" x14ac:dyDescent="0.3">
@@ -16137,10 +16404,10 @@
         <v>692</v>
       </c>
       <c r="B693" t="s">
-        <v>1214</v>
+        <v>1210</v>
       </c>
       <c r="C693" t="s">
-        <v>1223</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="694" spans="1:3" x14ac:dyDescent="0.3">
@@ -16148,10 +16415,10 @@
         <v>693</v>
       </c>
       <c r="B694" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="C694" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.3">
@@ -16159,10 +16426,10 @@
         <v>694</v>
       </c>
       <c r="B695" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="C695" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="696" spans="1:3" x14ac:dyDescent="0.3">
@@ -16170,10 +16437,10 @@
         <v>695</v>
       </c>
       <c r="B696" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="C696" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="697" spans="1:3" x14ac:dyDescent="0.3">
@@ -16181,10 +16448,10 @@
         <v>696</v>
       </c>
       <c r="B697" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="C697" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="698" spans="1:3" x14ac:dyDescent="0.3">
@@ -16192,10 +16459,10 @@
         <v>697</v>
       </c>
       <c r="B698" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="C698" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="699" spans="1:3" x14ac:dyDescent="0.3">
@@ -16203,10 +16470,10 @@
         <v>698</v>
       </c>
       <c r="B699" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="C699" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="700" spans="1:3" x14ac:dyDescent="0.3">
@@ -16214,10 +16481,10 @@
         <v>699</v>
       </c>
       <c r="B700" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="C700" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="701" spans="1:3" x14ac:dyDescent="0.3">
@@ -16225,10 +16492,10 @@
         <v>700</v>
       </c>
       <c r="B701" t="s">
-        <v>1307</v>
+        <v>1220</v>
       </c>
       <c r="C701" t="s">
-        <v>1313</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="702" spans="1:3" x14ac:dyDescent="0.3">
@@ -16236,10 +16503,10 @@
         <v>701</v>
       </c>
       <c r="B702" t="s">
-        <v>1308</v>
+        <v>1221</v>
       </c>
       <c r="C702" t="s">
-        <v>1314</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="703" spans="1:3" x14ac:dyDescent="0.3">
@@ -16247,10 +16514,10 @@
         <v>702</v>
       </c>
       <c r="B703" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="C703" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="704" spans="1:3" x14ac:dyDescent="0.3">
@@ -16258,10 +16525,10 @@
         <v>703</v>
       </c>
       <c r="B704" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="C704" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="705" spans="1:3" x14ac:dyDescent="0.3">
@@ -16269,10 +16536,10 @@
         <v>704</v>
       </c>
       <c r="B705" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="C705" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.3">
@@ -16280,10 +16547,10 @@
         <v>705</v>
       </c>
       <c r="B706" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="C706" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="707" spans="1:3" x14ac:dyDescent="0.3">
@@ -16291,10 +16558,10 @@
         <v>706</v>
       </c>
       <c r="B707" t="s">
-        <v>1319</v>
+        <v>1311</v>
       </c>
       <c r="C707" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="708" spans="1:3" x14ac:dyDescent="0.3">
@@ -16302,10 +16569,10 @@
         <v>707</v>
       </c>
       <c r="B708" t="s">
-        <v>1329</v>
+        <v>1312</v>
       </c>
       <c r="C708" t="s">
-        <v>1326</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="709" spans="1:3" x14ac:dyDescent="0.3">
@@ -16313,10 +16580,10 @@
         <v>708</v>
       </c>
       <c r="B709" t="s">
-        <v>1330</v>
+        <v>1319</v>
       </c>
       <c r="C709" t="s">
-        <v>1327</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="710" spans="1:3" x14ac:dyDescent="0.3">
@@ -16324,10 +16591,10 @@
         <v>709</v>
       </c>
       <c r="B710" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="C710" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="711" spans="1:3" x14ac:dyDescent="0.3">
@@ -16335,10 +16602,10 @@
         <v>710</v>
       </c>
       <c r="B711" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="C711" t="s">
-        <v>1333</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="712" spans="1:3" x14ac:dyDescent="0.3">
@@ -16346,10 +16613,10 @@
         <v>711</v>
       </c>
       <c r="B712" t="s">
-        <v>1339</v>
+        <v>1331</v>
       </c>
       <c r="C712" t="s">
-        <v>1334</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="713" spans="1:3" x14ac:dyDescent="0.3">
@@ -16357,10 +16624,10 @@
         <v>712</v>
       </c>
       <c r="B713" t="s">
-        <v>1340</v>
+        <v>1332</v>
       </c>
       <c r="C713" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="714" spans="1:3" x14ac:dyDescent="0.3">
@@ -16368,10 +16635,10 @@
         <v>713</v>
       </c>
       <c r="B714" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="C714" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="715" spans="1:3" x14ac:dyDescent="0.3">
@@ -16379,10 +16646,10 @@
         <v>714</v>
       </c>
       <c r="B715" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="C715" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="716" spans="1:3" x14ac:dyDescent="0.3">
@@ -16390,10 +16657,10 @@
         <v>715</v>
       </c>
       <c r="B716" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="C716" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.3">
@@ -16401,10 +16668,10 @@
         <v>716</v>
       </c>
       <c r="B717" t="s">
-        <v>1346</v>
+        <v>1342</v>
       </c>
       <c r="C717" t="s">
-        <v>1347</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="718" spans="1:3" x14ac:dyDescent="0.3">
@@ -16412,10 +16679,10 @@
         <v>717</v>
       </c>
       <c r="B718" t="s">
-        <v>1352</v>
+        <v>1343</v>
       </c>
       <c r="C718" t="s">
-        <v>1353</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="719" spans="1:3" x14ac:dyDescent="0.3">
@@ -16423,10 +16690,10 @@
         <v>718</v>
       </c>
       <c r="B719" t="s">
-        <v>1354</v>
+        <v>1346</v>
       </c>
       <c r="C719" t="s">
-        <v>1355</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="720" spans="1:3" x14ac:dyDescent="0.3">
@@ -16434,10 +16701,10 @@
         <v>719</v>
       </c>
       <c r="B720" t="s">
-        <v>1359</v>
+        <v>1352</v>
       </c>
       <c r="C720" t="s">
-        <v>1362</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="721" spans="1:3" x14ac:dyDescent="0.3">
@@ -16445,10 +16712,10 @@
         <v>720</v>
       </c>
       <c r="B721" t="s">
-        <v>1360</v>
+        <v>1354</v>
       </c>
       <c r="C721" t="s">
-        <v>1363</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="722" spans="1:3" x14ac:dyDescent="0.3">
@@ -16456,10 +16723,10 @@
         <v>721</v>
       </c>
       <c r="B722" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="C722" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="723" spans="1:3" x14ac:dyDescent="0.3">
@@ -16467,10 +16734,10 @@
         <v>722</v>
       </c>
       <c r="B723" t="s">
-        <v>1365</v>
+        <v>1360</v>
       </c>
       <c r="C723" t="s">
-        <v>1366</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="724" spans="1:3" x14ac:dyDescent="0.3">
@@ -16478,10 +16745,10 @@
         <v>723</v>
       </c>
       <c r="B724" t="s">
-        <v>1367</v>
+        <v>1361</v>
       </c>
       <c r="C724" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="725" spans="1:3" x14ac:dyDescent="0.3">
@@ -16489,10 +16756,10 @@
         <v>724</v>
       </c>
       <c r="B725" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="C725" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="726" spans="1:3" x14ac:dyDescent="0.3">
@@ -16500,10 +16767,10 @@
         <v>725</v>
       </c>
       <c r="B726" t="s">
-        <v>1379</v>
+        <v>1367</v>
       </c>
       <c r="C726" t="s">
-        <v>1380</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="727" spans="1:3" x14ac:dyDescent="0.3">
@@ -16511,10 +16778,10 @@
         <v>726</v>
       </c>
       <c r="B727" t="s">
-        <v>1381</v>
+        <v>1369</v>
       </c>
       <c r="C727" t="s">
-        <v>1382</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.3">
@@ -16522,10 +16789,10 @@
         <v>727</v>
       </c>
       <c r="B728" t="s">
-        <v>1383</v>
+        <v>1379</v>
       </c>
       <c r="C728" t="s">
-        <v>1384</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="729" spans="1:3" x14ac:dyDescent="0.3">
@@ -16533,10 +16800,10 @@
         <v>728</v>
       </c>
       <c r="B729" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
       <c r="C729" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="730" spans="1:3" x14ac:dyDescent="0.3">
@@ -16544,10 +16811,10 @@
         <v>729</v>
       </c>
       <c r="B730" t="s">
-        <v>1387</v>
+        <v>1383</v>
       </c>
       <c r="C730" t="s">
-        <v>1388</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="731" spans="1:3" x14ac:dyDescent="0.3">
@@ -16555,10 +16822,10 @@
         <v>730</v>
       </c>
       <c r="B731" t="s">
-        <v>1391</v>
+        <v>1385</v>
       </c>
       <c r="C731" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="732" spans="1:3" x14ac:dyDescent="0.3">
@@ -16566,10 +16833,10 @@
         <v>731</v>
       </c>
       <c r="B732" t="s">
-        <v>1392</v>
+        <v>1387</v>
       </c>
       <c r="C732" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="733" spans="1:3" x14ac:dyDescent="0.3">
@@ -16577,10 +16844,10 @@
         <v>732</v>
       </c>
       <c r="B733" t="s">
-        <v>1416</v>
+        <v>1391</v>
       </c>
       <c r="C733" t="s">
-        <v>1422</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="734" spans="1:3" x14ac:dyDescent="0.3">
@@ -16588,10 +16855,10 @@
         <v>733</v>
       </c>
       <c r="B734" t="s">
-        <v>1417</v>
+        <v>1392</v>
       </c>
       <c r="C734" t="s">
-        <v>1423</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="735" spans="1:3" x14ac:dyDescent="0.3">
@@ -16599,10 +16866,10 @@
         <v>734</v>
       </c>
       <c r="B735" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="C735" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="736" spans="1:3" x14ac:dyDescent="0.3">
@@ -16610,10 +16877,10 @@
         <v>735</v>
       </c>
       <c r="B736" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="C736" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="737" spans="1:3" x14ac:dyDescent="0.3">
@@ -16621,10 +16888,10 @@
         <v>736</v>
       </c>
       <c r="B737" t="s">
-        <v>1431</v>
+        <v>1418</v>
       </c>
       <c r="C737" t="s">
-        <v>1432</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="738" spans="1:3" x14ac:dyDescent="0.3">
@@ -16632,10 +16899,10 @@
         <v>737</v>
       </c>
       <c r="B738" t="s">
-        <v>1452</v>
+        <v>1419</v>
       </c>
       <c r="C738" t="s">
-        <v>1454</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.3">
@@ -16643,10 +16910,10 @@
         <v>738</v>
       </c>
       <c r="B739" t="s">
-        <v>1453</v>
+        <v>1431</v>
       </c>
       <c r="C739" t="s">
-        <v>1455</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="740" spans="1:3" x14ac:dyDescent="0.3">
@@ -16654,10 +16921,10 @@
         <v>739</v>
       </c>
       <c r="B740" t="s">
-        <v>1456</v>
+        <v>1452</v>
       </c>
       <c r="C740" t="s">
-        <v>1458</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="741" spans="1:3" x14ac:dyDescent="0.3">
@@ -16665,10 +16932,10 @@
         <v>740</v>
       </c>
       <c r="B741" t="s">
-        <v>1457</v>
+        <v>1453</v>
       </c>
       <c r="C741" t="s">
-        <v>1459</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="742" spans="1:3" x14ac:dyDescent="0.3">
@@ -16676,10 +16943,10 @@
         <v>741</v>
       </c>
       <c r="B742" t="s">
-        <v>1460</v>
+        <v>1456</v>
       </c>
       <c r="C742" t="s">
-        <v>1468</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="743" spans="1:3" x14ac:dyDescent="0.3">
@@ -16687,10 +16954,10 @@
         <v>742</v>
       </c>
       <c r="B743" t="s">
-        <v>1461</v>
+        <v>1457</v>
       </c>
       <c r="C743" t="s">
-        <v>1469</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="744" spans="1:3" x14ac:dyDescent="0.3">
@@ -16698,10 +16965,10 @@
         <v>743</v>
       </c>
       <c r="B744" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="C744" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="745" spans="1:3" x14ac:dyDescent="0.3">
@@ -16709,10 +16976,10 @@
         <v>744</v>
       </c>
       <c r="B745" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="C745" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="746" spans="1:3" x14ac:dyDescent="0.3">
@@ -16720,10 +16987,10 @@
         <v>745</v>
       </c>
       <c r="B746" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="C746" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="747" spans="1:3" x14ac:dyDescent="0.3">
@@ -16731,10 +16998,10 @@
         <v>746</v>
       </c>
       <c r="B747" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="C747" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="748" spans="1:3" x14ac:dyDescent="0.3">
@@ -16742,10 +17009,10 @@
         <v>747</v>
       </c>
       <c r="B748" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
       <c r="C748" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="749" spans="1:3" x14ac:dyDescent="0.3">
@@ -16753,10 +17020,10 @@
         <v>748</v>
       </c>
       <c r="B749" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="C749" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.3">
@@ -16764,10 +17031,10 @@
         <v>749</v>
       </c>
       <c r="B750" t="s">
-        <v>1476</v>
+        <v>1466</v>
       </c>
       <c r="C750" t="s">
-        <v>1486</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="751" spans="1:3" x14ac:dyDescent="0.3">
@@ -16775,10 +17042,10 @@
         <v>750</v>
       </c>
       <c r="B751" t="s">
-        <v>1477</v>
+        <v>1467</v>
       </c>
       <c r="C751" t="s">
-        <v>1486</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="752" spans="1:3" x14ac:dyDescent="0.3">
@@ -16786,7 +17053,7 @@
         <v>751</v>
       </c>
       <c r="B752" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="C752" t="s">
         <v>1486</v>
@@ -16797,7 +17064,7 @@
         <v>752</v>
       </c>
       <c r="B753" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="C753" t="s">
         <v>1486</v>
@@ -16808,7 +17075,7 @@
         <v>753</v>
       </c>
       <c r="B754" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="C754" t="s">
         <v>1486</v>
@@ -16819,10 +17086,10 @@
         <v>754</v>
       </c>
       <c r="B755" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="C755" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="756" spans="1:3" x14ac:dyDescent="0.3">
@@ -16830,10 +17097,10 @@
         <v>755</v>
       </c>
       <c r="B756" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="C756" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="757" spans="1:3" x14ac:dyDescent="0.3">
@@ -16841,7 +17108,7 @@
         <v>756</v>
       </c>
       <c r="B757" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="C757" t="s">
         <v>1487</v>
@@ -16852,7 +17119,7 @@
         <v>757</v>
       </c>
       <c r="B758" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="C758" t="s">
         <v>1487</v>
@@ -16863,7 +17130,7 @@
         <v>758</v>
       </c>
       <c r="B759" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="C759" t="s">
         <v>1487</v>
@@ -16874,10 +17141,10 @@
         <v>759</v>
       </c>
       <c r="B760" t="s">
-        <v>1488</v>
+        <v>1484</v>
       </c>
       <c r="C760" t="s">
-        <v>1490</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.3">
@@ -16885,10 +17152,10 @@
         <v>760</v>
       </c>
       <c r="B761" t="s">
-        <v>1489</v>
+        <v>1485</v>
       </c>
       <c r="C761" t="s">
-        <v>1491</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="762" spans="1:3" x14ac:dyDescent="0.3">
@@ -16896,10 +17163,10 @@
         <v>761</v>
       </c>
       <c r="B762" t="s">
-        <v>1492</v>
+        <v>1488</v>
       </c>
       <c r="C762" t="s">
-        <v>1493</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="763" spans="1:3" x14ac:dyDescent="0.3">
@@ -16907,10 +17174,10 @@
         <v>762</v>
       </c>
       <c r="B763" t="s">
-        <v>1495</v>
+        <v>1489</v>
       </c>
       <c r="C763" t="s">
-        <v>1494</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="764" spans="1:3" x14ac:dyDescent="0.3">
@@ -16918,10 +17185,10 @@
         <v>763</v>
       </c>
       <c r="B764" t="s">
-        <v>1497</v>
+        <v>1492</v>
       </c>
       <c r="C764" t="s">
-        <v>1498</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="765" spans="1:3" x14ac:dyDescent="0.3">
@@ -16929,10 +17196,10 @@
         <v>764</v>
       </c>
       <c r="B765" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="C765" t="s">
-        <v>1499</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="766" spans="1:3" x14ac:dyDescent="0.3">
@@ -16940,10 +17207,10 @@
         <v>765</v>
       </c>
       <c r="B766" t="s">
-        <v>1500</v>
+        <v>1497</v>
       </c>
       <c r="C766" t="s">
-        <v>1506</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="767" spans="1:3" x14ac:dyDescent="0.3">
@@ -16951,10 +17218,10 @@
         <v>766</v>
       </c>
       <c r="B767" t="s">
-        <v>1501</v>
+        <v>1496</v>
       </c>
       <c r="C767" t="s">
-        <v>1507</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="768" spans="1:3" x14ac:dyDescent="0.3">
@@ -16962,10 +17229,10 @@
         <v>767</v>
       </c>
       <c r="B768" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="C768" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="769" spans="1:3" x14ac:dyDescent="0.3">
@@ -16973,10 +17240,10 @@
         <v>768</v>
       </c>
       <c r="B769" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="C769" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="770" spans="1:3" x14ac:dyDescent="0.3">
@@ -16984,10 +17251,10 @@
         <v>769</v>
       </c>
       <c r="B770" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="C770" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="771" spans="1:3" x14ac:dyDescent="0.3">
@@ -16995,10 +17262,439 @@
         <v>770</v>
       </c>
       <c r="B771" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C771" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="772" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A772">
+        <v>771</v>
+      </c>
+      <c r="B772" t="s">
+        <v>1504</v>
+      </c>
+      <c r="C772" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="773" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A773">
+        <v>772</v>
+      </c>
+      <c r="B773" t="s">
         <v>1505</v>
       </c>
-      <c r="C771" t="s">
+      <c r="C773" t="s">
         <v>1511</v>
+      </c>
+    </row>
+    <row r="774" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A774">
+        <v>773</v>
+      </c>
+      <c r="B774" t="s">
+        <v>1556</v>
+      </c>
+      <c r="C774" t="s">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="775" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A775">
+        <v>774</v>
+      </c>
+      <c r="B775" t="s">
+        <v>1550</v>
+      </c>
+      <c r="C775" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="776" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A776">
+        <v>775</v>
+      </c>
+      <c r="B776" t="s">
+        <v>1551</v>
+      </c>
+      <c r="C776" t="s">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="777" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A777">
+        <v>776</v>
+      </c>
+      <c r="B777" t="s">
+        <v>1552</v>
+      </c>
+      <c r="C777" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="778" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A778">
+        <v>777</v>
+      </c>
+      <c r="B778" t="s">
+        <v>1553</v>
+      </c>
+      <c r="C778" t="s">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="779" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A779">
+        <v>778</v>
+      </c>
+      <c r="B779" t="s">
+        <v>1554</v>
+      </c>
+      <c r="C779" t="s">
+        <v>1561</v>
+      </c>
+    </row>
+    <row r="780" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A780">
+        <v>779</v>
+      </c>
+      <c r="B780" t="s">
+        <v>1555</v>
+      </c>
+      <c r="C780" t="s">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="781" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A781">
+        <v>780</v>
+      </c>
+      <c r="B781" t="s">
+        <v>1604</v>
+      </c>
+      <c r="C781" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="782" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A782">
+        <v>781</v>
+      </c>
+      <c r="B782" t="s">
+        <v>1564</v>
+      </c>
+      <c r="C782" t="s">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="783" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A783">
+        <v>782</v>
+      </c>
+      <c r="B783" t="s">
+        <v>1565</v>
+      </c>
+      <c r="C783" t="s">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="784" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A784">
+        <v>783</v>
+      </c>
+      <c r="B784" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C784" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="785" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A785">
+        <v>784</v>
+      </c>
+      <c r="B785" t="s">
+        <v>1567</v>
+      </c>
+      <c r="C785" t="s">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="786" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A786">
+        <v>785</v>
+      </c>
+      <c r="B786" t="s">
+        <v>1568</v>
+      </c>
+      <c r="C786" t="s">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="787" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A787">
+        <v>786</v>
+      </c>
+      <c r="B787" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C787" t="s">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="788" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A788">
+        <v>787</v>
+      </c>
+      <c r="B788" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C788" t="s">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="789" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A789">
+        <v>788</v>
+      </c>
+      <c r="B789" t="s">
+        <v>1606</v>
+      </c>
+      <c r="C789" t="s">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="790" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A790">
+        <v>789</v>
+      </c>
+      <c r="B790" t="s">
+        <v>1547</v>
+      </c>
+      <c r="C790" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="791" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A791">
+        <v>790</v>
+      </c>
+      <c r="B791" t="s">
+        <v>1548</v>
+      </c>
+      <c r="C791" t="s">
+        <v>1576</v>
+      </c>
+    </row>
+    <row r="792" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A792">
+        <v>791</v>
+      </c>
+      <c r="B792" t="s">
+        <v>1579</v>
+      </c>
+      <c r="C792" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="793" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A793">
+        <v>792</v>
+      </c>
+      <c r="B793" t="s">
+        <v>1580</v>
+      </c>
+      <c r="C793" t="s">
+        <v>1618</v>
+      </c>
+    </row>
+    <row r="794" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A794">
+        <v>793</v>
+      </c>
+      <c r="B794" t="s">
+        <v>1581</v>
+      </c>
+      <c r="C794" t="s">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="795" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A795">
+        <v>794</v>
+      </c>
+      <c r="B795" t="s">
+        <v>1582</v>
+      </c>
+      <c r="C795" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="796" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A796">
+        <v>795</v>
+      </c>
+      <c r="B796" t="s">
+        <v>1590</v>
+      </c>
+      <c r="C796" t="s">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="797" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A797">
+        <v>796</v>
+      </c>
+      <c r="B797" t="s">
+        <v>1591</v>
+      </c>
+      <c r="C797" t="s">
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="798" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A798">
+        <v>797</v>
+      </c>
+      <c r="B798" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C798" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="799" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A799">
+        <v>798</v>
+      </c>
+      <c r="B799" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C799" t="s">
+        <v>1587</v>
+      </c>
+    </row>
+    <row r="800" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A800">
+        <v>799</v>
+      </c>
+      <c r="B800" t="s">
+        <v>1594</v>
+      </c>
+      <c r="C800" t="s">
+        <v>1588</v>
+      </c>
+    </row>
+    <row r="801" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A801">
+        <v>800</v>
+      </c>
+      <c r="B801" t="s">
+        <v>1595</v>
+      </c>
+      <c r="C801" t="s">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="802" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A802">
+        <v>801</v>
+      </c>
+      <c r="B802" t="s">
+        <v>1596</v>
+      </c>
+      <c r="C802" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="803" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A803">
+        <v>802</v>
+      </c>
+      <c r="B803" t="s">
+        <v>1601</v>
+      </c>
+      <c r="C803" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="804" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A804">
+        <v>803</v>
+      </c>
+      <c r="B804" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C804" t="s">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="805" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A805">
+        <v>804</v>
+      </c>
+      <c r="B805" t="s">
+        <v>1603</v>
+      </c>
+      <c r="C805" t="s">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="806" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A806">
+        <v>805</v>
+      </c>
+      <c r="B806" t="s">
+        <v>1607</v>
+      </c>
+      <c r="C806" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="807" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A807">
+        <v>806</v>
+      </c>
+      <c r="B807" t="s">
+        <v>1612</v>
+      </c>
+      <c r="C807" t="s">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="808" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A808">
+        <v>807</v>
+      </c>
+      <c r="B808" t="s">
+        <v>1613</v>
+      </c>
+      <c r="C808" t="s">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="809" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A809">
+        <v>808</v>
+      </c>
+      <c r="B809" t="s">
+        <v>1614</v>
+      </c>
+      <c r="C809" t="s">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="810" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A810">
+        <v>809</v>
+      </c>
+      <c r="B810" t="s">
+        <v>1615</v>
+      </c>
+      <c r="C810" t="s">
+        <v>1611</v>
       </c>
     </row>
   </sheetData>

--- a/30_table/01_테스트버전/Table_STR_String.xlsx
+++ b/30_table/01_테스트버전/Table_STR_String.xlsx
@@ -3025,14 +3025,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>생각보다 간단하죠.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>소지품을 선택해서 아이템을 선택하세요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>그러면 사용할 수 있는 아이템은 사용버튼이 나옵니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3065,10 +3057,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>소지품을 선택해서 아이템을 선택해 보게.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>무기나 방어구를 선택하면 장착 버튼이 나올걸세.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3149,18 +3137,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>어이, 안녕하신가? 난 잠시 쉬는 중이야.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>그럼 각성을 시도해 봐.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>더 강해지고 싶어?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>각성은 5번까지만 가능해.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3226,10 +3206,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>영웅 메뉴를 누르면 영웅 관리창이 나오는데,</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>빈 슬롯을 선택하면 영웅을 소환할 수 있다네.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3545,10 +3521,6 @@
     <t>동쪽 숲 1</t>
   </si>
   <si>
-    <t>소지품을 선택해서 가방확장을 누르면 가방을 확장할 수 있다네.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>광산 마을 입구</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5585,6 +5557,34 @@
   </si>
   <si>
     <t>개발실</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생각보다 어렵지 않아요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일단 소지품 버튼을 눌러서 아이템을 선택하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소지품 버튼을 눌러서 아이템을 선택해 보게.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소지품 버튼을 눌러서 가방확장을 누르면 가방을 확장할 수 있다네.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅 버튼을 누르면 영웅 관리창이 나오는데,</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안녕? 뭐 궁금한 거 있어?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>더 강해지고 싶다구?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -9840,7 +9840,7 @@
         <v>38</v>
       </c>
       <c r="C96" t="s">
-        <v>1151</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
@@ -9851,7 +9851,7 @@
         <v>39</v>
       </c>
       <c r="C97" t="s">
-        <v>1152</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
@@ -9884,7 +9884,7 @@
         <v>486</v>
       </c>
       <c r="C100" t="s">
-        <v>1541</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
@@ -9895,7 +9895,7 @@
         <v>487</v>
       </c>
       <c r="C101" t="s">
-        <v>1528</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
@@ -10225,7 +10225,7 @@
         <v>601</v>
       </c>
       <c r="C131" t="s">
-        <v>1351</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
@@ -10984,7 +10984,7 @@
         <v>516</v>
       </c>
       <c r="C200" t="s">
-        <v>1542</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
@@ -10995,7 +10995,7 @@
         <v>517</v>
       </c>
       <c r="C201" t="s">
-        <v>1529</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
@@ -11006,7 +11006,7 @@
         <v>54</v>
       </c>
       <c r="C202" t="s">
-        <v>1026</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
@@ -11017,7 +11017,7 @@
         <v>55</v>
       </c>
       <c r="C203" t="s">
-        <v>1027</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
@@ -11028,7 +11028,7 @@
         <v>56</v>
       </c>
       <c r="C204" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
@@ -11039,7 +11039,7 @@
         <v>57</v>
       </c>
       <c r="C205" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
@@ -11050,7 +11050,7 @@
         <v>58</v>
       </c>
       <c r="C206" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
@@ -11058,10 +11058,10 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>1403</v>
+        <v>1396</v>
       </c>
       <c r="C207" t="s">
-        <v>1404</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.3">
@@ -11105,7 +11105,7 @@
         <v>62</v>
       </c>
       <c r="C211" t="s">
-        <v>1130</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
@@ -11116,7 +11116,7 @@
         <v>63</v>
       </c>
       <c r="C212" t="s">
-        <v>1131</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
@@ -11127,7 +11127,7 @@
         <v>64</v>
       </c>
       <c r="C213" t="s">
-        <v>1155</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
@@ -11138,7 +11138,7 @@
         <v>65</v>
       </c>
       <c r="C214" t="s">
-        <v>1156</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
@@ -11149,7 +11149,7 @@
         <v>66</v>
       </c>
       <c r="C215" t="s">
-        <v>1512</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
@@ -11160,7 +11160,7 @@
         <v>67</v>
       </c>
       <c r="C216" t="s">
-        <v>1513</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
@@ -11171,7 +11171,7 @@
         <v>68</v>
       </c>
       <c r="C217" t="s">
-        <v>1514</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
@@ -11182,7 +11182,7 @@
         <v>69</v>
       </c>
       <c r="C218" t="s">
-        <v>1515</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
@@ -11608,7 +11608,7 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>1231</v>
+        <v>1224</v>
       </c>
       <c r="C257" t="s">
         <v>253</v>
@@ -11619,7 +11619,7 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>1232</v>
+        <v>1225</v>
       </c>
       <c r="C258" t="s">
         <v>254</v>
@@ -11630,7 +11630,7 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>1233</v>
+        <v>1226</v>
       </c>
       <c r="C259" t="s">
         <v>252</v>
@@ -11641,7 +11641,7 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>1234</v>
+        <v>1227</v>
       </c>
       <c r="C260" t="s">
         <v>355</v>
@@ -11652,7 +11652,7 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>1235</v>
+        <v>1228</v>
       </c>
       <c r="C261" t="s">
         <v>356</v>
@@ -11663,7 +11663,7 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>1236</v>
+        <v>1229</v>
       </c>
       <c r="C262" t="s">
         <v>372</v>
@@ -11674,7 +11674,7 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>1237</v>
+        <v>1230</v>
       </c>
       <c r="C263" t="s">
         <v>371</v>
@@ -11729,7 +11729,7 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>1238</v>
+        <v>1231</v>
       </c>
       <c r="C268" t="s">
         <v>92</v>
@@ -11740,7 +11740,7 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>1239</v>
+        <v>1232</v>
       </c>
       <c r="C269" t="s">
         <v>255</v>
@@ -11751,7 +11751,7 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>1240</v>
+        <v>1233</v>
       </c>
       <c r="C270" t="s">
         <v>296</v>
@@ -11762,7 +11762,7 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>1241</v>
+        <v>1234</v>
       </c>
       <c r="C271" t="s">
         <v>256</v>
@@ -11773,10 +11773,10 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>1242</v>
+        <v>1235</v>
       </c>
       <c r="C272" t="s">
-        <v>1076</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
@@ -11784,10 +11784,10 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>1243</v>
+        <v>1236</v>
       </c>
       <c r="C273" t="s">
-        <v>1061</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.3">
@@ -11795,7 +11795,7 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>1244</v>
+        <v>1237</v>
       </c>
       <c r="C274" t="s">
         <v>357</v>
@@ -11809,7 +11809,7 @@
         <v>87</v>
       </c>
       <c r="C275" t="s">
-        <v>1429</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.3">
@@ -12051,7 +12051,7 @@
         <v>88</v>
       </c>
       <c r="C297" t="s">
-        <v>1433</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.3">
@@ -12062,7 +12062,7 @@
         <v>89</v>
       </c>
       <c r="C298" t="s">
-        <v>1433</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
@@ -12073,7 +12073,7 @@
         <v>108</v>
       </c>
       <c r="C299" t="s">
-        <v>1434</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
@@ -12084,7 +12084,7 @@
         <v>109</v>
       </c>
       <c r="C300" t="s">
-        <v>1435</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.3">
@@ -12095,7 +12095,7 @@
         <v>110</v>
       </c>
       <c r="C301" t="s">
-        <v>1436</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.3">
@@ -12106,7 +12106,7 @@
         <v>111</v>
       </c>
       <c r="C302" t="s">
-        <v>1437</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.3">
@@ -12117,7 +12117,7 @@
         <v>112</v>
       </c>
       <c r="C303" t="s">
-        <v>1438</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.3">
@@ -12128,7 +12128,7 @@
         <v>113</v>
       </c>
       <c r="C304" t="s">
-        <v>1439</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.3">
@@ -12139,7 +12139,7 @@
         <v>114</v>
       </c>
       <c r="C305" t="s">
-        <v>1440</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.3">
@@ -12150,7 +12150,7 @@
         <v>115</v>
       </c>
       <c r="C306" t="s">
-        <v>1441</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.3">
@@ -12161,7 +12161,7 @@
         <v>116</v>
       </c>
       <c r="C307" t="s">
-        <v>1442</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.3">
@@ -12172,7 +12172,7 @@
         <v>117</v>
       </c>
       <c r="C308" t="s">
-        <v>1443</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.3">
@@ -12183,7 +12183,7 @@
         <v>118</v>
       </c>
       <c r="C309" t="s">
-        <v>1444</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.3">
@@ -12194,7 +12194,7 @@
         <v>119</v>
       </c>
       <c r="C310" t="s">
-        <v>1445</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.3">
@@ -12205,7 +12205,7 @@
         <v>120</v>
       </c>
       <c r="C311" t="s">
-        <v>1446</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.3">
@@ -12216,7 +12216,7 @@
         <v>121</v>
       </c>
       <c r="C312" t="s">
-        <v>1447</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.3">
@@ -12227,7 +12227,7 @@
         <v>122</v>
       </c>
       <c r="C313" t="s">
-        <v>1448</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.3">
@@ -12238,7 +12238,7 @@
         <v>394</v>
       </c>
       <c r="C314" t="s">
-        <v>1449</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.3">
@@ -12249,7 +12249,7 @@
         <v>395</v>
       </c>
       <c r="C315" t="s">
-        <v>1445</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.3">
@@ -12260,7 +12260,7 @@
         <v>396</v>
       </c>
       <c r="C316" t="s">
-        <v>1450</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.3">
@@ -12271,7 +12271,7 @@
         <v>397</v>
       </c>
       <c r="C317" t="s">
-        <v>1451</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.3">
@@ -12282,7 +12282,7 @@
         <v>398</v>
       </c>
       <c r="C318" t="s">
-        <v>1448</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.3">
@@ -12293,7 +12293,7 @@
         <v>162</v>
       </c>
       <c r="C319" t="s">
-        <v>1530</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.3">
@@ -12568,7 +12568,7 @@
         <v>190</v>
       </c>
       <c r="C344" t="s">
-        <v>1344</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.3">
@@ -12818,10 +12818,10 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>1406</v>
+        <v>1399</v>
       </c>
       <c r="C367" t="s">
-        <v>1405</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.3">
@@ -12840,10 +12840,10 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>1356</v>
+        <v>1349</v>
       </c>
       <c r="C369" s="27" t="s">
-        <v>1348</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.3">
@@ -12854,7 +12854,7 @@
         <v>215</v>
       </c>
       <c r="C370" t="s">
-        <v>1345</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.3">
@@ -12862,10 +12862,10 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>1358</v>
+        <v>1351</v>
       </c>
       <c r="C371" t="s">
-        <v>1357</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.3">
@@ -12887,7 +12887,7 @@
         <v>218</v>
       </c>
       <c r="C373" t="s">
-        <v>1520</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.3">
@@ -12898,7 +12898,7 @@
         <v>219</v>
       </c>
       <c r="C374" t="s">
-        <v>1521</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.3">
@@ -12931,7 +12931,7 @@
         <v>225</v>
       </c>
       <c r="C377" t="s">
-        <v>1519</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.3">
@@ -12953,7 +12953,7 @@
         <v>226</v>
       </c>
       <c r="C379" t="s">
-        <v>1518</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.3">
@@ -12986,7 +12986,7 @@
         <v>230</v>
       </c>
       <c r="C382" t="s">
-        <v>1522</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.3">
@@ -13052,7 +13052,7 @@
         <v>239</v>
       </c>
       <c r="C388" t="s">
-        <v>1349</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.3">
@@ -13063,7 +13063,7 @@
         <v>240</v>
       </c>
       <c r="C389" t="s">
-        <v>1350</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.3">
@@ -13118,7 +13118,7 @@
         <v>250</v>
       </c>
       <c r="C394" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.3">
@@ -13137,10 +13137,10 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="C396" t="s">
-        <v>1413</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.3">
@@ -13148,10 +13148,10 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
       <c r="C397" t="s">
-        <v>1546</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.3">
@@ -13159,10 +13159,10 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>1411</v>
+        <v>1404</v>
       </c>
       <c r="C398" t="s">
-        <v>1414</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.3">
@@ -13170,10 +13170,10 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>1412</v>
+        <v>1405</v>
       </c>
       <c r="C399" t="s">
-        <v>1415</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.3">
@@ -13203,10 +13203,10 @@
         <v>401</v>
       </c>
       <c r="B402" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
       <c r="C402" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.3">
@@ -13214,10 +13214,10 @@
         <v>402</v>
       </c>
       <c r="B403" t="s">
-        <v>995</v>
+        <v>989</v>
       </c>
       <c r="C403" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.3">
@@ -13225,10 +13225,10 @@
         <v>403</v>
       </c>
       <c r="B404" t="s">
-        <v>1393</v>
+        <v>1386</v>
       </c>
       <c r="C404" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.3">
@@ -13236,10 +13236,10 @@
         <v>404</v>
       </c>
       <c r="B405" t="s">
-        <v>1394</v>
+        <v>1387</v>
       </c>
       <c r="C405" t="s">
-        <v>1395</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.3">
@@ -13247,10 +13247,10 @@
         <v>405</v>
       </c>
       <c r="B406" t="s">
-        <v>1516</v>
+        <v>1509</v>
       </c>
       <c r="C406" t="s">
-        <v>1517</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.3">
@@ -13261,7 +13261,7 @@
         <v>259</v>
       </c>
       <c r="C407" t="s">
-        <v>1531</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.3">
@@ -13382,7 +13382,7 @@
         <v>363</v>
       </c>
       <c r="C418" t="s">
-        <v>1532</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.3">
@@ -13393,7 +13393,7 @@
         <v>269</v>
       </c>
       <c r="C419" t="s">
-        <v>1533</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.3">
@@ -13404,7 +13404,7 @@
         <v>270</v>
       </c>
       <c r="C420" t="s">
-        <v>1534</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.3">
@@ -13415,7 +13415,7 @@
         <v>271</v>
       </c>
       <c r="C421" t="s">
-        <v>1535</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.3">
@@ -13426,7 +13426,7 @@
         <v>272</v>
       </c>
       <c r="C422" t="s">
-        <v>1536</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.3">
@@ -13437,7 +13437,7 @@
         <v>273</v>
       </c>
       <c r="C423" t="s">
-        <v>1537</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.3">
@@ -13448,7 +13448,7 @@
         <v>274</v>
       </c>
       <c r="C424" t="s">
-        <v>1538</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.3">
@@ -13459,7 +13459,7 @@
         <v>275</v>
       </c>
       <c r="C425" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.3">
@@ -13533,10 +13533,10 @@
         <v>431</v>
       </c>
       <c r="B432" t="s">
-        <v>1157</v>
+        <v>1150</v>
       </c>
       <c r="C432" t="s">
-        <v>1162</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.3">
@@ -13544,10 +13544,10 @@
         <v>432</v>
       </c>
       <c r="B433" t="s">
-        <v>1158</v>
+        <v>1151</v>
       </c>
       <c r="C433" t="s">
-        <v>1163</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.3">
@@ -13555,10 +13555,10 @@
         <v>433</v>
       </c>
       <c r="B434" t="s">
-        <v>1159</v>
+        <v>1152</v>
       </c>
       <c r="C434" t="s">
-        <v>1164</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.3">
@@ -13566,10 +13566,10 @@
         <v>434</v>
       </c>
       <c r="B435" t="s">
-        <v>1160</v>
+        <v>1153</v>
       </c>
       <c r="C435" t="s">
-        <v>1165</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.3">
@@ -13577,10 +13577,10 @@
         <v>435</v>
       </c>
       <c r="B436" t="s">
-        <v>1161</v>
+        <v>1154</v>
       </c>
       <c r="C436" t="s">
-        <v>1166</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.3">
@@ -13588,10 +13588,10 @@
         <v>436</v>
       </c>
       <c r="B437" t="s">
-        <v>1409</v>
+        <v>1402</v>
       </c>
       <c r="C437" t="s">
-        <v>1167</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.3">
@@ -13599,10 +13599,10 @@
         <v>437</v>
       </c>
       <c r="B438" t="s">
-        <v>1410</v>
+        <v>1403</v>
       </c>
       <c r="C438" t="s">
-        <v>1168</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.3">
@@ -13610,10 +13610,10 @@
         <v>438</v>
       </c>
       <c r="B439" t="s">
-        <v>1407</v>
+        <v>1400</v>
       </c>
       <c r="C439" t="s">
-        <v>1408</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.3">
@@ -13635,7 +13635,7 @@
         <v>365</v>
       </c>
       <c r="C441" t="s">
-        <v>1540</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.3">
@@ -13646,7 +13646,7 @@
         <v>366</v>
       </c>
       <c r="C442" t="s">
-        <v>1539</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.3">
@@ -13657,7 +13657,7 @@
         <v>388</v>
       </c>
       <c r="C443" t="s">
-        <v>1544</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.3">
@@ -13698,10 +13698,10 @@
         <v>446</v>
       </c>
       <c r="B447" t="s">
-        <v>1169</v>
+        <v>1162</v>
       </c>
       <c r="C447" t="s">
-        <v>1173</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.3">
@@ -13709,10 +13709,10 @@
         <v>447</v>
       </c>
       <c r="B448" t="s">
-        <v>1170</v>
+        <v>1163</v>
       </c>
       <c r="C448" t="s">
-        <v>1174</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.3">
@@ -13720,10 +13720,10 @@
         <v>448</v>
       </c>
       <c r="B449" t="s">
-        <v>1171</v>
+        <v>1164</v>
       </c>
       <c r="C449" t="s">
-        <v>1175</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.3">
@@ -13731,10 +13731,10 @@
         <v>449</v>
       </c>
       <c r="B450" t="s">
-        <v>1172</v>
+        <v>1165</v>
       </c>
       <c r="C450" t="s">
-        <v>1176</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.3">
@@ -13742,10 +13742,10 @@
         <v>450</v>
       </c>
       <c r="B451" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="C451" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.3">
@@ -13753,10 +13753,10 @@
         <v>451</v>
       </c>
       <c r="B452" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="C452" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.3">
@@ -13764,10 +13764,10 @@
         <v>452</v>
       </c>
       <c r="B453" t="s">
-        <v>1424</v>
+        <v>1417</v>
       </c>
       <c r="C453" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.3">
@@ -13775,10 +13775,10 @@
         <v>453</v>
       </c>
       <c r="B454" t="s">
-        <v>1425</v>
+        <v>1418</v>
       </c>
       <c r="C454" t="s">
-        <v>1427</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.3">
@@ -13786,10 +13786,10 @@
         <v>454</v>
       </c>
       <c r="B455" t="s">
-        <v>1426</v>
+        <v>1419</v>
       </c>
       <c r="C455" t="s">
-        <v>1428</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.3">
@@ -13808,10 +13808,10 @@
         <v>456</v>
       </c>
       <c r="B457" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="C457" t="s">
-        <v>989</v>
+        <v>983</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.3">
@@ -13819,10 +13819,10 @@
         <v>457</v>
       </c>
       <c r="B458" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="C458" t="s">
-        <v>990</v>
+        <v>984</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.3">
@@ -13830,10 +13830,10 @@
         <v>458</v>
       </c>
       <c r="B459" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
       <c r="C459" t="s">
-        <v>1396</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.3">
@@ -13841,10 +13841,10 @@
         <v>459</v>
       </c>
       <c r="B460" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
       <c r="C460" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.3">
@@ -13852,10 +13852,10 @@
         <v>460</v>
       </c>
       <c r="B461" t="s">
-        <v>1177</v>
+        <v>1170</v>
       </c>
       <c r="C461" t="s">
-        <v>1178</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.3">
@@ -13863,10 +13863,10 @@
         <v>461</v>
       </c>
       <c r="B462" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C462" t="s">
         <v>1371</v>
-      </c>
-      <c r="C462" t="s">
-        <v>1378</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.3">
@@ -13874,10 +13874,10 @@
         <v>462</v>
       </c>
       <c r="B463" t="s">
-        <v>1372</v>
+        <v>1365</v>
       </c>
       <c r="C463" t="s">
-        <v>1399</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.3">
@@ -13885,10 +13885,10 @@
         <v>463</v>
       </c>
       <c r="B464" t="s">
-        <v>1373</v>
+        <v>1366</v>
       </c>
       <c r="C464" t="s">
-        <v>1400</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.3">
@@ -13896,10 +13896,10 @@
         <v>464</v>
       </c>
       <c r="B465" t="s">
-        <v>1374</v>
+        <v>1367</v>
       </c>
       <c r="C465" t="s">
-        <v>1401</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.3">
@@ -13907,10 +13907,10 @@
         <v>465</v>
       </c>
       <c r="B466" t="s">
-        <v>1375</v>
+        <v>1368</v>
       </c>
       <c r="C466" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.3">
@@ -13918,10 +13918,10 @@
         <v>466</v>
       </c>
       <c r="B467" t="s">
-        <v>1376</v>
+        <v>1369</v>
       </c>
       <c r="C467" t="s">
-        <v>1397</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.3">
@@ -13929,10 +13929,10 @@
         <v>467</v>
       </c>
       <c r="B468" t="s">
-        <v>1377</v>
+        <v>1370</v>
       </c>
       <c r="C468" t="s">
-        <v>1398</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.3">
@@ -14248,10 +14248,10 @@
         <v>496</v>
       </c>
       <c r="B497" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="C497" t="s">
-        <v>979</v>
+        <v>973</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.3">
@@ -14259,10 +14259,10 @@
         <v>497</v>
       </c>
       <c r="B498" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="C498" t="s">
-        <v>980</v>
+        <v>974</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.3">
@@ -14270,10 +14270,10 @@
         <v>498</v>
       </c>
       <c r="B499" t="s">
-        <v>1132</v>
+        <v>1125</v>
       </c>
       <c r="C499" t="s">
-        <v>979</v>
+        <v>973</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.3">
@@ -14281,10 +14281,10 @@
         <v>499</v>
       </c>
       <c r="B500" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="C500" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.3">
@@ -14292,10 +14292,10 @@
         <v>500</v>
       </c>
       <c r="B501" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="C501" t="s">
-        <v>1008</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.3">
@@ -14303,10 +14303,10 @@
         <v>501</v>
       </c>
       <c r="B502" t="s">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="C502" t="s">
-        <v>1007</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.3">
@@ -14314,10 +14314,10 @@
         <v>502</v>
       </c>
       <c r="B503" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="C503" t="s">
-        <v>1009</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.3">
@@ -14325,10 +14325,10 @@
         <v>503</v>
       </c>
       <c r="B504" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="C504" t="s">
-        <v>1011</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.3">
@@ -14336,10 +14336,10 @@
         <v>504</v>
       </c>
       <c r="B505" t="s">
-        <v>1024</v>
+        <v>1018</v>
       </c>
       <c r="C505" t="s">
-        <v>1025</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.3">
@@ -14347,10 +14347,10 @@
         <v>505</v>
       </c>
       <c r="B506" t="s">
-        <v>1001</v>
+        <v>995</v>
       </c>
       <c r="C506" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.3">
@@ -14358,10 +14358,10 @@
         <v>506</v>
       </c>
       <c r="B507" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="C507" t="s">
-        <v>1005</v>
+        <v>999</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.3">
@@ -14369,10 +14369,10 @@
         <v>507</v>
       </c>
       <c r="B508" t="s">
-        <v>1003</v>
+        <v>997</v>
       </c>
       <c r="C508" t="s">
-        <v>1006</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.3">
@@ -14380,10 +14380,10 @@
         <v>508</v>
       </c>
       <c r="B509" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="C509" t="s">
-        <v>1523</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.3">
@@ -14391,10 +14391,10 @@
         <v>509</v>
       </c>
       <c r="B510" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="C510" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.3">
@@ -14402,10 +14402,10 @@
         <v>510</v>
       </c>
       <c r="B511" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="C511" t="s">
-        <v>1017</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.3">
@@ -14413,10 +14413,10 @@
         <v>511</v>
       </c>
       <c r="B512" t="s">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="C512" t="s">
-        <v>1524</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.3">
@@ -14424,10 +14424,10 @@
         <v>512</v>
       </c>
       <c r="B513" t="s">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="C513" t="s">
-        <v>1525</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.3">
@@ -14435,10 +14435,10 @@
         <v>513</v>
       </c>
       <c r="B514" t="s">
-        <v>1019</v>
+        <v>1013</v>
       </c>
       <c r="C514" t="s">
-        <v>1021</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.3">
@@ -14446,10 +14446,10 @@
         <v>514</v>
       </c>
       <c r="B515" t="s">
-        <v>1022</v>
+        <v>1016</v>
       </c>
       <c r="C515" t="s">
-        <v>1023</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.3">
@@ -14526,7 +14526,7 @@
         <v>865</v>
       </c>
       <c r="C522" t="s">
-        <v>1062</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.3">
@@ -14534,10 +14534,10 @@
         <v>522</v>
       </c>
       <c r="B523" t="s">
-        <v>1068</v>
+        <v>1061</v>
       </c>
       <c r="C523" t="s">
-        <v>1063</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.3">
@@ -14545,10 +14545,10 @@
         <v>523</v>
       </c>
       <c r="B524" t="s">
-        <v>1069</v>
+        <v>1062</v>
       </c>
       <c r="C524" t="s">
-        <v>1064</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.3">
@@ -14556,10 +14556,10 @@
         <v>524</v>
       </c>
       <c r="B525" t="s">
-        <v>1070</v>
+        <v>1063</v>
       </c>
       <c r="C525" t="s">
-        <v>1065</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.3">
@@ -14567,10 +14567,10 @@
         <v>525</v>
       </c>
       <c r="B526" t="s">
-        <v>1071</v>
+        <v>1064</v>
       </c>
       <c r="C526" t="s">
-        <v>1066</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.3">
@@ -14578,10 +14578,10 @@
         <v>526</v>
       </c>
       <c r="B527" t="s">
-        <v>1072</v>
+        <v>1065</v>
       </c>
       <c r="C527" t="s">
-        <v>1067</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.3">
@@ -14644,7 +14644,7 @@
         <v>532</v>
       </c>
       <c r="B533" t="s">
-        <v>1245</v>
+        <v>1238</v>
       </c>
       <c r="C533" t="s">
         <v>878</v>
@@ -14655,7 +14655,7 @@
         <v>533</v>
       </c>
       <c r="B534" t="s">
-        <v>1246</v>
+        <v>1239</v>
       </c>
       <c r="C534" t="s">
         <v>879</v>
@@ -14666,7 +14666,7 @@
         <v>534</v>
       </c>
       <c r="B535" t="s">
-        <v>1247</v>
+        <v>1240</v>
       </c>
       <c r="C535" t="s">
         <v>880</v>
@@ -14677,7 +14677,7 @@
         <v>535</v>
       </c>
       <c r="B536" t="s">
-        <v>1248</v>
+        <v>1241</v>
       </c>
       <c r="C536" t="s">
         <v>876</v>
@@ -14688,7 +14688,7 @@
         <v>536</v>
       </c>
       <c r="B537" t="s">
-        <v>1249</v>
+        <v>1242</v>
       </c>
       <c r="C537" t="s">
         <v>877</v>
@@ -14699,7 +14699,7 @@
         <v>537</v>
       </c>
       <c r="B538" t="s">
-        <v>1250</v>
+        <v>1243</v>
       </c>
       <c r="C538" t="s">
         <v>881</v>
@@ -14710,7 +14710,7 @@
         <v>538</v>
       </c>
       <c r="B539" t="s">
-        <v>1251</v>
+        <v>1244</v>
       </c>
       <c r="C539" t="s">
         <v>882</v>
@@ -14721,7 +14721,7 @@
         <v>539</v>
       </c>
       <c r="B540" t="s">
-        <v>1252</v>
+        <v>1245</v>
       </c>
       <c r="C540" t="s">
         <v>883</v>
@@ -14732,7 +14732,7 @@
         <v>540</v>
       </c>
       <c r="B541" t="s">
-        <v>1253</v>
+        <v>1246</v>
       </c>
       <c r="C541" t="s">
         <v>884</v>
@@ -14743,7 +14743,7 @@
         <v>541</v>
       </c>
       <c r="B542" t="s">
-        <v>1254</v>
+        <v>1247</v>
       </c>
       <c r="C542" t="s">
         <v>885</v>
@@ -14754,7 +14754,7 @@
         <v>542</v>
       </c>
       <c r="B543" t="s">
-        <v>1255</v>
+        <v>1248</v>
       </c>
       <c r="C543" t="s">
         <v>886</v>
@@ -14765,7 +14765,7 @@
         <v>543</v>
       </c>
       <c r="B544" t="s">
-        <v>1256</v>
+        <v>1249</v>
       </c>
       <c r="C544" t="s">
         <v>887</v>
@@ -14776,10 +14776,10 @@
         <v>544</v>
       </c>
       <c r="B545" t="s">
-        <v>1257</v>
+        <v>1250</v>
       </c>
       <c r="C545" t="s">
-        <v>1526</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.3">
@@ -14787,7 +14787,7 @@
         <v>545</v>
       </c>
       <c r="B546" t="s">
-        <v>1258</v>
+        <v>1251</v>
       </c>
       <c r="C546" t="s">
         <v>888</v>
@@ -14798,10 +14798,10 @@
         <v>546</v>
       </c>
       <c r="B547" t="s">
-        <v>1259</v>
+        <v>1252</v>
       </c>
       <c r="C547" t="s">
-        <v>1118</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.3">
@@ -14809,7 +14809,7 @@
         <v>547</v>
       </c>
       <c r="B548" t="s">
-        <v>1260</v>
+        <v>1253</v>
       </c>
       <c r="C548" t="s">
         <v>892</v>
@@ -14820,7 +14820,7 @@
         <v>548</v>
       </c>
       <c r="B549" t="s">
-        <v>1261</v>
+        <v>1254</v>
       </c>
       <c r="C549" t="s">
         <v>889</v>
@@ -14831,7 +14831,7 @@
         <v>549</v>
       </c>
       <c r="B550" t="s">
-        <v>1262</v>
+        <v>1255</v>
       </c>
       <c r="C550" t="s">
         <v>890</v>
@@ -14842,7 +14842,7 @@
         <v>550</v>
       </c>
       <c r="B551" t="s">
-        <v>1263</v>
+        <v>1256</v>
       </c>
       <c r="C551" t="s">
         <v>891</v>
@@ -14853,10 +14853,10 @@
         <v>551</v>
       </c>
       <c r="B552" t="s">
-        <v>1264</v>
+        <v>1257</v>
       </c>
       <c r="C552" t="s">
-        <v>1041</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.3">
@@ -14864,10 +14864,10 @@
         <v>552</v>
       </c>
       <c r="B553" t="s">
-        <v>1265</v>
+        <v>1258</v>
       </c>
       <c r="C553" t="s">
-        <v>1042</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.3">
@@ -14875,10 +14875,10 @@
         <v>553</v>
       </c>
       <c r="B554" t="s">
-        <v>1266</v>
+        <v>1259</v>
       </c>
       <c r="C554" t="s">
-        <v>1043</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.3">
@@ -14886,10 +14886,10 @@
         <v>554</v>
       </c>
       <c r="B555" t="s">
-        <v>1267</v>
+        <v>1260</v>
       </c>
       <c r="C555" t="s">
-        <v>1044</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.3">
@@ -14897,10 +14897,10 @@
         <v>555</v>
       </c>
       <c r="B556" t="s">
-        <v>1268</v>
+        <v>1261</v>
       </c>
       <c r="C556" t="s">
-        <v>1045</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.3">
@@ -14908,10 +14908,10 @@
         <v>556</v>
       </c>
       <c r="B557" t="s">
-        <v>1269</v>
+        <v>1262</v>
       </c>
       <c r="C557" t="s">
-        <v>1046</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.3">
@@ -14919,10 +14919,10 @@
         <v>557</v>
       </c>
       <c r="B558" t="s">
-        <v>1270</v>
+        <v>1263</v>
       </c>
       <c r="C558" t="s">
-        <v>1047</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.3">
@@ -14930,10 +14930,10 @@
         <v>558</v>
       </c>
       <c r="B559" t="s">
-        <v>1271</v>
+        <v>1264</v>
       </c>
       <c r="C559" t="s">
-        <v>1048</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.3">
@@ -14941,10 +14941,10 @@
         <v>559</v>
       </c>
       <c r="B560" t="s">
-        <v>1272</v>
+        <v>1265</v>
       </c>
       <c r="C560" t="s">
-        <v>1049</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.3">
@@ -14952,10 +14952,10 @@
         <v>560</v>
       </c>
       <c r="B561" t="s">
-        <v>1273</v>
+        <v>1266</v>
       </c>
       <c r="C561" t="s">
-        <v>1050</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.3">
@@ -14963,10 +14963,10 @@
         <v>561</v>
       </c>
       <c r="B562" t="s">
-        <v>1274</v>
+        <v>1267</v>
       </c>
       <c r="C562" t="s">
-        <v>1051</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.3">
@@ -14974,10 +14974,10 @@
         <v>562</v>
       </c>
       <c r="B563" t="s">
-        <v>1275</v>
+        <v>1268</v>
       </c>
       <c r="C563" t="s">
-        <v>1052</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.3">
@@ -14985,10 +14985,10 @@
         <v>563</v>
       </c>
       <c r="B564" t="s">
-        <v>1276</v>
+        <v>1269</v>
       </c>
       <c r="C564" t="s">
-        <v>1527</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.3">
@@ -14996,10 +14996,10 @@
         <v>564</v>
       </c>
       <c r="B565" t="s">
-        <v>1277</v>
+        <v>1270</v>
       </c>
       <c r="C565" t="s">
-        <v>1075</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.3">
@@ -15007,10 +15007,10 @@
         <v>565</v>
       </c>
       <c r="B566" t="s">
-        <v>1278</v>
+        <v>1271</v>
       </c>
       <c r="C566" t="s">
-        <v>1053</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.3">
@@ -15018,10 +15018,10 @@
         <v>566</v>
       </c>
       <c r="B567" t="s">
-        <v>1279</v>
+        <v>1272</v>
       </c>
       <c r="C567" t="s">
-        <v>1054</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.3">
@@ -15029,10 +15029,10 @@
         <v>567</v>
       </c>
       <c r="B568" t="s">
-        <v>1280</v>
+        <v>1273</v>
       </c>
       <c r="C568" t="s">
-        <v>1055</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.3">
@@ -15040,10 +15040,10 @@
         <v>568</v>
       </c>
       <c r="B569" t="s">
-        <v>1281</v>
+        <v>1274</v>
       </c>
       <c r="C569" t="s">
-        <v>1056</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.3">
@@ -15051,10 +15051,10 @@
         <v>569</v>
       </c>
       <c r="B570" t="s">
-        <v>1282</v>
+        <v>1275</v>
       </c>
       <c r="C570" t="s">
-        <v>1057</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.3">
@@ -15073,10 +15073,10 @@
         <v>571</v>
       </c>
       <c r="B572" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="C572" t="s">
-        <v>895</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.3">
@@ -15084,10 +15084,10 @@
         <v>572</v>
       </c>
       <c r="B573" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C573" t="s">
-        <v>896</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.3">
@@ -15095,10 +15095,10 @@
         <v>573</v>
       </c>
       <c r="B574" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="C574" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.3">
@@ -15106,10 +15106,10 @@
         <v>574</v>
       </c>
       <c r="B575" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="C575" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.3">
@@ -15117,10 +15117,10 @@
         <v>575</v>
       </c>
       <c r="B576" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="C576" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.3">
@@ -15128,10 +15128,10 @@
         <v>576</v>
       </c>
       <c r="B577" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="C577" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.3">
@@ -15139,10 +15139,10 @@
         <v>577</v>
       </c>
       <c r="B578" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="C578" t="s">
-        <v>906</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.3">
@@ -15150,10 +15150,10 @@
         <v>578</v>
       </c>
       <c r="B579" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="C579" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.3">
@@ -15161,10 +15161,10 @@
         <v>579</v>
       </c>
       <c r="B580" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="C580" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.3">
@@ -15172,10 +15172,10 @@
         <v>580</v>
       </c>
       <c r="B581" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="C581" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.3">
@@ -15183,10 +15183,10 @@
         <v>581</v>
       </c>
       <c r="B582" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="C582" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.3">
@@ -15194,10 +15194,10 @@
         <v>582</v>
       </c>
       <c r="B583" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="C583" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.3">
@@ -15205,10 +15205,10 @@
         <v>583</v>
       </c>
       <c r="B584" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="C584" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.3">
@@ -15216,10 +15216,10 @@
         <v>584</v>
       </c>
       <c r="B585" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="C585" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.3">
@@ -15227,10 +15227,10 @@
         <v>585</v>
       </c>
       <c r="B586" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="C586" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.3">
@@ -15238,10 +15238,10 @@
         <v>586</v>
       </c>
       <c r="B587" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="C587" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.3">
@@ -15249,10 +15249,10 @@
         <v>587</v>
       </c>
       <c r="B588" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="C588" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.3">
@@ -15260,10 +15260,10 @@
         <v>588</v>
       </c>
       <c r="B589" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
       <c r="C589" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.3">
@@ -15271,10 +15271,10 @@
         <v>589</v>
       </c>
       <c r="B590" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="C590" t="s">
-        <v>1038</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.3">
@@ -15282,10 +15282,10 @@
         <v>590</v>
       </c>
       <c r="B591" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="C591" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.3">
@@ -15293,10 +15293,10 @@
         <v>591</v>
       </c>
       <c r="B592" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="C592" t="s">
-        <v>929</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.3">
@@ -15304,10 +15304,10 @@
         <v>592</v>
       </c>
       <c r="B593" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="C593" t="s">
-        <v>931</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.3">
@@ -15315,10 +15315,10 @@
         <v>593</v>
       </c>
       <c r="B594" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="C594" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.3">
@@ -15326,10 +15326,10 @@
         <v>594</v>
       </c>
       <c r="B595" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
       <c r="C595" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.3">
@@ -15337,10 +15337,10 @@
         <v>595</v>
       </c>
       <c r="B596" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="C596" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.3">
@@ -15348,10 +15348,10 @@
         <v>596</v>
       </c>
       <c r="B597" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="C597" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.3">
@@ -15359,10 +15359,10 @@
         <v>597</v>
       </c>
       <c r="B598" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="C598" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.3">
@@ -15370,10 +15370,10 @@
         <v>598</v>
       </c>
       <c r="B599" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
       <c r="C599" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.3">
@@ -15381,10 +15381,10 @@
         <v>599</v>
       </c>
       <c r="B600" t="s">
-        <v>953</v>
+        <v>947</v>
       </c>
       <c r="C600" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.3">
@@ -15392,10 +15392,10 @@
         <v>600</v>
       </c>
       <c r="B601" t="s">
-        <v>954</v>
+        <v>948</v>
       </c>
       <c r="C601" t="s">
-        <v>951</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.3">
@@ -15403,10 +15403,10 @@
         <v>601</v>
       </c>
       <c r="B602" t="s">
-        <v>955</v>
+        <v>949</v>
       </c>
       <c r="C602" t="s">
-        <v>952</v>
+        <v>946</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.3">
@@ -15414,10 +15414,10 @@
         <v>602</v>
       </c>
       <c r="B603" t="s">
-        <v>956</v>
+        <v>950</v>
       </c>
       <c r="C603" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.3">
@@ -15425,10 +15425,10 @@
         <v>603</v>
       </c>
       <c r="B604" t="s">
-        <v>962</v>
+        <v>956</v>
       </c>
       <c r="C604" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.3">
@@ -15436,10 +15436,10 @@
         <v>604</v>
       </c>
       <c r="B605" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="C605" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.3">
@@ -15447,10 +15447,10 @@
         <v>605</v>
       </c>
       <c r="B606" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
       <c r="C606" t="s">
-        <v>960</v>
+        <v>954</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.3">
@@ -15458,10 +15458,10 @@
         <v>606</v>
       </c>
       <c r="B607" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="C607" t="s">
-        <v>961</v>
+        <v>955</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.3">
@@ -15469,10 +15469,10 @@
         <v>607</v>
       </c>
       <c r="B608" t="s">
-        <v>966</v>
+        <v>960</v>
       </c>
       <c r="C608" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.3">
@@ -15480,10 +15480,10 @@
         <v>608</v>
       </c>
       <c r="B609" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="C609" t="s">
-        <v>968</v>
+        <v>962</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.3">
@@ -15491,10 +15491,10 @@
         <v>609</v>
       </c>
       <c r="B610" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
       <c r="C610" t="s">
-        <v>969</v>
+        <v>963</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.3">
@@ -15502,10 +15502,10 @@
         <v>610</v>
       </c>
       <c r="B611" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="C611" t="s">
-        <v>970</v>
+        <v>964</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.3">
@@ -15513,10 +15513,10 @@
         <v>611</v>
       </c>
       <c r="B612" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="C612" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.3">
@@ -15524,10 +15524,10 @@
         <v>612</v>
       </c>
       <c r="B613" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="C613" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.3">
@@ -15535,10 +15535,10 @@
         <v>613</v>
       </c>
       <c r="B614" t="s">
-        <v>1073</v>
+        <v>1066</v>
       </c>
       <c r="C614" t="s">
-        <v>1074</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.3">
@@ -15546,10 +15546,10 @@
         <v>614</v>
       </c>
       <c r="B615" t="s">
-        <v>1283</v>
+        <v>1276</v>
       </c>
       <c r="C615" t="s">
-        <v>1037</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.3">
@@ -15557,10 +15557,10 @@
         <v>615</v>
       </c>
       <c r="B616" t="s">
-        <v>1284</v>
+        <v>1277</v>
       </c>
       <c r="C616" t="s">
-        <v>1031</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.3">
@@ -15568,10 +15568,10 @@
         <v>616</v>
       </c>
       <c r="B617" t="s">
-        <v>1285</v>
+        <v>1278</v>
       </c>
       <c r="C617" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.3">
@@ -15579,10 +15579,10 @@
         <v>617</v>
       </c>
       <c r="B618" t="s">
-        <v>1286</v>
+        <v>1279</v>
       </c>
       <c r="C618" t="s">
-        <v>1033</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.3">
@@ -15590,10 +15590,10 @@
         <v>618</v>
       </c>
       <c r="B619" t="s">
-        <v>1287</v>
+        <v>1280</v>
       </c>
       <c r="C619" t="s">
-        <v>1034</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.3">
@@ -15601,10 +15601,10 @@
         <v>619</v>
       </c>
       <c r="B620" t="s">
-        <v>1288</v>
+        <v>1281</v>
       </c>
       <c r="C620" t="s">
-        <v>1035</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.3">
@@ -15612,10 +15612,10 @@
         <v>620</v>
       </c>
       <c r="B621" t="s">
-        <v>1289</v>
+        <v>1282</v>
       </c>
       <c r="C621" t="s">
-        <v>1036</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.3">
@@ -15623,10 +15623,10 @@
         <v>621</v>
       </c>
       <c r="B622" t="s">
-        <v>1290</v>
+        <v>1283</v>
       </c>
       <c r="C622" t="s">
-        <v>1039</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.3">
@@ -15634,10 +15634,10 @@
         <v>622</v>
       </c>
       <c r="B623" t="s">
-        <v>1291</v>
+        <v>1284</v>
       </c>
       <c r="C623" t="s">
-        <v>1040</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.3">
@@ -15645,10 +15645,10 @@
         <v>623</v>
       </c>
       <c r="B624" t="s">
-        <v>1292</v>
+        <v>1285</v>
       </c>
       <c r="C624" t="s">
-        <v>1077</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.3">
@@ -15656,10 +15656,10 @@
         <v>624</v>
       </c>
       <c r="B625" t="s">
-        <v>1293</v>
+        <v>1286</v>
       </c>
       <c r="C625" t="s">
-        <v>1078</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.3">
@@ -15667,10 +15667,10 @@
         <v>625</v>
       </c>
       <c r="B626" t="s">
-        <v>1294</v>
+        <v>1287</v>
       </c>
       <c r="C626" t="s">
-        <v>1079</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.3">
@@ -15678,10 +15678,10 @@
         <v>626</v>
       </c>
       <c r="B627" t="s">
-        <v>1295</v>
+        <v>1288</v>
       </c>
       <c r="C627" t="s">
-        <v>1058</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.3">
@@ -15689,10 +15689,10 @@
         <v>627</v>
       </c>
       <c r="B628" t="s">
-        <v>1296</v>
+        <v>1289</v>
       </c>
       <c r="C628" t="s">
-        <v>1058</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.3">
@@ -15700,10 +15700,10 @@
         <v>628</v>
       </c>
       <c r="B629" t="s">
-        <v>1297</v>
+        <v>1290</v>
       </c>
       <c r="C629" t="s">
-        <v>1058</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.3">
@@ -15711,10 +15711,10 @@
         <v>629</v>
       </c>
       <c r="B630" t="s">
-        <v>1298</v>
+        <v>1291</v>
       </c>
       <c r="C630" t="s">
-        <v>1058</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.3">
@@ -15722,10 +15722,10 @@
         <v>630</v>
       </c>
       <c r="B631" t="s">
-        <v>1299</v>
+        <v>1292</v>
       </c>
       <c r="C631" t="s">
-        <v>1058</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.3">
@@ -15733,10 +15733,10 @@
         <v>631</v>
       </c>
       <c r="B632" t="s">
-        <v>1300</v>
+        <v>1293</v>
       </c>
       <c r="C632" t="s">
-        <v>1058</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.3">
@@ -15744,10 +15744,10 @@
         <v>632</v>
       </c>
       <c r="B633" t="s">
-        <v>1301</v>
+        <v>1294</v>
       </c>
       <c r="C633" t="s">
-        <v>1058</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.3">
@@ -15755,10 +15755,10 @@
         <v>633</v>
       </c>
       <c r="B634" t="s">
-        <v>1302</v>
+        <v>1295</v>
       </c>
       <c r="C634" t="s">
-        <v>1060</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.3">
@@ -15766,10 +15766,10 @@
         <v>634</v>
       </c>
       <c r="B635" t="s">
-        <v>1303</v>
+        <v>1296</v>
       </c>
       <c r="C635" t="s">
-        <v>1059</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.3">
@@ -15777,10 +15777,10 @@
         <v>635</v>
       </c>
       <c r="B636" t="s">
-        <v>1304</v>
+        <v>1297</v>
       </c>
       <c r="C636" t="s">
-        <v>1055</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.3">
@@ -15788,10 +15788,10 @@
         <v>636</v>
       </c>
       <c r="B637" t="s">
-        <v>1305</v>
+        <v>1298</v>
       </c>
       <c r="C637" t="s">
-        <v>1056</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.3">
@@ -15799,10 +15799,10 @@
         <v>637</v>
       </c>
       <c r="B638" t="s">
-        <v>1306</v>
+        <v>1299</v>
       </c>
       <c r="C638" t="s">
-        <v>1080</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.3">
@@ -15810,10 +15810,10 @@
         <v>638</v>
       </c>
       <c r="B639" t="s">
-        <v>1081</v>
+        <v>1074</v>
       </c>
       <c r="C639" t="s">
-        <v>1082</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.3">
@@ -15821,10 +15821,10 @@
         <v>639</v>
       </c>
       <c r="B640" t="s">
-        <v>1083</v>
+        <v>1076</v>
       </c>
       <c r="C640" t="s">
-        <v>1093</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.3">
@@ -15832,10 +15832,10 @@
         <v>640</v>
       </c>
       <c r="B641" t="s">
-        <v>1084</v>
+        <v>1077</v>
       </c>
       <c r="C641" t="s">
-        <v>1085</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.3">
@@ -15843,10 +15843,10 @@
         <v>641</v>
       </c>
       <c r="B642" s="28" t="s">
-        <v>1086</v>
+        <v>1079</v>
       </c>
       <c r="C642" t="s">
-        <v>1321</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.3">
@@ -15854,10 +15854,10 @@
         <v>642</v>
       </c>
       <c r="B643" s="28" t="s">
-        <v>1087</v>
+        <v>1080</v>
       </c>
       <c r="C643" t="s">
-        <v>1322</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.3">
@@ -15865,10 +15865,10 @@
         <v>643</v>
       </c>
       <c r="B644" s="28" t="s">
-        <v>1088</v>
+        <v>1081</v>
       </c>
       <c r="C644" t="s">
-        <v>1323</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.3">
@@ -15876,10 +15876,10 @@
         <v>644</v>
       </c>
       <c r="B645" s="28" t="s">
-        <v>1089</v>
+        <v>1082</v>
       </c>
       <c r="C645" t="s">
-        <v>1324</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.3">
@@ -15887,10 +15887,10 @@
         <v>645</v>
       </c>
       <c r="B646" s="28" t="s">
-        <v>1090</v>
+        <v>1083</v>
       </c>
       <c r="C646" t="s">
-        <v>1325</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.3">
@@ -15898,10 +15898,10 @@
         <v>646</v>
       </c>
       <c r="B647" s="28" t="s">
-        <v>1091</v>
+        <v>1084</v>
       </c>
       <c r="C647" t="s">
-        <v>1092</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.3">
@@ -15909,10 +15909,10 @@
         <v>647</v>
       </c>
       <c r="B648" t="s">
-        <v>1094</v>
+        <v>1087</v>
       </c>
       <c r="C648" t="s">
-        <v>1095</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.3">
@@ -15920,10 +15920,10 @@
         <v>648</v>
       </c>
       <c r="B649" t="s">
-        <v>1096</v>
+        <v>1089</v>
       </c>
       <c r="C649" t="s">
-        <v>1097</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.3">
@@ -15931,10 +15931,10 @@
         <v>649</v>
       </c>
       <c r="B650" s="28" t="s">
-        <v>1114</v>
+        <v>1107</v>
       </c>
       <c r="C650" t="s">
-        <v>1098</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.3">
@@ -15942,10 +15942,10 @@
         <v>650</v>
       </c>
       <c r="B651" s="28" t="s">
-        <v>1115</v>
+        <v>1108</v>
       </c>
       <c r="C651" t="s">
-        <v>1099</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.3">
@@ -15953,10 +15953,10 @@
         <v>651</v>
       </c>
       <c r="B652" s="28" t="s">
-        <v>1116</v>
+        <v>1109</v>
       </c>
       <c r="C652" t="s">
-        <v>1100</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.3">
@@ -15964,10 +15964,10 @@
         <v>652</v>
       </c>
       <c r="B653" s="28" t="s">
-        <v>1117</v>
+        <v>1110</v>
       </c>
       <c r="C653" t="s">
-        <v>1101</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.3">
@@ -15975,10 +15975,10 @@
         <v>653</v>
       </c>
       <c r="B654" s="28" t="s">
-        <v>1102</v>
+        <v>1095</v>
       </c>
       <c r="C654" t="s">
-        <v>1105</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.3">
@@ -15986,10 +15986,10 @@
         <v>654</v>
       </c>
       <c r="B655" t="s">
-        <v>1103</v>
+        <v>1096</v>
       </c>
       <c r="C655" t="s">
-        <v>1106</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.3">
@@ -15997,10 +15997,10 @@
         <v>655</v>
       </c>
       <c r="B656" t="s">
-        <v>1104</v>
+        <v>1097</v>
       </c>
       <c r="C656" t="s">
-        <v>1107</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.3">
@@ -16008,10 +16008,10 @@
         <v>656</v>
       </c>
       <c r="B657" t="s">
-        <v>1108</v>
+        <v>1101</v>
       </c>
       <c r="C657" t="s">
-        <v>1113</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.3">
@@ -16019,10 +16019,10 @@
         <v>657</v>
       </c>
       <c r="B658" t="s">
-        <v>1109</v>
+        <v>1102</v>
       </c>
       <c r="C658" t="s">
-        <v>1112</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.3">
@@ -16030,10 +16030,10 @@
         <v>658</v>
       </c>
       <c r="B659" t="s">
-        <v>1110</v>
+        <v>1103</v>
       </c>
       <c r="C659" t="s">
-        <v>1111</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.3">
@@ -16041,10 +16041,10 @@
         <v>659</v>
       </c>
       <c r="B660" t="s">
-        <v>1125</v>
+        <v>1118</v>
       </c>
       <c r="C660" t="s">
-        <v>1430</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.3">
@@ -16052,10 +16052,10 @@
         <v>660</v>
       </c>
       <c r="B661" t="s">
-        <v>1126</v>
+        <v>1119</v>
       </c>
       <c r="C661" t="s">
-        <v>1119</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.3">
@@ -16063,10 +16063,10 @@
         <v>661</v>
       </c>
       <c r="B662" t="s">
-        <v>1127</v>
+        <v>1120</v>
       </c>
       <c r="C662" t="s">
-        <v>1120</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.3">
@@ -16074,10 +16074,10 @@
         <v>662</v>
       </c>
       <c r="B663" t="s">
-        <v>1128</v>
+        <v>1121</v>
       </c>
       <c r="C663" t="s">
-        <v>1121</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.3">
@@ -16085,10 +16085,10 @@
         <v>663</v>
       </c>
       <c r="B664" t="s">
-        <v>1129</v>
+        <v>1122</v>
       </c>
       <c r="C664" t="s">
-        <v>1122</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.3">
@@ -16096,10 +16096,10 @@
         <v>664</v>
       </c>
       <c r="B665" t="s">
-        <v>1620</v>
+        <v>1613</v>
       </c>
       <c r="C665" t="s">
-        <v>1621</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.3">
@@ -16107,10 +16107,10 @@
         <v>665</v>
       </c>
       <c r="B666" t="s">
-        <v>1123</v>
+        <v>1116</v>
       </c>
       <c r="C666" t="s">
-        <v>1124</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.3">
@@ -16118,10 +16118,10 @@
         <v>666</v>
       </c>
       <c r="B667" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="C667" t="s">
-        <v>1134</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.3">
@@ -16129,10 +16129,10 @@
         <v>667</v>
       </c>
       <c r="B668" t="s">
-        <v>1135</v>
+        <v>1128</v>
       </c>
       <c r="C668" t="s">
-        <v>1136</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.3">
@@ -16140,10 +16140,10 @@
         <v>668</v>
       </c>
       <c r="B669" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="C669" t="s">
-        <v>1140</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.3">
@@ -16151,10 +16151,10 @@
         <v>669</v>
       </c>
       <c r="B670" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="C670" t="s">
-        <v>1141</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.3">
@@ -16162,10 +16162,10 @@
         <v>670</v>
       </c>
       <c r="B671" t="s">
-        <v>1139</v>
+        <v>1132</v>
       </c>
       <c r="C671" t="s">
-        <v>1142</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.3">
@@ -16173,10 +16173,10 @@
         <v>671</v>
       </c>
       <c r="B672" t="s">
-        <v>1143</v>
+        <v>1136</v>
       </c>
       <c r="C672" t="s">
-        <v>1146</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.3">
@@ -16184,10 +16184,10 @@
         <v>672</v>
       </c>
       <c r="B673" t="s">
-        <v>1144</v>
+        <v>1137</v>
       </c>
       <c r="C673" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="674" spans="1:3" x14ac:dyDescent="0.3">
@@ -16195,10 +16195,10 @@
         <v>673</v>
       </c>
       <c r="B674" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
       <c r="C674" t="s">
-        <v>1148</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.3">
@@ -16206,10 +16206,10 @@
         <v>674</v>
       </c>
       <c r="B675" t="s">
-        <v>1149</v>
+        <v>1142</v>
       </c>
       <c r="C675" t="s">
-        <v>1150</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.3">
@@ -16217,10 +16217,10 @@
         <v>675</v>
       </c>
       <c r="B676" t="s">
-        <v>1154</v>
+        <v>1147</v>
       </c>
       <c r="C676" t="s">
-        <v>1153</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="677" spans="1:3" x14ac:dyDescent="0.3">
@@ -16228,10 +16228,10 @@
         <v>676</v>
       </c>
       <c r="B677" t="s">
-        <v>1179</v>
+        <v>1172</v>
       </c>
       <c r="C677" t="s">
-        <v>1180</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.3">
@@ -16239,10 +16239,10 @@
         <v>677</v>
       </c>
       <c r="B678" t="s">
-        <v>1181</v>
+        <v>1174</v>
       </c>
       <c r="C678" t="s">
-        <v>1184</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.3">
@@ -16250,10 +16250,10 @@
         <v>678</v>
       </c>
       <c r="B679" t="s">
-        <v>1182</v>
+        <v>1175</v>
       </c>
       <c r="C679" t="s">
-        <v>1185</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.3">
@@ -16261,10 +16261,10 @@
         <v>679</v>
       </c>
       <c r="B680" t="s">
-        <v>1183</v>
+        <v>1176</v>
       </c>
       <c r="C680" t="s">
-        <v>1186</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.3">
@@ -16272,10 +16272,10 @@
         <v>680</v>
       </c>
       <c r="B681" t="s">
-        <v>1187</v>
+        <v>1180</v>
       </c>
       <c r="C681" t="s">
-        <v>1188</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.3">
@@ -16283,10 +16283,10 @@
         <v>681</v>
       </c>
       <c r="B682" t="s">
-        <v>1189</v>
+        <v>1182</v>
       </c>
       <c r="C682" t="s">
-        <v>1190</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.3">
@@ -16294,10 +16294,10 @@
         <v>682</v>
       </c>
       <c r="B683" t="s">
-        <v>1191</v>
+        <v>1184</v>
       </c>
       <c r="C683" t="s">
-        <v>1192</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.3">
@@ -16305,10 +16305,10 @@
         <v>683</v>
       </c>
       <c r="B684" t="s">
-        <v>1193</v>
+        <v>1186</v>
       </c>
       <c r="C684" t="s">
-        <v>1194</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.3">
@@ -16316,10 +16316,10 @@
         <v>684</v>
       </c>
       <c r="B685" t="s">
-        <v>1195</v>
+        <v>1188</v>
       </c>
       <c r="C685" t="s">
-        <v>1196</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.3">
@@ -16327,10 +16327,10 @@
         <v>685</v>
       </c>
       <c r="B686" t="s">
-        <v>1199</v>
+        <v>1192</v>
       </c>
       <c r="C686" t="s">
-        <v>1200</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.3">
@@ -16338,10 +16338,10 @@
         <v>686</v>
       </c>
       <c r="B687" t="s">
-        <v>1201</v>
+        <v>1194</v>
       </c>
       <c r="C687" t="s">
-        <v>1205</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="688" spans="1:3" x14ac:dyDescent="0.3">
@@ -16349,10 +16349,10 @@
         <v>687</v>
       </c>
       <c r="B688" t="s">
-        <v>1202</v>
+        <v>1195</v>
       </c>
       <c r="C688" t="s">
-        <v>1206</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="689" spans="1:3" x14ac:dyDescent="0.3">
@@ -16360,10 +16360,10 @@
         <v>688</v>
       </c>
       <c r="B689" t="s">
-        <v>1203</v>
+        <v>1196</v>
       </c>
       <c r="C689" t="s">
-        <v>1207</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="690" spans="1:3" x14ac:dyDescent="0.3">
@@ -16371,10 +16371,10 @@
         <v>689</v>
       </c>
       <c r="B690" t="s">
-        <v>1204</v>
+        <v>1197</v>
       </c>
       <c r="C690" t="s">
-        <v>1208</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="691" spans="1:3" x14ac:dyDescent="0.3">
@@ -16382,10 +16382,10 @@
         <v>690</v>
       </c>
       <c r="B691" t="s">
-        <v>1197</v>
+        <v>1190</v>
       </c>
       <c r="C691" t="s">
-        <v>1198</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="692" spans="1:3" x14ac:dyDescent="0.3">
@@ -16393,10 +16393,10 @@
         <v>691</v>
       </c>
       <c r="B692" t="s">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="C692" t="s">
-        <v>1211</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="693" spans="1:3" x14ac:dyDescent="0.3">
@@ -16404,10 +16404,10 @@
         <v>692</v>
       </c>
       <c r="B693" t="s">
-        <v>1210</v>
+        <v>1203</v>
       </c>
       <c r="C693" t="s">
-        <v>1212</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="694" spans="1:3" x14ac:dyDescent="0.3">
@@ -16415,10 +16415,10 @@
         <v>693</v>
       </c>
       <c r="B694" t="s">
-        <v>1213</v>
+        <v>1206</v>
       </c>
       <c r="C694" t="s">
-        <v>1222</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.3">
@@ -16426,10 +16426,10 @@
         <v>694</v>
       </c>
       <c r="B695" t="s">
-        <v>1214</v>
+        <v>1207</v>
       </c>
       <c r="C695" t="s">
-        <v>1223</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="696" spans="1:3" x14ac:dyDescent="0.3">
@@ -16437,10 +16437,10 @@
         <v>695</v>
       </c>
       <c r="B696" t="s">
-        <v>1215</v>
+        <v>1208</v>
       </c>
       <c r="C696" t="s">
-        <v>1224</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="697" spans="1:3" x14ac:dyDescent="0.3">
@@ -16448,10 +16448,10 @@
         <v>696</v>
       </c>
       <c r="B697" t="s">
-        <v>1216</v>
+        <v>1209</v>
       </c>
       <c r="C697" t="s">
-        <v>1225</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="698" spans="1:3" x14ac:dyDescent="0.3">
@@ -16459,10 +16459,10 @@
         <v>697</v>
       </c>
       <c r="B698" t="s">
-        <v>1217</v>
+        <v>1210</v>
       </c>
       <c r="C698" t="s">
-        <v>1226</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="699" spans="1:3" x14ac:dyDescent="0.3">
@@ -16470,10 +16470,10 @@
         <v>698</v>
       </c>
       <c r="B699" t="s">
-        <v>1218</v>
+        <v>1211</v>
       </c>
       <c r="C699" t="s">
-        <v>1227</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="700" spans="1:3" x14ac:dyDescent="0.3">
@@ -16481,10 +16481,10 @@
         <v>699</v>
       </c>
       <c r="B700" t="s">
-        <v>1219</v>
+        <v>1212</v>
       </c>
       <c r="C700" t="s">
-        <v>1228</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="701" spans="1:3" x14ac:dyDescent="0.3">
@@ -16492,10 +16492,10 @@
         <v>700</v>
       </c>
       <c r="B701" t="s">
-        <v>1220</v>
+        <v>1213</v>
       </c>
       <c r="C701" t="s">
-        <v>1229</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="702" spans="1:3" x14ac:dyDescent="0.3">
@@ -16503,10 +16503,10 @@
         <v>701</v>
       </c>
       <c r="B702" t="s">
-        <v>1221</v>
+        <v>1214</v>
       </c>
       <c r="C702" t="s">
-        <v>1230</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="703" spans="1:3" x14ac:dyDescent="0.3">
@@ -16514,10 +16514,10 @@
         <v>702</v>
       </c>
       <c r="B703" t="s">
-        <v>1307</v>
+        <v>1300</v>
       </c>
       <c r="C703" t="s">
-        <v>1313</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="704" spans="1:3" x14ac:dyDescent="0.3">
@@ -16525,10 +16525,10 @@
         <v>703</v>
       </c>
       <c r="B704" t="s">
-        <v>1308</v>
+        <v>1301</v>
       </c>
       <c r="C704" t="s">
-        <v>1314</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="705" spans="1:3" x14ac:dyDescent="0.3">
@@ -16536,10 +16536,10 @@
         <v>704</v>
       </c>
       <c r="B705" t="s">
-        <v>1309</v>
+        <v>1302</v>
       </c>
       <c r="C705" t="s">
-        <v>1315</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.3">
@@ -16547,10 +16547,10 @@
         <v>705</v>
       </c>
       <c r="B706" t="s">
-        <v>1310</v>
+        <v>1303</v>
       </c>
       <c r="C706" t="s">
-        <v>1316</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="707" spans="1:3" x14ac:dyDescent="0.3">
@@ -16558,10 +16558,10 @@
         <v>706</v>
       </c>
       <c r="B707" t="s">
-        <v>1311</v>
+        <v>1304</v>
       </c>
       <c r="C707" t="s">
-        <v>1317</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="708" spans="1:3" x14ac:dyDescent="0.3">
@@ -16569,10 +16569,10 @@
         <v>707</v>
       </c>
       <c r="B708" t="s">
-        <v>1312</v>
+        <v>1305</v>
       </c>
       <c r="C708" t="s">
-        <v>1318</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="709" spans="1:3" x14ac:dyDescent="0.3">
@@ -16580,10 +16580,10 @@
         <v>708</v>
       </c>
       <c r="B709" t="s">
-        <v>1319</v>
+        <v>1312</v>
       </c>
       <c r="C709" t="s">
-        <v>1320</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="710" spans="1:3" x14ac:dyDescent="0.3">
@@ -16591,10 +16591,10 @@
         <v>709</v>
       </c>
       <c r="B710" t="s">
-        <v>1329</v>
+        <v>1322</v>
       </c>
       <c r="C710" t="s">
-        <v>1326</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="711" spans="1:3" x14ac:dyDescent="0.3">
@@ -16602,10 +16602,10 @@
         <v>710</v>
       </c>
       <c r="B711" t="s">
-        <v>1330</v>
+        <v>1323</v>
       </c>
       <c r="C711" t="s">
-        <v>1327</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="712" spans="1:3" x14ac:dyDescent="0.3">
@@ -16613,10 +16613,10 @@
         <v>711</v>
       </c>
       <c r="B712" t="s">
-        <v>1331</v>
+        <v>1324</v>
       </c>
       <c r="C712" t="s">
-        <v>1328</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="713" spans="1:3" x14ac:dyDescent="0.3">
@@ -16624,10 +16624,10 @@
         <v>712</v>
       </c>
       <c r="B713" t="s">
-        <v>1332</v>
+        <v>1325</v>
       </c>
       <c r="C713" t="s">
-        <v>1333</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="714" spans="1:3" x14ac:dyDescent="0.3">
@@ -16635,10 +16635,10 @@
         <v>713</v>
       </c>
       <c r="B714" t="s">
-        <v>1339</v>
+        <v>1332</v>
       </c>
       <c r="C714" t="s">
-        <v>1334</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="715" spans="1:3" x14ac:dyDescent="0.3">
@@ -16646,10 +16646,10 @@
         <v>714</v>
       </c>
       <c r="B715" t="s">
-        <v>1340</v>
+        <v>1333</v>
       </c>
       <c r="C715" t="s">
-        <v>1335</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="716" spans="1:3" x14ac:dyDescent="0.3">
@@ -16657,10 +16657,10 @@
         <v>715</v>
       </c>
       <c r="B716" t="s">
-        <v>1341</v>
+        <v>1334</v>
       </c>
       <c r="C716" t="s">
-        <v>1336</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.3">
@@ -16668,10 +16668,10 @@
         <v>716</v>
       </c>
       <c r="B717" t="s">
-        <v>1342</v>
+        <v>1335</v>
       </c>
       <c r="C717" t="s">
-        <v>1337</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="718" spans="1:3" x14ac:dyDescent="0.3">
@@ -16679,10 +16679,10 @@
         <v>717</v>
       </c>
       <c r="B718" t="s">
-        <v>1343</v>
+        <v>1336</v>
       </c>
       <c r="C718" t="s">
-        <v>1338</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="719" spans="1:3" x14ac:dyDescent="0.3">
@@ -16690,10 +16690,10 @@
         <v>718</v>
       </c>
       <c r="B719" t="s">
-        <v>1346</v>
+        <v>1339</v>
       </c>
       <c r="C719" t="s">
-        <v>1347</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="720" spans="1:3" x14ac:dyDescent="0.3">
@@ -16701,10 +16701,10 @@
         <v>719</v>
       </c>
       <c r="B720" t="s">
-        <v>1352</v>
+        <v>1345</v>
       </c>
       <c r="C720" t="s">
-        <v>1353</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="721" spans="1:3" x14ac:dyDescent="0.3">
@@ -16712,10 +16712,10 @@
         <v>720</v>
       </c>
       <c r="B721" t="s">
-        <v>1354</v>
+        <v>1347</v>
       </c>
       <c r="C721" t="s">
-        <v>1355</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="722" spans="1:3" x14ac:dyDescent="0.3">
@@ -16723,10 +16723,10 @@
         <v>721</v>
       </c>
       <c r="B722" t="s">
-        <v>1359</v>
+        <v>1352</v>
       </c>
       <c r="C722" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="723" spans="1:3" x14ac:dyDescent="0.3">
@@ -16734,10 +16734,10 @@
         <v>722</v>
       </c>
       <c r="B723" t="s">
-        <v>1360</v>
+        <v>1353</v>
       </c>
       <c r="C723" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="724" spans="1:3" x14ac:dyDescent="0.3">
@@ -16745,10 +16745,10 @@
         <v>723</v>
       </c>
       <c r="B724" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="C724" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="725" spans="1:3" x14ac:dyDescent="0.3">
@@ -16756,10 +16756,10 @@
         <v>724</v>
       </c>
       <c r="B725" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="C725" t="s">
-        <v>1366</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="726" spans="1:3" x14ac:dyDescent="0.3">
@@ -16767,10 +16767,10 @@
         <v>725</v>
       </c>
       <c r="B726" t="s">
-        <v>1367</v>
+        <v>1360</v>
       </c>
       <c r="C726" t="s">
-        <v>1368</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="727" spans="1:3" x14ac:dyDescent="0.3">
@@ -16778,10 +16778,10 @@
         <v>726</v>
       </c>
       <c r="B727" t="s">
-        <v>1369</v>
+        <v>1362</v>
       </c>
       <c r="C727" t="s">
-        <v>1370</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.3">
@@ -16789,10 +16789,10 @@
         <v>727</v>
       </c>
       <c r="B728" t="s">
-        <v>1379</v>
+        <v>1372</v>
       </c>
       <c r="C728" t="s">
-        <v>1380</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="729" spans="1:3" x14ac:dyDescent="0.3">
@@ -16800,10 +16800,10 @@
         <v>728</v>
       </c>
       <c r="B729" t="s">
-        <v>1381</v>
+        <v>1374</v>
       </c>
       <c r="C729" t="s">
-        <v>1382</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="730" spans="1:3" x14ac:dyDescent="0.3">
@@ -16811,10 +16811,10 @@
         <v>729</v>
       </c>
       <c r="B730" t="s">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="C730" t="s">
-        <v>1384</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="731" spans="1:3" x14ac:dyDescent="0.3">
@@ -16822,10 +16822,10 @@
         <v>730</v>
       </c>
       <c r="B731" t="s">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="C731" t="s">
-        <v>1386</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="732" spans="1:3" x14ac:dyDescent="0.3">
@@ -16833,10 +16833,10 @@
         <v>731</v>
       </c>
       <c r="B732" t="s">
-        <v>1387</v>
+        <v>1380</v>
       </c>
       <c r="C732" t="s">
-        <v>1388</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="733" spans="1:3" x14ac:dyDescent="0.3">
@@ -16844,10 +16844,10 @@
         <v>732</v>
       </c>
       <c r="B733" t="s">
-        <v>1391</v>
+        <v>1384</v>
       </c>
       <c r="C733" t="s">
-        <v>1389</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="734" spans="1:3" x14ac:dyDescent="0.3">
@@ -16855,10 +16855,10 @@
         <v>733</v>
       </c>
       <c r="B734" t="s">
-        <v>1392</v>
+        <v>1385</v>
       </c>
       <c r="C734" t="s">
-        <v>1390</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="735" spans="1:3" x14ac:dyDescent="0.3">
@@ -16866,10 +16866,10 @@
         <v>734</v>
       </c>
       <c r="B735" t="s">
-        <v>1416</v>
+        <v>1409</v>
       </c>
       <c r="C735" t="s">
-        <v>1422</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="736" spans="1:3" x14ac:dyDescent="0.3">
@@ -16877,10 +16877,10 @@
         <v>735</v>
       </c>
       <c r="B736" t="s">
-        <v>1417</v>
+        <v>1410</v>
       </c>
       <c r="C736" t="s">
-        <v>1423</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="737" spans="1:3" x14ac:dyDescent="0.3">
@@ -16888,10 +16888,10 @@
         <v>736</v>
       </c>
       <c r="B737" t="s">
-        <v>1418</v>
+        <v>1411</v>
       </c>
       <c r="C737" t="s">
-        <v>1420</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="738" spans="1:3" x14ac:dyDescent="0.3">
@@ -16899,10 +16899,10 @@
         <v>737</v>
       </c>
       <c r="B738" t="s">
-        <v>1419</v>
+        <v>1412</v>
       </c>
       <c r="C738" t="s">
-        <v>1421</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.3">
@@ -16910,10 +16910,10 @@
         <v>738</v>
       </c>
       <c r="B739" t="s">
-        <v>1431</v>
+        <v>1424</v>
       </c>
       <c r="C739" t="s">
-        <v>1432</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="740" spans="1:3" x14ac:dyDescent="0.3">
@@ -16921,10 +16921,10 @@
         <v>739</v>
       </c>
       <c r="B740" t="s">
-        <v>1452</v>
+        <v>1445</v>
       </c>
       <c r="C740" t="s">
-        <v>1454</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="741" spans="1:3" x14ac:dyDescent="0.3">
@@ -16932,10 +16932,10 @@
         <v>740</v>
       </c>
       <c r="B741" t="s">
-        <v>1453</v>
+        <v>1446</v>
       </c>
       <c r="C741" t="s">
-        <v>1455</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="742" spans="1:3" x14ac:dyDescent="0.3">
@@ -16943,10 +16943,10 @@
         <v>741</v>
       </c>
       <c r="B742" t="s">
-        <v>1456</v>
+        <v>1449</v>
       </c>
       <c r="C742" t="s">
-        <v>1458</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="743" spans="1:3" x14ac:dyDescent="0.3">
@@ -16954,10 +16954,10 @@
         <v>742</v>
       </c>
       <c r="B743" t="s">
-        <v>1457</v>
+        <v>1450</v>
       </c>
       <c r="C743" t="s">
-        <v>1459</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="744" spans="1:3" x14ac:dyDescent="0.3">
@@ -16965,10 +16965,10 @@
         <v>743</v>
       </c>
       <c r="B744" t="s">
-        <v>1460</v>
+        <v>1453</v>
       </c>
       <c r="C744" t="s">
-        <v>1468</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="745" spans="1:3" x14ac:dyDescent="0.3">
@@ -16976,10 +16976,10 @@
         <v>744</v>
       </c>
       <c r="B745" t="s">
-        <v>1461</v>
+        <v>1454</v>
       </c>
       <c r="C745" t="s">
-        <v>1469</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="746" spans="1:3" x14ac:dyDescent="0.3">
@@ -16987,10 +16987,10 @@
         <v>745</v>
       </c>
       <c r="B746" t="s">
-        <v>1462</v>
+        <v>1455</v>
       </c>
       <c r="C746" t="s">
-        <v>1470</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="747" spans="1:3" x14ac:dyDescent="0.3">
@@ -16998,10 +16998,10 @@
         <v>746</v>
       </c>
       <c r="B747" t="s">
-        <v>1463</v>
+        <v>1456</v>
       </c>
       <c r="C747" t="s">
-        <v>1471</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="748" spans="1:3" x14ac:dyDescent="0.3">
@@ -17009,10 +17009,10 @@
         <v>747</v>
       </c>
       <c r="B748" t="s">
-        <v>1464</v>
+        <v>1457</v>
       </c>
       <c r="C748" t="s">
-        <v>1472</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="749" spans="1:3" x14ac:dyDescent="0.3">
@@ -17020,10 +17020,10 @@
         <v>748</v>
       </c>
       <c r="B749" t="s">
-        <v>1465</v>
+        <v>1458</v>
       </c>
       <c r="C749" t="s">
-        <v>1473</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.3">
@@ -17031,10 +17031,10 @@
         <v>749</v>
       </c>
       <c r="B750" t="s">
-        <v>1466</v>
+        <v>1459</v>
       </c>
       <c r="C750" t="s">
-        <v>1474</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="751" spans="1:3" x14ac:dyDescent="0.3">
@@ -17042,10 +17042,10 @@
         <v>750</v>
       </c>
       <c r="B751" t="s">
-        <v>1467</v>
+        <v>1460</v>
       </c>
       <c r="C751" t="s">
-        <v>1475</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="752" spans="1:3" x14ac:dyDescent="0.3">
@@ -17053,10 +17053,10 @@
         <v>751</v>
       </c>
       <c r="B752" t="s">
-        <v>1476</v>
+        <v>1469</v>
       </c>
       <c r="C752" t="s">
-        <v>1486</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="753" spans="1:3" x14ac:dyDescent="0.3">
@@ -17064,10 +17064,10 @@
         <v>752</v>
       </c>
       <c r="B753" t="s">
-        <v>1477</v>
+        <v>1470</v>
       </c>
       <c r="C753" t="s">
-        <v>1486</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="754" spans="1:3" x14ac:dyDescent="0.3">
@@ -17075,10 +17075,10 @@
         <v>753</v>
       </c>
       <c r="B754" t="s">
-        <v>1478</v>
+        <v>1471</v>
       </c>
       <c r="C754" t="s">
-        <v>1486</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="755" spans="1:3" x14ac:dyDescent="0.3">
@@ -17086,10 +17086,10 @@
         <v>754</v>
       </c>
       <c r="B755" t="s">
+        <v>1472</v>
+      </c>
+      <c r="C755" t="s">
         <v>1479</v>
-      </c>
-      <c r="C755" t="s">
-        <v>1486</v>
       </c>
     </row>
     <row r="756" spans="1:3" x14ac:dyDescent="0.3">
@@ -17097,10 +17097,10 @@
         <v>755</v>
       </c>
       <c r="B756" t="s">
-        <v>1480</v>
+        <v>1473</v>
       </c>
       <c r="C756" t="s">
-        <v>1486</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="757" spans="1:3" x14ac:dyDescent="0.3">
@@ -17108,10 +17108,10 @@
         <v>756</v>
       </c>
       <c r="B757" t="s">
-        <v>1481</v>
+        <v>1474</v>
       </c>
       <c r="C757" t="s">
-        <v>1487</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="758" spans="1:3" x14ac:dyDescent="0.3">
@@ -17119,10 +17119,10 @@
         <v>757</v>
       </c>
       <c r="B758" t="s">
-        <v>1482</v>
+        <v>1475</v>
       </c>
       <c r="C758" t="s">
-        <v>1487</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="759" spans="1:3" x14ac:dyDescent="0.3">
@@ -17130,10 +17130,10 @@
         <v>758</v>
       </c>
       <c r="B759" t="s">
-        <v>1483</v>
+        <v>1476</v>
       </c>
       <c r="C759" t="s">
-        <v>1487</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="760" spans="1:3" x14ac:dyDescent="0.3">
@@ -17141,10 +17141,10 @@
         <v>759</v>
       </c>
       <c r="B760" t="s">
-        <v>1484</v>
+        <v>1477</v>
       </c>
       <c r="C760" t="s">
-        <v>1487</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.3">
@@ -17152,10 +17152,10 @@
         <v>760</v>
       </c>
       <c r="B761" t="s">
-        <v>1485</v>
+        <v>1478</v>
       </c>
       <c r="C761" t="s">
-        <v>1487</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="762" spans="1:3" x14ac:dyDescent="0.3">
@@ -17163,10 +17163,10 @@
         <v>761</v>
       </c>
       <c r="B762" t="s">
-        <v>1488</v>
+        <v>1481</v>
       </c>
       <c r="C762" t="s">
-        <v>1490</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="763" spans="1:3" x14ac:dyDescent="0.3">
@@ -17174,10 +17174,10 @@
         <v>762</v>
       </c>
       <c r="B763" t="s">
-        <v>1489</v>
+        <v>1482</v>
       </c>
       <c r="C763" t="s">
-        <v>1491</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="764" spans="1:3" x14ac:dyDescent="0.3">
@@ -17185,10 +17185,10 @@
         <v>763</v>
       </c>
       <c r="B764" t="s">
-        <v>1492</v>
+        <v>1485</v>
       </c>
       <c r="C764" t="s">
-        <v>1493</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="765" spans="1:3" x14ac:dyDescent="0.3">
@@ -17196,10 +17196,10 @@
         <v>764</v>
       </c>
       <c r="B765" t="s">
-        <v>1495</v>
+        <v>1488</v>
       </c>
       <c r="C765" t="s">
-        <v>1494</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="766" spans="1:3" x14ac:dyDescent="0.3">
@@ -17207,10 +17207,10 @@
         <v>765</v>
       </c>
       <c r="B766" t="s">
-        <v>1497</v>
+        <v>1490</v>
       </c>
       <c r="C766" t="s">
-        <v>1498</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="767" spans="1:3" x14ac:dyDescent="0.3">
@@ -17218,10 +17218,10 @@
         <v>766</v>
       </c>
       <c r="B767" t="s">
-        <v>1496</v>
+        <v>1489</v>
       </c>
       <c r="C767" t="s">
-        <v>1499</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="768" spans="1:3" x14ac:dyDescent="0.3">
@@ -17229,10 +17229,10 @@
         <v>767</v>
       </c>
       <c r="B768" t="s">
-        <v>1500</v>
+        <v>1493</v>
       </c>
       <c r="C768" t="s">
-        <v>1506</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="769" spans="1:3" x14ac:dyDescent="0.3">
@@ -17240,10 +17240,10 @@
         <v>768</v>
       </c>
       <c r="B769" t="s">
-        <v>1501</v>
+        <v>1494</v>
       </c>
       <c r="C769" t="s">
-        <v>1507</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="770" spans="1:3" x14ac:dyDescent="0.3">
@@ -17251,10 +17251,10 @@
         <v>769</v>
       </c>
       <c r="B770" t="s">
-        <v>1502</v>
+        <v>1495</v>
       </c>
       <c r="C770" t="s">
-        <v>1508</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="771" spans="1:3" x14ac:dyDescent="0.3">
@@ -17262,10 +17262,10 @@
         <v>770</v>
       </c>
       <c r="B771" t="s">
-        <v>1503</v>
+        <v>1496</v>
       </c>
       <c r="C771" t="s">
-        <v>1509</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.3">
@@ -17273,10 +17273,10 @@
         <v>771</v>
       </c>
       <c r="B772" t="s">
-        <v>1504</v>
+        <v>1497</v>
       </c>
       <c r="C772" t="s">
-        <v>1510</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="773" spans="1:3" x14ac:dyDescent="0.3">
@@ -17284,10 +17284,10 @@
         <v>772</v>
       </c>
       <c r="B773" t="s">
-        <v>1505</v>
+        <v>1498</v>
       </c>
       <c r="C773" t="s">
-        <v>1511</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="774" spans="1:3" x14ac:dyDescent="0.3">
@@ -17295,10 +17295,10 @@
         <v>773</v>
       </c>
       <c r="B774" t="s">
-        <v>1556</v>
+        <v>1549</v>
       </c>
       <c r="C774" t="s">
-        <v>1557</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="775" spans="1:3" x14ac:dyDescent="0.3">
@@ -17306,10 +17306,10 @@
         <v>774</v>
       </c>
       <c r="B775" t="s">
-        <v>1550</v>
+        <v>1543</v>
       </c>
       <c r="C775" t="s">
-        <v>1558</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="776" spans="1:3" x14ac:dyDescent="0.3">
@@ -17317,10 +17317,10 @@
         <v>775</v>
       </c>
       <c r="B776" t="s">
-        <v>1551</v>
+        <v>1544</v>
       </c>
       <c r="C776" t="s">
-        <v>1559</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="777" spans="1:3" x14ac:dyDescent="0.3">
@@ -17328,10 +17328,10 @@
         <v>776</v>
       </c>
       <c r="B777" t="s">
-        <v>1552</v>
+        <v>1545</v>
       </c>
       <c r="C777" t="s">
-        <v>1563</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="778" spans="1:3" x14ac:dyDescent="0.3">
@@ -17339,10 +17339,10 @@
         <v>777</v>
       </c>
       <c r="B778" t="s">
+        <v>1546</v>
+      </c>
+      <c r="C778" t="s">
         <v>1553</v>
-      </c>
-      <c r="C778" t="s">
-        <v>1560</v>
       </c>
     </row>
     <row r="779" spans="1:3" x14ac:dyDescent="0.3">
@@ -17350,10 +17350,10 @@
         <v>778</v>
       </c>
       <c r="B779" t="s">
+        <v>1547</v>
+      </c>
+      <c r="C779" t="s">
         <v>1554</v>
-      </c>
-      <c r="C779" t="s">
-        <v>1561</v>
       </c>
     </row>
     <row r="780" spans="1:3" x14ac:dyDescent="0.3">
@@ -17361,10 +17361,10 @@
         <v>779</v>
       </c>
       <c r="B780" t="s">
+        <v>1548</v>
+      </c>
+      <c r="C780" t="s">
         <v>1555</v>
-      </c>
-      <c r="C780" t="s">
-        <v>1562</v>
       </c>
     </row>
     <row r="781" spans="1:3" x14ac:dyDescent="0.3">
@@ -17372,10 +17372,10 @@
         <v>780</v>
       </c>
       <c r="B781" t="s">
-        <v>1604</v>
+        <v>1597</v>
       </c>
       <c r="C781" t="s">
-        <v>1605</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="782" spans="1:3" x14ac:dyDescent="0.3">
@@ -17383,10 +17383,10 @@
         <v>781</v>
       </c>
       <c r="B782" t="s">
+        <v>1557</v>
+      </c>
+      <c r="C782" t="s">
         <v>1564</v>
-      </c>
-      <c r="C782" t="s">
-        <v>1571</v>
       </c>
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.3">
@@ -17394,10 +17394,10 @@
         <v>782</v>
       </c>
       <c r="B783" t="s">
-        <v>1565</v>
+        <v>1558</v>
       </c>
       <c r="C783" t="s">
-        <v>1573</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="784" spans="1:3" x14ac:dyDescent="0.3">
@@ -17405,10 +17405,10 @@
         <v>783</v>
       </c>
       <c r="B784" t="s">
-        <v>1566</v>
+        <v>1559</v>
       </c>
       <c r="C784" t="s">
-        <v>1616</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="785" spans="1:3" x14ac:dyDescent="0.3">
@@ -17416,10 +17416,10 @@
         <v>784</v>
       </c>
       <c r="B785" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="C785" t="s">
-        <v>1572</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="786" spans="1:3" x14ac:dyDescent="0.3">
@@ -17427,10 +17427,10 @@
         <v>785</v>
       </c>
       <c r="B786" t="s">
-        <v>1568</v>
+        <v>1561</v>
       </c>
       <c r="C786" t="s">
-        <v>1617</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="787" spans="1:3" x14ac:dyDescent="0.3">
@@ -17438,10 +17438,10 @@
         <v>786</v>
       </c>
       <c r="B787" t="s">
-        <v>1569</v>
+        <v>1562</v>
       </c>
       <c r="C787" t="s">
-        <v>1574</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="788" spans="1:3" x14ac:dyDescent="0.3">
@@ -17449,10 +17449,10 @@
         <v>787</v>
       </c>
       <c r="B788" t="s">
-        <v>1570</v>
+        <v>1563</v>
       </c>
       <c r="C788" t="s">
-        <v>1575</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="789" spans="1:3" x14ac:dyDescent="0.3">
@@ -17460,10 +17460,10 @@
         <v>788</v>
       </c>
       <c r="B789" t="s">
-        <v>1606</v>
+        <v>1599</v>
       </c>
       <c r="C789" t="s">
-        <v>1572</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="790" spans="1:3" x14ac:dyDescent="0.3">
@@ -17471,10 +17471,10 @@
         <v>789</v>
       </c>
       <c r="B790" t="s">
-        <v>1547</v>
+        <v>1540</v>
       </c>
       <c r="C790" t="s">
-        <v>1549</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="791" spans="1:3" x14ac:dyDescent="0.3">
@@ -17482,10 +17482,10 @@
         <v>790</v>
       </c>
       <c r="B791" t="s">
-        <v>1548</v>
+        <v>1541</v>
       </c>
       <c r="C791" t="s">
-        <v>1576</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="792" spans="1:3" x14ac:dyDescent="0.3">
@@ -17493,10 +17493,10 @@
         <v>791</v>
       </c>
       <c r="B792" t="s">
-        <v>1579</v>
+        <v>1572</v>
       </c>
       <c r="C792" t="s">
-        <v>1577</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="793" spans="1:3" x14ac:dyDescent="0.3">
@@ -17504,10 +17504,10 @@
         <v>792</v>
       </c>
       <c r="B793" t="s">
-        <v>1580</v>
+        <v>1573</v>
       </c>
       <c r="C793" t="s">
-        <v>1618</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.3">
@@ -17515,10 +17515,10 @@
         <v>793</v>
       </c>
       <c r="B794" t="s">
-        <v>1581</v>
+        <v>1574</v>
       </c>
       <c r="C794" t="s">
-        <v>1578</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="795" spans="1:3" x14ac:dyDescent="0.3">
@@ -17526,10 +17526,10 @@
         <v>794</v>
       </c>
       <c r="B795" t="s">
-        <v>1582</v>
+        <v>1575</v>
       </c>
       <c r="C795" t="s">
-        <v>1583</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="796" spans="1:3" x14ac:dyDescent="0.3">
@@ -17537,10 +17537,10 @@
         <v>795</v>
       </c>
       <c r="B796" t="s">
-        <v>1590</v>
+        <v>1583</v>
       </c>
       <c r="C796" t="s">
-        <v>1584</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="797" spans="1:3" x14ac:dyDescent="0.3">
@@ -17548,10 +17548,10 @@
         <v>796</v>
       </c>
       <c r="B797" t="s">
-        <v>1591</v>
+        <v>1584</v>
       </c>
       <c r="C797" t="s">
-        <v>1585</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="798" spans="1:3" x14ac:dyDescent="0.3">
@@ -17559,10 +17559,10 @@
         <v>797</v>
       </c>
       <c r="B798" t="s">
-        <v>1592</v>
+        <v>1585</v>
       </c>
       <c r="C798" t="s">
-        <v>1586</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="799" spans="1:3" x14ac:dyDescent="0.3">
@@ -17570,10 +17570,10 @@
         <v>798</v>
       </c>
       <c r="B799" t="s">
-        <v>1593</v>
+        <v>1586</v>
       </c>
       <c r="C799" t="s">
-        <v>1587</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="800" spans="1:3" x14ac:dyDescent="0.3">
@@ -17581,10 +17581,10 @@
         <v>799</v>
       </c>
       <c r="B800" t="s">
-        <v>1594</v>
+        <v>1587</v>
       </c>
       <c r="C800" t="s">
-        <v>1588</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="801" spans="1:3" x14ac:dyDescent="0.3">
@@ -17592,10 +17592,10 @@
         <v>800</v>
       </c>
       <c r="B801" t="s">
-        <v>1595</v>
+        <v>1588</v>
       </c>
       <c r="C801" t="s">
-        <v>1589</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="802" spans="1:3" x14ac:dyDescent="0.3">
@@ -17603,10 +17603,10 @@
         <v>801</v>
       </c>
       <c r="B802" t="s">
-        <v>1596</v>
+        <v>1589</v>
       </c>
       <c r="C802" t="s">
-        <v>1597</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="803" spans="1:3" x14ac:dyDescent="0.3">
@@ -17614,10 +17614,10 @@
         <v>802</v>
       </c>
       <c r="B803" t="s">
-        <v>1601</v>
+        <v>1594</v>
       </c>
       <c r="C803" t="s">
-        <v>1598</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="804" spans="1:3" x14ac:dyDescent="0.3">
@@ -17625,10 +17625,10 @@
         <v>803</v>
       </c>
       <c r="B804" t="s">
-        <v>1602</v>
+        <v>1595</v>
       </c>
       <c r="C804" t="s">
-        <v>1599</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.3">
@@ -17636,10 +17636,10 @@
         <v>804</v>
       </c>
       <c r="B805" t="s">
-        <v>1603</v>
+        <v>1596</v>
       </c>
       <c r="C805" t="s">
-        <v>1600</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="806" spans="1:3" x14ac:dyDescent="0.3">
@@ -17647,10 +17647,10 @@
         <v>805</v>
       </c>
       <c r="B806" t="s">
-        <v>1607</v>
+        <v>1600</v>
       </c>
       <c r="C806" t="s">
-        <v>1608</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="807" spans="1:3" x14ac:dyDescent="0.3">
@@ -17658,10 +17658,10 @@
         <v>806</v>
       </c>
       <c r="B807" t="s">
-        <v>1612</v>
+        <v>1605</v>
       </c>
       <c r="C807" t="s">
-        <v>1609</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="808" spans="1:3" x14ac:dyDescent="0.3">
@@ -17669,10 +17669,10 @@
         <v>807</v>
       </c>
       <c r="B808" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="C808" t="s">
-        <v>1619</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="809" spans="1:3" x14ac:dyDescent="0.3">
@@ -17680,10 +17680,10 @@
         <v>808</v>
       </c>
       <c r="B809" t="s">
-        <v>1614</v>
+        <v>1607</v>
       </c>
       <c r="C809" t="s">
-        <v>1610</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="810" spans="1:3" x14ac:dyDescent="0.3">
@@ -17691,10 +17691,10 @@
         <v>809</v>
       </c>
       <c r="B810" t="s">
-        <v>1615</v>
+        <v>1608</v>
       </c>
       <c r="C810" t="s">
-        <v>1611</v>
+        <v>1604</v>
       </c>
     </row>
   </sheetData>

--- a/30_table/01_테스트버전/Table_STR_String.xlsx
+++ b/30_table/01_테스트버전/Table_STR_String.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1661" uniqueCount="1622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="1736">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5585,6 +5585,351 @@
   </si>
   <si>
     <t>더 강해지고 싶다구?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_MAP_S4_001</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_002</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_003</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_004</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_005</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_006</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_007</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_008</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_009</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_010</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_011</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_012</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_013</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_014</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_015</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_016</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_017</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_018</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_019</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_020</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_021</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_022</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_023</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_024</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_025</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_026</t>
+  </si>
+  <si>
+    <t>욕심</t>
+  </si>
+  <si>
+    <t>죽은 자의 동굴  1층</t>
+  </si>
+  <si>
+    <t>좀비 조심</t>
+  </si>
+  <si>
+    <t>박쥐 사냥</t>
+  </si>
+  <si>
+    <t>좀비방</t>
+  </si>
+  <si>
+    <t>숨겨진 방으로</t>
+  </si>
+  <si>
+    <t>보물방</t>
+  </si>
+  <si>
+    <t>믿음</t>
+  </si>
+  <si>
+    <t>만족</t>
+  </si>
+  <si>
+    <t>지하 2층으로</t>
+  </si>
+  <si>
+    <t>죽은 자의 동굴 2층</t>
+  </si>
+  <si>
+    <t>구울 조심</t>
+  </si>
+  <si>
+    <t>함정 1</t>
+  </si>
+  <si>
+    <t>구울방</t>
+  </si>
+  <si>
+    <t>함정 2</t>
+  </si>
+  <si>
+    <t>라미를 찾아서</t>
+  </si>
+  <si>
+    <t>라미의 부탁</t>
+  </si>
+  <si>
+    <t>좀비의 영혼</t>
+  </si>
+  <si>
+    <t>라미에게 줄 선물</t>
+  </si>
+  <si>
+    <t>라미의 조언</t>
+  </si>
+  <si>
+    <t>서큐버스를 찾아서 1</t>
+  </si>
+  <si>
+    <t>서큐버스를 찾아서 2</t>
+  </si>
+  <si>
+    <t>서큐버스 처치</t>
+  </si>
+  <si>
+    <t>서고로 이동</t>
+  </si>
+  <si>
+    <t>동굴 1층</t>
+  </si>
+  <si>
+    <t>단서</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_001_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_002_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_003_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_004_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_005_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_006_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_007_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_008_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_009_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_010_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_011_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_012_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_013_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_014_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_015_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_016_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_017_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_018_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_019_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_020_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_021_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_022_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_023_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_024_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_025_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_026_DESC</t>
+  </si>
+  <si>
+    <t>보물에 현혹되지 말고 이동하세요.</t>
+  </si>
+  <si>
+    <t>덫을 피해 목표 지점까지 이동하세요.</t>
+  </si>
+  <si>
+    <t>좀비를 피해 목표 지점까지 이동하세요.</t>
+  </si>
+  <si>
+    <t>박쥐를 모두 처치 하세요.</t>
+  </si>
+  <si>
+    <t>좀비를 모두 처치 하세요.</t>
+  </si>
+  <si>
+    <t>문을 열고 숨겨진 방으로 이동하세요.</t>
+  </si>
+  <si>
+    <t>숨겨진 방에서 골드를 획득한다.</t>
+  </si>
+  <si>
+    <t>목표 지점으로 이동하세요.</t>
+  </si>
+  <si>
+    <t>제한 시간 안에 목표 지점으로 이동하세요.</t>
+  </si>
+  <si>
+    <t>지하 2층으로 이동하세요</t>
+  </si>
+  <si>
+    <t>화염을 피해 다음 지역으로 이동하세요</t>
+  </si>
+  <si>
+    <t>구울을 피해 다음 지역으로 이동하세요.</t>
+  </si>
+  <si>
+    <t>발 밑을 조심하며 다음 지역으로 이동하세요.</t>
+  </si>
+  <si>
+    <t>구울을 모두 처치하세요.</t>
+  </si>
+  <si>
+    <t>영혼 수집가 라미를 찾아 보세요.</t>
+  </si>
+  <si>
+    <t>라미와 대화해 보세요.</t>
+  </si>
+  <si>
+    <t>좀비를 잡아 좀비의 영혼을 얻으세요.</t>
+  </si>
+  <si>
+    <t>라미에게 좀비의 영혼 1개를 주세요.</t>
+  </si>
+  <si>
+    <t>라미와 대화해 보세요</t>
+  </si>
+  <si>
+    <t>서큐버스를 찾으러 이동하세요.</t>
+  </si>
+  <si>
+    <t>서큐버스 방으로 이동하세요.</t>
+  </si>
+  <si>
+    <t>서큐버스를 처치하세요.</t>
+  </si>
+  <si>
+    <t>서고로 이동하세요.</t>
+  </si>
+  <si>
+    <t>책을 클릭해 샹그리라에 대한 정보를 얻어 보세요.</t>
+  </si>
+  <si>
+    <t>화살표로 이동하세요.</t>
+  </si>
+  <si>
+    <t>STR_MOB_N_0013</t>
+  </si>
+  <si>
+    <t>STR_MOB_N_0014</t>
+  </si>
+  <si>
+    <t>STR_BOX_N_0002</t>
+  </si>
+  <si>
+    <t>STR_BOX_N_0003</t>
+  </si>
+  <si>
+    <t>STR_TRAP_N_0002</t>
+  </si>
+  <si>
+    <t>STR_TRAP_N_0001</t>
+  </si>
+  <si>
+    <t>박쥐</t>
+  </si>
+  <si>
+    <t>구울</t>
+  </si>
+  <si>
+    <t>보물상자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>함정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>송곳</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8772,7 +9117,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E810"/>
+  <dimension ref="A1:E868"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="33" bestFit="1" customWidth="1"/>
@@ -17697,6 +18042,644 @@
         <v>1604</v>
       </c>
     </row>
+    <row r="811" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A811">
+        <v>810</v>
+      </c>
+      <c r="B811" t="s">
+        <v>1622</v>
+      </c>
+      <c r="C811" t="s">
+        <v>1648</v>
+      </c>
+    </row>
+    <row r="812" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A812">
+        <v>811</v>
+      </c>
+      <c r="B812" t="s">
+        <v>1623</v>
+      </c>
+      <c r="C812" t="s">
+        <v>1649</v>
+      </c>
+    </row>
+    <row r="813" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A813">
+        <v>812</v>
+      </c>
+      <c r="B813" t="s">
+        <v>1624</v>
+      </c>
+      <c r="C813" t="s">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="814" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A814">
+        <v>813</v>
+      </c>
+      <c r="B814" t="s">
+        <v>1625</v>
+      </c>
+      <c r="C814" t="s">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="815" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A815">
+        <v>814</v>
+      </c>
+      <c r="B815" t="s">
+        <v>1626</v>
+      </c>
+      <c r="C815" t="s">
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="816" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A816">
+        <v>815</v>
+      </c>
+      <c r="B816" t="s">
+        <v>1627</v>
+      </c>
+      <c r="C816" t="s">
+        <v>1653</v>
+      </c>
+    </row>
+    <row r="817" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A817">
+        <v>816</v>
+      </c>
+      <c r="B817" t="s">
+        <v>1628</v>
+      </c>
+      <c r="C817" t="s">
+        <v>1654</v>
+      </c>
+    </row>
+    <row r="818" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A818">
+        <v>817</v>
+      </c>
+      <c r="B818" t="s">
+        <v>1629</v>
+      </c>
+      <c r="C818" t="s">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="819" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A819">
+        <v>818</v>
+      </c>
+      <c r="B819" t="s">
+        <v>1630</v>
+      </c>
+      <c r="C819" t="s">
+        <v>1655</v>
+      </c>
+    </row>
+    <row r="820" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A820">
+        <v>819</v>
+      </c>
+      <c r="B820" t="s">
+        <v>1631</v>
+      </c>
+      <c r="C820" t="s">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="821" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A821">
+        <v>820</v>
+      </c>
+      <c r="B821" t="s">
+        <v>1632</v>
+      </c>
+      <c r="C821" t="s">
+        <v>1657</v>
+      </c>
+    </row>
+    <row r="822" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A822">
+        <v>821</v>
+      </c>
+      <c r="B822" t="s">
+        <v>1633</v>
+      </c>
+      <c r="C822" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="823" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A823">
+        <v>822</v>
+      </c>
+      <c r="B823" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C823" t="s">
+        <v>1659</v>
+      </c>
+    </row>
+    <row r="824" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A824">
+        <v>823</v>
+      </c>
+      <c r="B824" t="s">
+        <v>1635</v>
+      </c>
+      <c r="C824" t="s">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="825" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A825">
+        <v>824</v>
+      </c>
+      <c r="B825" t="s">
+        <v>1636</v>
+      </c>
+      <c r="C825" t="s">
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="826" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A826">
+        <v>825</v>
+      </c>
+      <c r="B826" t="s">
+        <v>1637</v>
+      </c>
+      <c r="C826" t="s">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="827" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A827">
+        <v>826</v>
+      </c>
+      <c r="B827" t="s">
+        <v>1638</v>
+      </c>
+      <c r="C827" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="828" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A828">
+        <v>827</v>
+      </c>
+      <c r="B828" t="s">
+        <v>1639</v>
+      </c>
+      <c r="C828" t="s">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="829" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A829">
+        <v>828</v>
+      </c>
+      <c r="B829" t="s">
+        <v>1640</v>
+      </c>
+      <c r="C829" t="s">
+        <v>1665</v>
+      </c>
+    </row>
+    <row r="830" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A830">
+        <v>829</v>
+      </c>
+      <c r="B830" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C830" t="s">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="831" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A831">
+        <v>830</v>
+      </c>
+      <c r="B831" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C831" t="s">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="832" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A832">
+        <v>831</v>
+      </c>
+      <c r="B832" t="s">
+        <v>1643</v>
+      </c>
+      <c r="C832" t="s">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="833" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A833">
+        <v>832</v>
+      </c>
+      <c r="B833" t="s">
+        <v>1644</v>
+      </c>
+      <c r="C833" t="s">
+        <v>1669</v>
+      </c>
+    </row>
+    <row r="834" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A834">
+        <v>833</v>
+      </c>
+      <c r="B834" t="s">
+        <v>1645</v>
+      </c>
+      <c r="C834" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="835" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A835">
+        <v>834</v>
+      </c>
+      <c r="B835" t="s">
+        <v>1646</v>
+      </c>
+      <c r="C835" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="836" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A836">
+        <v>835</v>
+      </c>
+      <c r="B836" t="s">
+        <v>1647</v>
+      </c>
+      <c r="C836" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="837" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A837">
+        <v>836</v>
+      </c>
+      <c r="B837" t="s">
+        <v>1674</v>
+      </c>
+      <c r="C837" t="s">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="838" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A838">
+        <v>837</v>
+      </c>
+      <c r="B838" t="s">
+        <v>1675</v>
+      </c>
+      <c r="C838" t="s">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="839" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A839">
+        <v>838</v>
+      </c>
+      <c r="B839" t="s">
+        <v>1676</v>
+      </c>
+      <c r="C839" t="s">
+        <v>1702</v>
+      </c>
+    </row>
+    <row r="840" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A840">
+        <v>839</v>
+      </c>
+      <c r="B840" t="s">
+        <v>1677</v>
+      </c>
+      <c r="C840" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="841" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A841">
+        <v>840</v>
+      </c>
+      <c r="B841" t="s">
+        <v>1678</v>
+      </c>
+      <c r="C841" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="842" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A842">
+        <v>841</v>
+      </c>
+      <c r="B842" t="s">
+        <v>1679</v>
+      </c>
+      <c r="C842" t="s">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="843" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A843">
+        <v>842</v>
+      </c>
+      <c r="B843" t="s">
+        <v>1680</v>
+      </c>
+      <c r="C843" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="844" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A844">
+        <v>843</v>
+      </c>
+      <c r="B844" t="s">
+        <v>1681</v>
+      </c>
+      <c r="C844" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="845" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A845">
+        <v>844</v>
+      </c>
+      <c r="B845" t="s">
+        <v>1682</v>
+      </c>
+      <c r="C845" t="s">
+        <v>1707</v>
+      </c>
+    </row>
+    <row r="846" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A846">
+        <v>845</v>
+      </c>
+      <c r="B846" t="s">
+        <v>1683</v>
+      </c>
+      <c r="C846" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="847" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A847">
+        <v>846</v>
+      </c>
+      <c r="B847" t="s">
+        <v>1684</v>
+      </c>
+      <c r="C847" t="s">
+        <v>1709</v>
+      </c>
+    </row>
+    <row r="848" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A848">
+        <v>847</v>
+      </c>
+      <c r="B848" t="s">
+        <v>1685</v>
+      </c>
+      <c r="C848" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="849" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A849">
+        <v>848</v>
+      </c>
+      <c r="B849" t="s">
+        <v>1686</v>
+      </c>
+      <c r="C849" t="s">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="850" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A850">
+        <v>849</v>
+      </c>
+      <c r="B850" t="s">
+        <v>1687</v>
+      </c>
+      <c r="C850" t="s">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="851" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A851">
+        <v>850</v>
+      </c>
+      <c r="B851" t="s">
+        <v>1688</v>
+      </c>
+      <c r="C851" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="852" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A852">
+        <v>851</v>
+      </c>
+      <c r="B852" t="s">
+        <v>1689</v>
+      </c>
+      <c r="C852" t="s">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="853" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A853">
+        <v>852</v>
+      </c>
+      <c r="B853" t="s">
+        <v>1690</v>
+      </c>
+      <c r="C853" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="854" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A854">
+        <v>853</v>
+      </c>
+      <c r="B854" t="s">
+        <v>1691</v>
+      </c>
+      <c r="C854" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="855" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A855">
+        <v>854</v>
+      </c>
+      <c r="B855" t="s">
+        <v>1692</v>
+      </c>
+      <c r="C855" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="856" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A856">
+        <v>855</v>
+      </c>
+      <c r="B856" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C856" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="857" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A857">
+        <v>856</v>
+      </c>
+      <c r="B857" t="s">
+        <v>1694</v>
+      </c>
+      <c r="C857" t="s">
+        <v>1718</v>
+      </c>
+    </row>
+    <row r="858" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A858">
+        <v>857</v>
+      </c>
+      <c r="B858" t="s">
+        <v>1695</v>
+      </c>
+      <c r="C858" t="s">
+        <v>1719</v>
+      </c>
+    </row>
+    <row r="859" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A859">
+        <v>858</v>
+      </c>
+      <c r="B859" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C859" t="s">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="860" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A860">
+        <v>859</v>
+      </c>
+      <c r="B860" t="s">
+        <v>1697</v>
+      </c>
+      <c r="C860" t="s">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="861" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A861">
+        <v>860</v>
+      </c>
+      <c r="B861" t="s">
+        <v>1698</v>
+      </c>
+      <c r="C861" t="s">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="862" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A862">
+        <v>861</v>
+      </c>
+      <c r="B862" t="s">
+        <v>1699</v>
+      </c>
+      <c r="C862" t="s">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="863" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A863">
+        <v>862</v>
+      </c>
+      <c r="B863" t="s">
+        <v>1725</v>
+      </c>
+      <c r="C863" t="s">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="864" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A864">
+        <v>863</v>
+      </c>
+      <c r="B864" t="s">
+        <v>1726</v>
+      </c>
+      <c r="C864" t="s">
+        <v>1732</v>
+      </c>
+    </row>
+    <row r="865" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A865">
+        <v>864</v>
+      </c>
+      <c r="B865" t="s">
+        <v>1727</v>
+      </c>
+      <c r="C865" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="866" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A866">
+        <v>865</v>
+      </c>
+      <c r="B866" t="s">
+        <v>1728</v>
+      </c>
+      <c r="C866" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="867" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A867">
+        <v>866</v>
+      </c>
+      <c r="B867" t="s">
+        <v>1730</v>
+      </c>
+      <c r="C867" t="s">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="868" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A868">
+        <v>867</v>
+      </c>
+      <c r="B868" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C868" t="s">
+        <v>1735</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/30_table/01_테스트버전/Table_STR_String.xlsx
+++ b/30_table/01_테스트버전/Table_STR_String.xlsx
@@ -5681,12 +5681,6 @@
     <t>좀비방</t>
   </si>
   <si>
-    <t>숨겨진 방으로</t>
-  </si>
-  <si>
-    <t>보물방</t>
-  </si>
-  <si>
     <t>믿음</t>
   </si>
   <si>
@@ -5837,12 +5831,6 @@
     <t>좀비를 모두 처치 하세요.</t>
   </si>
   <si>
-    <t>문을 열고 숨겨진 방으로 이동하세요.</t>
-  </si>
-  <si>
-    <t>숨겨진 방에서 골드를 획득한다.</t>
-  </si>
-  <si>
     <t>목표 지점으로 이동하세요.</t>
   </si>
   <si>
@@ -5930,6 +5918,22 @@
   </si>
   <si>
     <t>송곳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비밀의 동굴로 이동하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>문을 열고 보물창고로 이동하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보물 창고로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보물 창고</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -16125,7 +16129,7 @@
         <v>1297</v>
       </c>
       <c r="C636" t="s">
-        <v>1048</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.3">
@@ -18105,7 +18109,7 @@
         <v>1627</v>
       </c>
       <c r="C816" t="s">
-        <v>1653</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="817" spans="1:3" x14ac:dyDescent="0.3">
@@ -18116,7 +18120,7 @@
         <v>1628</v>
       </c>
       <c r="C817" t="s">
-        <v>1654</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="818" spans="1:3" x14ac:dyDescent="0.3">
@@ -18127,7 +18131,7 @@
         <v>1629</v>
       </c>
       <c r="C818" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="819" spans="1:3" x14ac:dyDescent="0.3">
@@ -18138,7 +18142,7 @@
         <v>1630</v>
       </c>
       <c r="C819" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="820" spans="1:3" x14ac:dyDescent="0.3">
@@ -18149,7 +18153,7 @@
         <v>1631</v>
       </c>
       <c r="C820" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="821" spans="1:3" x14ac:dyDescent="0.3">
@@ -18160,7 +18164,7 @@
         <v>1632</v>
       </c>
       <c r="C821" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="822" spans="1:3" x14ac:dyDescent="0.3">
@@ -18171,7 +18175,7 @@
         <v>1633</v>
       </c>
       <c r="C822" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="823" spans="1:3" x14ac:dyDescent="0.3">
@@ -18182,7 +18186,7 @@
         <v>1634</v>
       </c>
       <c r="C823" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="824" spans="1:3" x14ac:dyDescent="0.3">
@@ -18193,7 +18197,7 @@
         <v>1635</v>
       </c>
       <c r="C824" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="825" spans="1:3" x14ac:dyDescent="0.3">
@@ -18204,7 +18208,7 @@
         <v>1636</v>
       </c>
       <c r="C825" t="s">
-        <v>1661</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="826" spans="1:3" x14ac:dyDescent="0.3">
@@ -18215,7 +18219,7 @@
         <v>1637</v>
       </c>
       <c r="C826" t="s">
-        <v>1662</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.3">
@@ -18226,7 +18230,7 @@
         <v>1638</v>
       </c>
       <c r="C827" t="s">
-        <v>1663</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="828" spans="1:3" x14ac:dyDescent="0.3">
@@ -18237,7 +18241,7 @@
         <v>1639</v>
       </c>
       <c r="C828" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="829" spans="1:3" x14ac:dyDescent="0.3">
@@ -18248,7 +18252,7 @@
         <v>1640</v>
       </c>
       <c r="C829" t="s">
-        <v>1665</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="830" spans="1:3" x14ac:dyDescent="0.3">
@@ -18259,7 +18263,7 @@
         <v>1641</v>
       </c>
       <c r="C830" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="831" spans="1:3" x14ac:dyDescent="0.3">
@@ -18270,7 +18274,7 @@
         <v>1642</v>
       </c>
       <c r="C831" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="832" spans="1:3" x14ac:dyDescent="0.3">
@@ -18281,7 +18285,7 @@
         <v>1643</v>
       </c>
       <c r="C832" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="833" spans="1:3" x14ac:dyDescent="0.3">
@@ -18292,7 +18296,7 @@
         <v>1644</v>
       </c>
       <c r="C833" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="834" spans="1:3" x14ac:dyDescent="0.3">
@@ -18303,7 +18307,7 @@
         <v>1645</v>
       </c>
       <c r="C834" t="s">
-        <v>1670</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="835" spans="1:3" x14ac:dyDescent="0.3">
@@ -18314,7 +18318,7 @@
         <v>1646</v>
       </c>
       <c r="C835" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="836" spans="1:3" x14ac:dyDescent="0.3">
@@ -18325,7 +18329,7 @@
         <v>1647</v>
       </c>
       <c r="C836" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="837" spans="1:3" x14ac:dyDescent="0.3">
@@ -18333,10 +18337,10 @@
         <v>836</v>
       </c>
       <c r="B837" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
       <c r="C837" t="s">
-        <v>1700</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.3">
@@ -18344,10 +18348,10 @@
         <v>837</v>
       </c>
       <c r="B838" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="C838" t="s">
-        <v>1701</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="839" spans="1:3" x14ac:dyDescent="0.3">
@@ -18355,10 +18359,10 @@
         <v>838</v>
       </c>
       <c r="B839" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
       <c r="C839" t="s">
-        <v>1702</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="840" spans="1:3" x14ac:dyDescent="0.3">
@@ -18366,10 +18370,10 @@
         <v>839</v>
       </c>
       <c r="B840" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="C840" t="s">
-        <v>1703</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="841" spans="1:3" x14ac:dyDescent="0.3">
@@ -18377,10 +18381,10 @@
         <v>840</v>
       </c>
       <c r="B841" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="C841" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="842" spans="1:3" x14ac:dyDescent="0.3">
@@ -18388,10 +18392,10 @@
         <v>841</v>
       </c>
       <c r="B842" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="C842" t="s">
-        <v>1705</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="843" spans="1:3" x14ac:dyDescent="0.3">
@@ -18399,10 +18403,10 @@
         <v>842</v>
       </c>
       <c r="B843" t="s">
-        <v>1680</v>
+        <v>1678</v>
       </c>
       <c r="C843" t="s">
-        <v>1706</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="844" spans="1:3" x14ac:dyDescent="0.3">
@@ -18410,10 +18414,10 @@
         <v>843</v>
       </c>
       <c r="B844" t="s">
-        <v>1681</v>
+        <v>1679</v>
       </c>
       <c r="C844" t="s">
-        <v>1724</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="845" spans="1:3" x14ac:dyDescent="0.3">
@@ -18421,10 +18425,10 @@
         <v>844</v>
       </c>
       <c r="B845" t="s">
-        <v>1682</v>
+        <v>1680</v>
       </c>
       <c r="C845" t="s">
-        <v>1707</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="846" spans="1:3" x14ac:dyDescent="0.3">
@@ -18432,10 +18436,10 @@
         <v>845</v>
       </c>
       <c r="B846" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
       <c r="C846" t="s">
-        <v>1708</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="847" spans="1:3" x14ac:dyDescent="0.3">
@@ -18443,10 +18447,10 @@
         <v>846</v>
       </c>
       <c r="B847" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
       <c r="C847" t="s">
-        <v>1709</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="848" spans="1:3" x14ac:dyDescent="0.3">
@@ -18454,10 +18458,10 @@
         <v>847</v>
       </c>
       <c r="B848" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="C848" t="s">
-        <v>1710</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.3">
@@ -18465,10 +18469,10 @@
         <v>848</v>
       </c>
       <c r="B849" t="s">
-        <v>1686</v>
+        <v>1684</v>
       </c>
       <c r="C849" t="s">
-        <v>1711</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="850" spans="1:3" x14ac:dyDescent="0.3">
@@ -18476,10 +18480,10 @@
         <v>849</v>
       </c>
       <c r="B850" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="C850" t="s">
-        <v>1712</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="851" spans="1:3" x14ac:dyDescent="0.3">
@@ -18487,10 +18491,10 @@
         <v>850</v>
       </c>
       <c r="B851" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
       <c r="C851" t="s">
-        <v>1713</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="852" spans="1:3" x14ac:dyDescent="0.3">
@@ -18498,10 +18502,10 @@
         <v>851</v>
       </c>
       <c r="B852" t="s">
-        <v>1689</v>
+        <v>1687</v>
       </c>
       <c r="C852" t="s">
-        <v>1712</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="853" spans="1:3" x14ac:dyDescent="0.3">
@@ -18509,10 +18513,10 @@
         <v>852</v>
       </c>
       <c r="B853" t="s">
-        <v>1690</v>
+        <v>1688</v>
       </c>
       <c r="C853" t="s">
-        <v>1714</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="854" spans="1:3" x14ac:dyDescent="0.3">
@@ -18520,10 +18524,10 @@
         <v>853</v>
       </c>
       <c r="B854" t="s">
-        <v>1691</v>
+        <v>1689</v>
       </c>
       <c r="C854" t="s">
-        <v>1715</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="855" spans="1:3" x14ac:dyDescent="0.3">
@@ -18531,10 +18535,10 @@
         <v>854</v>
       </c>
       <c r="B855" t="s">
-        <v>1692</v>
+        <v>1690</v>
       </c>
       <c r="C855" t="s">
-        <v>1716</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="856" spans="1:3" x14ac:dyDescent="0.3">
@@ -18542,10 +18546,10 @@
         <v>855</v>
       </c>
       <c r="B856" t="s">
-        <v>1693</v>
+        <v>1691</v>
       </c>
       <c r="C856" t="s">
-        <v>1717</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="857" spans="1:3" x14ac:dyDescent="0.3">
@@ -18553,10 +18557,10 @@
         <v>856</v>
       </c>
       <c r="B857" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
       <c r="C857" t="s">
-        <v>1718</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="858" spans="1:3" x14ac:dyDescent="0.3">
@@ -18564,10 +18568,10 @@
         <v>857</v>
       </c>
       <c r="B858" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="C858" t="s">
-        <v>1719</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="859" spans="1:3" x14ac:dyDescent="0.3">
@@ -18575,10 +18579,10 @@
         <v>858</v>
       </c>
       <c r="B859" t="s">
-        <v>1696</v>
+        <v>1694</v>
       </c>
       <c r="C859" t="s">
-        <v>1720</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.3">
@@ -18586,10 +18590,10 @@
         <v>859</v>
       </c>
       <c r="B860" t="s">
-        <v>1697</v>
+        <v>1695</v>
       </c>
       <c r="C860" t="s">
-        <v>1721</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="861" spans="1:3" x14ac:dyDescent="0.3">
@@ -18597,10 +18601,10 @@
         <v>860</v>
       </c>
       <c r="B861" t="s">
-        <v>1698</v>
+        <v>1696</v>
       </c>
       <c r="C861" t="s">
-        <v>1722</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="862" spans="1:3" x14ac:dyDescent="0.3">
@@ -18608,10 +18612,10 @@
         <v>861</v>
       </c>
       <c r="B862" t="s">
-        <v>1699</v>
+        <v>1697</v>
       </c>
       <c r="C862" t="s">
-        <v>1723</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="863" spans="1:3" x14ac:dyDescent="0.3">
@@ -18619,10 +18623,10 @@
         <v>862</v>
       </c>
       <c r="B863" t="s">
-        <v>1725</v>
+        <v>1721</v>
       </c>
       <c r="C863" t="s">
-        <v>1731</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="864" spans="1:3" x14ac:dyDescent="0.3">
@@ -18630,10 +18634,10 @@
         <v>863</v>
       </c>
       <c r="B864" t="s">
-        <v>1726</v>
+        <v>1722</v>
       </c>
       <c r="C864" t="s">
-        <v>1732</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="865" spans="1:3" x14ac:dyDescent="0.3">
@@ -18641,10 +18645,10 @@
         <v>864</v>
       </c>
       <c r="B865" t="s">
-        <v>1727</v>
+        <v>1723</v>
       </c>
       <c r="C865" t="s">
-        <v>1733</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="866" spans="1:3" x14ac:dyDescent="0.3">
@@ -18652,10 +18656,10 @@
         <v>865</v>
       </c>
       <c r="B866" t="s">
-        <v>1728</v>
+        <v>1724</v>
       </c>
       <c r="C866" t="s">
-        <v>1733</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="867" spans="1:3" x14ac:dyDescent="0.3">
@@ -18663,10 +18667,10 @@
         <v>866</v>
       </c>
       <c r="B867" t="s">
+        <v>1726</v>
+      </c>
+      <c r="C867" t="s">
         <v>1730</v>
-      </c>
-      <c r="C867" t="s">
-        <v>1734</v>
       </c>
     </row>
     <row r="868" spans="1:3" x14ac:dyDescent="0.3">
@@ -18674,10 +18678,10 @@
         <v>867</v>
       </c>
       <c r="B868" t="s">
-        <v>1729</v>
+        <v>1725</v>
       </c>
       <c r="C868" t="s">
-        <v>1735</v>
+        <v>1731</v>
       </c>
     </row>
   </sheetData>

--- a/30_table/01_테스트버전/Table_STR_String.xlsx
+++ b/30_table/01_테스트버전/Table_STR_String.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="1736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="1738">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4861,22 +4861,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>버그 제보</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>버그 제보 페이지로 이동하겠습니까?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>게임 리뷰</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>게임 리뷰 페이지로 이동하겠습니까?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>STR_ERROR_8002</t>
   </si>
   <si>
@@ -5934,6 +5918,30 @@
   </si>
   <si>
     <t>보물 창고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_MSG_WARNING</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.본 게임의 영웅, 아이템 및 플레이 데이터는 게임 삭제 또는 데이터 삭제 시 모두 삭제되며, [ff0000]복구할 수 없습니다.[-]\n2.[ff0000]삭제에 대한 책임[-]은 유저 본인에게 있습니다.\n3.버그 이용, 기타 어뷰징 행위 시 회사는 해당 계정을 [ff0000]정지[-]할 수 있습니다.\n\n위 내용에 동의 하십니까?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>별점과 리뷰는 더 좋은 게임을 만들기 위해 소중히 사용됩니다.\n게임 리뷰 페이지로 이동하겠습니까?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>불편하게 해 드려 죄송합니다.\n오류 신고 페이지로 이동하겠습니까?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임 평가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>문의 또는 오류 신고</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -9121,7 +9129,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E868"/>
+  <dimension ref="A1:E869"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="33" bestFit="1" customWidth="1"/>
@@ -10233,7 +10241,7 @@
         <v>486</v>
       </c>
       <c r="C100" t="s">
-        <v>1534</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
@@ -10244,7 +10252,7 @@
         <v>487</v>
       </c>
       <c r="C101" t="s">
-        <v>1521</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
@@ -11333,7 +11341,7 @@
         <v>516</v>
       </c>
       <c r="C200" t="s">
-        <v>1535</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
@@ -11344,7 +11352,7 @@
         <v>517</v>
       </c>
       <c r="C201" t="s">
-        <v>1522</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
@@ -11498,7 +11506,7 @@
         <v>66</v>
       </c>
       <c r="C215" t="s">
-        <v>1505</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
@@ -11509,7 +11517,7 @@
         <v>67</v>
       </c>
       <c r="C216" t="s">
-        <v>1506</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
@@ -11520,7 +11528,7 @@
         <v>68</v>
       </c>
       <c r="C217" t="s">
-        <v>1507</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
@@ -11531,7 +11539,7 @@
         <v>69</v>
       </c>
       <c r="C218" t="s">
-        <v>1508</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
@@ -12158,7 +12166,7 @@
         <v>87</v>
       </c>
       <c r="C275" t="s">
-        <v>1422</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.3">
@@ -12400,7 +12408,7 @@
         <v>88</v>
       </c>
       <c r="C297" t="s">
-        <v>1426</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.3">
@@ -12411,7 +12419,7 @@
         <v>89</v>
       </c>
       <c r="C298" t="s">
-        <v>1426</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
@@ -12422,7 +12430,7 @@
         <v>108</v>
       </c>
       <c r="C299" t="s">
-        <v>1427</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
@@ -12433,7 +12441,7 @@
         <v>109</v>
       </c>
       <c r="C300" t="s">
-        <v>1428</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.3">
@@ -12444,7 +12452,7 @@
         <v>110</v>
       </c>
       <c r="C301" t="s">
-        <v>1429</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.3">
@@ -12455,7 +12463,7 @@
         <v>111</v>
       </c>
       <c r="C302" t="s">
-        <v>1430</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.3">
@@ -12466,7 +12474,7 @@
         <v>112</v>
       </c>
       <c r="C303" t="s">
-        <v>1431</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.3">
@@ -12477,7 +12485,7 @@
         <v>113</v>
       </c>
       <c r="C304" t="s">
-        <v>1432</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.3">
@@ -12488,7 +12496,7 @@
         <v>114</v>
       </c>
       <c r="C305" t="s">
-        <v>1433</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.3">
@@ -12499,7 +12507,7 @@
         <v>115</v>
       </c>
       <c r="C306" t="s">
-        <v>1434</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.3">
@@ -12510,7 +12518,7 @@
         <v>116</v>
       </c>
       <c r="C307" t="s">
-        <v>1435</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.3">
@@ -12521,7 +12529,7 @@
         <v>117</v>
       </c>
       <c r="C308" t="s">
-        <v>1436</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.3">
@@ -12532,7 +12540,7 @@
         <v>118</v>
       </c>
       <c r="C309" t="s">
-        <v>1437</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.3">
@@ -12543,7 +12551,7 @@
         <v>119</v>
       </c>
       <c r="C310" t="s">
-        <v>1438</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.3">
@@ -12554,7 +12562,7 @@
         <v>120</v>
       </c>
       <c r="C311" t="s">
-        <v>1439</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.3">
@@ -12565,7 +12573,7 @@
         <v>121</v>
       </c>
       <c r="C312" t="s">
-        <v>1440</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.3">
@@ -12576,7 +12584,7 @@
         <v>122</v>
       </c>
       <c r="C313" t="s">
-        <v>1441</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.3">
@@ -12587,7 +12595,7 @@
         <v>394</v>
       </c>
       <c r="C314" t="s">
-        <v>1442</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.3">
@@ -12598,7 +12606,7 @@
         <v>395</v>
       </c>
       <c r="C315" t="s">
-        <v>1438</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.3">
@@ -12609,7 +12617,7 @@
         <v>396</v>
       </c>
       <c r="C316" t="s">
-        <v>1443</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.3">
@@ -12620,7 +12628,7 @@
         <v>397</v>
       </c>
       <c r="C317" t="s">
-        <v>1444</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.3">
@@ -12631,7 +12639,7 @@
         <v>398</v>
       </c>
       <c r="C318" t="s">
-        <v>1441</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.3">
@@ -12642,7 +12650,7 @@
         <v>162</v>
       </c>
       <c r="C319" t="s">
-        <v>1523</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.3">
@@ -13236,7 +13244,7 @@
         <v>218</v>
       </c>
       <c r="C373" t="s">
-        <v>1513</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.3">
@@ -13247,7 +13255,7 @@
         <v>219</v>
       </c>
       <c r="C374" t="s">
-        <v>1514</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.3">
@@ -13280,7 +13288,7 @@
         <v>225</v>
       </c>
       <c r="C377" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.3">
@@ -13302,7 +13310,7 @@
         <v>226</v>
       </c>
       <c r="C379" t="s">
-        <v>1511</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.3">
@@ -13335,7 +13343,7 @@
         <v>230</v>
       </c>
       <c r="C382" t="s">
-        <v>1515</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.3">
@@ -13497,10 +13505,10 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>1538</v>
+        <v>1534</v>
       </c>
       <c r="C397" t="s">
-        <v>1539</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.3">
@@ -13596,10 +13604,10 @@
         <v>405</v>
       </c>
       <c r="B406" t="s">
-        <v>1509</v>
+        <v>1505</v>
       </c>
       <c r="C406" t="s">
-        <v>1510</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.3">
@@ -13610,7 +13618,7 @@
         <v>259</v>
       </c>
       <c r="C407" t="s">
-        <v>1524</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.3">
@@ -13731,7 +13739,7 @@
         <v>363</v>
       </c>
       <c r="C418" t="s">
-        <v>1525</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.3">
@@ -13742,7 +13750,7 @@
         <v>269</v>
       </c>
       <c r="C419" t="s">
-        <v>1526</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.3">
@@ -13753,7 +13761,7 @@
         <v>270</v>
       </c>
       <c r="C420" t="s">
-        <v>1527</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.3">
@@ -13764,7 +13772,7 @@
         <v>271</v>
       </c>
       <c r="C421" t="s">
-        <v>1528</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.3">
@@ -13775,7 +13783,7 @@
         <v>272</v>
       </c>
       <c r="C422" t="s">
-        <v>1529</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.3">
@@ -13786,7 +13794,7 @@
         <v>273</v>
       </c>
       <c r="C423" t="s">
-        <v>1530</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.3">
@@ -13797,7 +13805,7 @@
         <v>274</v>
       </c>
       <c r="C424" t="s">
-        <v>1531</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.3">
@@ -13808,7 +13816,7 @@
         <v>275</v>
       </c>
       <c r="C425" t="s">
-        <v>1536</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.3">
@@ -13984,7 +13992,7 @@
         <v>365</v>
       </c>
       <c r="C441" t="s">
-        <v>1533</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.3">
@@ -13995,7 +14003,7 @@
         <v>366</v>
       </c>
       <c r="C442" t="s">
-        <v>1532</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.3">
@@ -14006,7 +14014,7 @@
         <v>388</v>
       </c>
       <c r="C443" t="s">
-        <v>1537</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.3">
@@ -14113,7 +14121,7 @@
         <v>452</v>
       </c>
       <c r="B453" t="s">
-        <v>1417</v>
+        <v>1413</v>
       </c>
       <c r="C453" t="s">
         <v>991</v>
@@ -14124,10 +14132,10 @@
         <v>453</v>
       </c>
       <c r="B454" t="s">
-        <v>1418</v>
+        <v>1414</v>
       </c>
       <c r="C454" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.3">
@@ -14135,10 +14143,10 @@
         <v>454</v>
       </c>
       <c r="B455" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
       <c r="C455" t="s">
-        <v>1421</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.3">
@@ -14732,7 +14740,7 @@
         <v>1006</v>
       </c>
       <c r="C509" t="s">
-        <v>1516</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.3">
@@ -14765,7 +14773,7 @@
         <v>1012</v>
       </c>
       <c r="C512" t="s">
-        <v>1517</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.3">
@@ -14776,7 +14784,7 @@
         <v>1014</v>
       </c>
       <c r="C513" t="s">
-        <v>1518</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.3">
@@ -15128,7 +15136,7 @@
         <v>1250</v>
       </c>
       <c r="C545" t="s">
-        <v>1519</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.3">
@@ -15337,7 +15345,7 @@
         <v>1269</v>
       </c>
       <c r="C564" t="s">
-        <v>1520</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.3">
@@ -15425,7 +15433,7 @@
         <v>897</v>
       </c>
       <c r="C572" t="s">
-        <v>1615</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.3">
@@ -15436,7 +15444,7 @@
         <v>898</v>
       </c>
       <c r="C573" t="s">
-        <v>1616</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.3">
@@ -15491,7 +15499,7 @@
         <v>907</v>
       </c>
       <c r="C578" t="s">
-        <v>1617</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.3">
@@ -15623,7 +15631,7 @@
         <v>934</v>
       </c>
       <c r="C590" t="s">
-        <v>1618</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.3">
@@ -15645,7 +15653,7 @@
         <v>936</v>
       </c>
       <c r="C592" t="s">
-        <v>1620</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.3">
@@ -15656,7 +15664,7 @@
         <v>937</v>
       </c>
       <c r="C593" t="s">
-        <v>1621</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.3">
@@ -15744,7 +15752,7 @@
         <v>948</v>
       </c>
       <c r="C601" t="s">
-        <v>1619</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.3">
@@ -16129,7 +16137,7 @@
         <v>1297</v>
       </c>
       <c r="C636" t="s">
-        <v>1732</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.3">
@@ -16393,7 +16401,7 @@
         <v>1118</v>
       </c>
       <c r="C660" t="s">
-        <v>1423</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.3">
@@ -16445,10 +16453,10 @@
         <v>664</v>
       </c>
       <c r="B665" t="s">
-        <v>1613</v>
+        <v>1609</v>
       </c>
       <c r="C665" t="s">
-        <v>1614</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.3">
@@ -17218,7 +17226,7 @@
         <v>1409</v>
       </c>
       <c r="C735" t="s">
-        <v>1415</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="736" spans="1:3" x14ac:dyDescent="0.3">
@@ -17229,7 +17237,7 @@
         <v>1410</v>
       </c>
       <c r="C736" t="s">
-        <v>1416</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="737" spans="1:3" x14ac:dyDescent="0.3">
@@ -17240,7 +17248,7 @@
         <v>1411</v>
       </c>
       <c r="C737" t="s">
-        <v>1413</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="738" spans="1:3" x14ac:dyDescent="0.3">
@@ -17251,7 +17259,7 @@
         <v>1412</v>
       </c>
       <c r="C738" t="s">
-        <v>1414</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.3">
@@ -17259,10 +17267,10 @@
         <v>738</v>
       </c>
       <c r="B739" t="s">
-        <v>1424</v>
+        <v>1420</v>
       </c>
       <c r="C739" t="s">
-        <v>1425</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="740" spans="1:3" x14ac:dyDescent="0.3">
@@ -17270,10 +17278,10 @@
         <v>739</v>
       </c>
       <c r="B740" t="s">
-        <v>1445</v>
+        <v>1441</v>
       </c>
       <c r="C740" t="s">
-        <v>1447</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="741" spans="1:3" x14ac:dyDescent="0.3">
@@ -17281,10 +17289,10 @@
         <v>740</v>
       </c>
       <c r="B741" t="s">
-        <v>1446</v>
+        <v>1442</v>
       </c>
       <c r="C741" t="s">
-        <v>1448</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="742" spans="1:3" x14ac:dyDescent="0.3">
@@ -17292,10 +17300,10 @@
         <v>741</v>
       </c>
       <c r="B742" t="s">
-        <v>1449</v>
+        <v>1445</v>
       </c>
       <c r="C742" t="s">
-        <v>1451</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="743" spans="1:3" x14ac:dyDescent="0.3">
@@ -17303,10 +17311,10 @@
         <v>742</v>
       </c>
       <c r="B743" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="C743" t="s">
-        <v>1452</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="744" spans="1:3" x14ac:dyDescent="0.3">
@@ -17314,10 +17322,10 @@
         <v>743</v>
       </c>
       <c r="B744" t="s">
-        <v>1453</v>
+        <v>1449</v>
       </c>
       <c r="C744" t="s">
-        <v>1461</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="745" spans="1:3" x14ac:dyDescent="0.3">
@@ -17325,10 +17333,10 @@
         <v>744</v>
       </c>
       <c r="B745" t="s">
-        <v>1454</v>
+        <v>1450</v>
       </c>
       <c r="C745" t="s">
-        <v>1462</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="746" spans="1:3" x14ac:dyDescent="0.3">
@@ -17336,10 +17344,10 @@
         <v>745</v>
       </c>
       <c r="B746" t="s">
-        <v>1455</v>
+        <v>1451</v>
       </c>
       <c r="C746" t="s">
-        <v>1463</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="747" spans="1:3" x14ac:dyDescent="0.3">
@@ -17347,10 +17355,10 @@
         <v>746</v>
       </c>
       <c r="B747" t="s">
-        <v>1456</v>
+        <v>1452</v>
       </c>
       <c r="C747" t="s">
-        <v>1464</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="748" spans="1:3" x14ac:dyDescent="0.3">
@@ -17358,10 +17366,10 @@
         <v>747</v>
       </c>
       <c r="B748" t="s">
-        <v>1457</v>
+        <v>1453</v>
       </c>
       <c r="C748" t="s">
-        <v>1465</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="749" spans="1:3" x14ac:dyDescent="0.3">
@@ -17369,10 +17377,10 @@
         <v>748</v>
       </c>
       <c r="B749" t="s">
-        <v>1458</v>
+        <v>1454</v>
       </c>
       <c r="C749" t="s">
-        <v>1466</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.3">
@@ -17380,10 +17388,10 @@
         <v>749</v>
       </c>
       <c r="B750" t="s">
-        <v>1459</v>
+        <v>1455</v>
       </c>
       <c r="C750" t="s">
-        <v>1467</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="751" spans="1:3" x14ac:dyDescent="0.3">
@@ -17391,10 +17399,10 @@
         <v>750</v>
       </c>
       <c r="B751" t="s">
-        <v>1460</v>
+        <v>1456</v>
       </c>
       <c r="C751" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="752" spans="1:3" x14ac:dyDescent="0.3">
@@ -17402,10 +17410,10 @@
         <v>751</v>
       </c>
       <c r="B752" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
       <c r="C752" t="s">
-        <v>1479</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="753" spans="1:3" x14ac:dyDescent="0.3">
@@ -17413,10 +17421,10 @@
         <v>752</v>
       </c>
       <c r="B753" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
       <c r="C753" t="s">
-        <v>1479</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="754" spans="1:3" x14ac:dyDescent="0.3">
@@ -17424,10 +17432,10 @@
         <v>753</v>
       </c>
       <c r="B754" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
       <c r="C754" t="s">
-        <v>1479</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="755" spans="1:3" x14ac:dyDescent="0.3">
@@ -17435,10 +17443,10 @@
         <v>754</v>
       </c>
       <c r="B755" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
       <c r="C755" t="s">
-        <v>1479</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="756" spans="1:3" x14ac:dyDescent="0.3">
@@ -17446,10 +17454,10 @@
         <v>755</v>
       </c>
       <c r="B756" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
       <c r="C756" t="s">
-        <v>1479</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="757" spans="1:3" x14ac:dyDescent="0.3">
@@ -17457,10 +17465,10 @@
         <v>756</v>
       </c>
       <c r="B757" t="s">
-        <v>1474</v>
+        <v>1470</v>
       </c>
       <c r="C757" t="s">
-        <v>1480</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="758" spans="1:3" x14ac:dyDescent="0.3">
@@ -17468,10 +17476,10 @@
         <v>757</v>
       </c>
       <c r="B758" t="s">
-        <v>1475</v>
+        <v>1471</v>
       </c>
       <c r="C758" t="s">
-        <v>1480</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="759" spans="1:3" x14ac:dyDescent="0.3">
@@ -17479,10 +17487,10 @@
         <v>758</v>
       </c>
       <c r="B759" t="s">
+        <v>1472</v>
+      </c>
+      <c r="C759" t="s">
         <v>1476</v>
-      </c>
-      <c r="C759" t="s">
-        <v>1480</v>
       </c>
     </row>
     <row r="760" spans="1:3" x14ac:dyDescent="0.3">
@@ -17490,10 +17498,10 @@
         <v>759</v>
       </c>
       <c r="B760" t="s">
-        <v>1477</v>
+        <v>1473</v>
       </c>
       <c r="C760" t="s">
-        <v>1480</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.3">
@@ -17501,10 +17509,10 @@
         <v>760</v>
       </c>
       <c r="B761" t="s">
-        <v>1478</v>
+        <v>1474</v>
       </c>
       <c r="C761" t="s">
-        <v>1480</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="762" spans="1:3" x14ac:dyDescent="0.3">
@@ -17512,10 +17520,10 @@
         <v>761</v>
       </c>
       <c r="B762" t="s">
-        <v>1481</v>
+        <v>1477</v>
       </c>
       <c r="C762" t="s">
-        <v>1483</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="763" spans="1:3" x14ac:dyDescent="0.3">
@@ -17523,10 +17531,10 @@
         <v>762</v>
       </c>
       <c r="B763" t="s">
-        <v>1482</v>
+        <v>1478</v>
       </c>
       <c r="C763" t="s">
-        <v>1484</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="764" spans="1:3" x14ac:dyDescent="0.3">
@@ -17534,10 +17542,10 @@
         <v>763</v>
       </c>
       <c r="B764" t="s">
-        <v>1485</v>
+        <v>1481</v>
       </c>
       <c r="C764" t="s">
-        <v>1486</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="765" spans="1:3" x14ac:dyDescent="0.3">
@@ -17545,10 +17553,10 @@
         <v>764</v>
       </c>
       <c r="B765" t="s">
-        <v>1488</v>
+        <v>1484</v>
       </c>
       <c r="C765" t="s">
-        <v>1487</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="766" spans="1:3" x14ac:dyDescent="0.3">
@@ -17556,10 +17564,10 @@
         <v>765</v>
       </c>
       <c r="B766" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
       <c r="C766" t="s">
-        <v>1491</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="767" spans="1:3" x14ac:dyDescent="0.3">
@@ -17567,10 +17575,10 @@
         <v>766</v>
       </c>
       <c r="B767" t="s">
-        <v>1489</v>
+        <v>1485</v>
       </c>
       <c r="C767" t="s">
-        <v>1492</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="768" spans="1:3" x14ac:dyDescent="0.3">
@@ -17578,10 +17586,10 @@
         <v>767</v>
       </c>
       <c r="B768" t="s">
-        <v>1493</v>
+        <v>1489</v>
       </c>
       <c r="C768" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="769" spans="1:3" x14ac:dyDescent="0.3">
@@ -17589,10 +17597,10 @@
         <v>768</v>
       </c>
       <c r="B769" t="s">
-        <v>1494</v>
+        <v>1490</v>
       </c>
       <c r="C769" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="770" spans="1:3" x14ac:dyDescent="0.3">
@@ -17600,10 +17608,10 @@
         <v>769</v>
       </c>
       <c r="B770" t="s">
-        <v>1495</v>
+        <v>1491</v>
       </c>
       <c r="C770" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="771" spans="1:3" x14ac:dyDescent="0.3">
@@ -17611,10 +17619,10 @@
         <v>770</v>
       </c>
       <c r="B771" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="C771" t="s">
-        <v>1502</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.3">
@@ -17622,10 +17630,10 @@
         <v>771</v>
       </c>
       <c r="B772" t="s">
-        <v>1497</v>
+        <v>1493</v>
       </c>
       <c r="C772" t="s">
-        <v>1503</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="773" spans="1:3" x14ac:dyDescent="0.3">
@@ -17633,10 +17641,10 @@
         <v>772</v>
       </c>
       <c r="B773" t="s">
-        <v>1498</v>
+        <v>1494</v>
       </c>
       <c r="C773" t="s">
-        <v>1504</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="774" spans="1:3" x14ac:dyDescent="0.3">
@@ -17644,10 +17652,10 @@
         <v>773</v>
       </c>
       <c r="B774" t="s">
-        <v>1549</v>
+        <v>1545</v>
       </c>
       <c r="C774" t="s">
-        <v>1550</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="775" spans="1:3" x14ac:dyDescent="0.3">
@@ -17655,10 +17663,10 @@
         <v>774</v>
       </c>
       <c r="B775" t="s">
-        <v>1543</v>
+        <v>1539</v>
       </c>
       <c r="C775" t="s">
-        <v>1551</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="776" spans="1:3" x14ac:dyDescent="0.3">
@@ -17666,10 +17674,10 @@
         <v>775</v>
       </c>
       <c r="B776" t="s">
-        <v>1544</v>
+        <v>1540</v>
       </c>
       <c r="C776" t="s">
-        <v>1552</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="777" spans="1:3" x14ac:dyDescent="0.3">
@@ -17677,10 +17685,10 @@
         <v>776</v>
       </c>
       <c r="B777" t="s">
-        <v>1545</v>
+        <v>1541</v>
       </c>
       <c r="C777" t="s">
-        <v>1556</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="778" spans="1:3" x14ac:dyDescent="0.3">
@@ -17688,10 +17696,10 @@
         <v>777</v>
       </c>
       <c r="B778" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="C778" t="s">
-        <v>1553</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="779" spans="1:3" x14ac:dyDescent="0.3">
@@ -17699,10 +17707,10 @@
         <v>778</v>
       </c>
       <c r="B779" t="s">
-        <v>1547</v>
+        <v>1543</v>
       </c>
       <c r="C779" t="s">
-        <v>1554</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="780" spans="1:3" x14ac:dyDescent="0.3">
@@ -17710,10 +17718,10 @@
         <v>779</v>
       </c>
       <c r="B780" t="s">
-        <v>1548</v>
+        <v>1544</v>
       </c>
       <c r="C780" t="s">
-        <v>1555</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="781" spans="1:3" x14ac:dyDescent="0.3">
@@ -17721,10 +17729,10 @@
         <v>780</v>
       </c>
       <c r="B781" t="s">
-        <v>1597</v>
+        <v>1593</v>
       </c>
       <c r="C781" t="s">
-        <v>1598</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="782" spans="1:3" x14ac:dyDescent="0.3">
@@ -17732,10 +17740,10 @@
         <v>781</v>
       </c>
       <c r="B782" t="s">
-        <v>1557</v>
+        <v>1553</v>
       </c>
       <c r="C782" t="s">
-        <v>1564</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.3">
@@ -17743,10 +17751,10 @@
         <v>782</v>
       </c>
       <c r="B783" t="s">
-        <v>1558</v>
+        <v>1554</v>
       </c>
       <c r="C783" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="784" spans="1:3" x14ac:dyDescent="0.3">
@@ -17754,10 +17762,10 @@
         <v>783</v>
       </c>
       <c r="B784" t="s">
-        <v>1559</v>
+        <v>1555</v>
       </c>
       <c r="C784" t="s">
-        <v>1609</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="785" spans="1:3" x14ac:dyDescent="0.3">
@@ -17765,10 +17773,10 @@
         <v>784</v>
       </c>
       <c r="B785" t="s">
-        <v>1560</v>
+        <v>1556</v>
       </c>
       <c r="C785" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="786" spans="1:3" x14ac:dyDescent="0.3">
@@ -17776,10 +17784,10 @@
         <v>785</v>
       </c>
       <c r="B786" t="s">
-        <v>1561</v>
+        <v>1557</v>
       </c>
       <c r="C786" t="s">
-        <v>1610</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="787" spans="1:3" x14ac:dyDescent="0.3">
@@ -17787,10 +17795,10 @@
         <v>786</v>
       </c>
       <c r="B787" t="s">
-        <v>1562</v>
+        <v>1558</v>
       </c>
       <c r="C787" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="788" spans="1:3" x14ac:dyDescent="0.3">
@@ -17798,10 +17806,10 @@
         <v>787</v>
       </c>
       <c r="B788" t="s">
-        <v>1563</v>
+        <v>1559</v>
       </c>
       <c r="C788" t="s">
-        <v>1568</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="789" spans="1:3" x14ac:dyDescent="0.3">
@@ -17809,10 +17817,10 @@
         <v>788</v>
       </c>
       <c r="B789" t="s">
-        <v>1599</v>
+        <v>1595</v>
       </c>
       <c r="C789" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="790" spans="1:3" x14ac:dyDescent="0.3">
@@ -17820,10 +17828,10 @@
         <v>789</v>
       </c>
       <c r="B790" t="s">
-        <v>1540</v>
+        <v>1536</v>
       </c>
       <c r="C790" t="s">
-        <v>1542</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="791" spans="1:3" x14ac:dyDescent="0.3">
@@ -17831,10 +17839,10 @@
         <v>790</v>
       </c>
       <c r="B791" t="s">
-        <v>1541</v>
+        <v>1537</v>
       </c>
       <c r="C791" t="s">
-        <v>1569</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="792" spans="1:3" x14ac:dyDescent="0.3">
@@ -17842,10 +17850,10 @@
         <v>791</v>
       </c>
       <c r="B792" t="s">
-        <v>1572</v>
+        <v>1568</v>
       </c>
       <c r="C792" t="s">
-        <v>1570</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="793" spans="1:3" x14ac:dyDescent="0.3">
@@ -17853,10 +17861,10 @@
         <v>792</v>
       </c>
       <c r="B793" t="s">
-        <v>1573</v>
+        <v>1569</v>
       </c>
       <c r="C793" t="s">
-        <v>1611</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.3">
@@ -17864,10 +17872,10 @@
         <v>793</v>
       </c>
       <c r="B794" t="s">
-        <v>1574</v>
+        <v>1570</v>
       </c>
       <c r="C794" t="s">
-        <v>1571</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="795" spans="1:3" x14ac:dyDescent="0.3">
@@ -17875,10 +17883,10 @@
         <v>794</v>
       </c>
       <c r="B795" t="s">
-        <v>1575</v>
+        <v>1571</v>
       </c>
       <c r="C795" t="s">
-        <v>1576</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="796" spans="1:3" x14ac:dyDescent="0.3">
@@ -17886,10 +17894,10 @@
         <v>795</v>
       </c>
       <c r="B796" t="s">
-        <v>1583</v>
+        <v>1579</v>
       </c>
       <c r="C796" t="s">
-        <v>1577</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="797" spans="1:3" x14ac:dyDescent="0.3">
@@ -17897,10 +17905,10 @@
         <v>796</v>
       </c>
       <c r="B797" t="s">
-        <v>1584</v>
+        <v>1580</v>
       </c>
       <c r="C797" t="s">
-        <v>1578</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="798" spans="1:3" x14ac:dyDescent="0.3">
@@ -17908,10 +17916,10 @@
         <v>797</v>
       </c>
       <c r="B798" t="s">
-        <v>1585</v>
+        <v>1581</v>
       </c>
       <c r="C798" t="s">
-        <v>1579</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="799" spans="1:3" x14ac:dyDescent="0.3">
@@ -17919,10 +17927,10 @@
         <v>798</v>
       </c>
       <c r="B799" t="s">
-        <v>1586</v>
+        <v>1582</v>
       </c>
       <c r="C799" t="s">
-        <v>1580</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="800" spans="1:3" x14ac:dyDescent="0.3">
@@ -17930,10 +17938,10 @@
         <v>799</v>
       </c>
       <c r="B800" t="s">
-        <v>1587</v>
+        <v>1583</v>
       </c>
       <c r="C800" t="s">
-        <v>1581</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="801" spans="1:3" x14ac:dyDescent="0.3">
@@ -17941,10 +17949,10 @@
         <v>800</v>
       </c>
       <c r="B801" t="s">
-        <v>1588</v>
+        <v>1584</v>
       </c>
       <c r="C801" t="s">
-        <v>1582</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="802" spans="1:3" x14ac:dyDescent="0.3">
@@ -17952,10 +17960,10 @@
         <v>801</v>
       </c>
       <c r="B802" t="s">
-        <v>1589</v>
+        <v>1585</v>
       </c>
       <c r="C802" t="s">
-        <v>1590</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="803" spans="1:3" x14ac:dyDescent="0.3">
@@ -17963,10 +17971,10 @@
         <v>802</v>
       </c>
       <c r="B803" t="s">
-        <v>1594</v>
+        <v>1590</v>
       </c>
       <c r="C803" t="s">
-        <v>1591</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="804" spans="1:3" x14ac:dyDescent="0.3">
@@ -17974,10 +17982,10 @@
         <v>803</v>
       </c>
       <c r="B804" t="s">
-        <v>1595</v>
+        <v>1591</v>
       </c>
       <c r="C804" t="s">
-        <v>1592</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.3">
@@ -17985,10 +17993,10 @@
         <v>804</v>
       </c>
       <c r="B805" t="s">
-        <v>1596</v>
+        <v>1592</v>
       </c>
       <c r="C805" t="s">
-        <v>1593</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="806" spans="1:3" x14ac:dyDescent="0.3">
@@ -17996,10 +18004,10 @@
         <v>805</v>
       </c>
       <c r="B806" t="s">
-        <v>1600</v>
+        <v>1596</v>
       </c>
       <c r="C806" t="s">
-        <v>1601</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="807" spans="1:3" x14ac:dyDescent="0.3">
@@ -18007,10 +18015,10 @@
         <v>806</v>
       </c>
       <c r="B807" t="s">
-        <v>1605</v>
+        <v>1601</v>
       </c>
       <c r="C807" t="s">
-        <v>1602</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="808" spans="1:3" x14ac:dyDescent="0.3">
@@ -18018,10 +18026,10 @@
         <v>807</v>
       </c>
       <c r="B808" t="s">
-        <v>1606</v>
+        <v>1602</v>
       </c>
       <c r="C808" t="s">
-        <v>1612</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="809" spans="1:3" x14ac:dyDescent="0.3">
@@ -18029,10 +18037,10 @@
         <v>808</v>
       </c>
       <c r="B809" t="s">
-        <v>1607</v>
+        <v>1603</v>
       </c>
       <c r="C809" t="s">
-        <v>1603</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="810" spans="1:3" x14ac:dyDescent="0.3">
@@ -18040,10 +18048,10 @@
         <v>809</v>
       </c>
       <c r="B810" t="s">
-        <v>1608</v>
+        <v>1604</v>
       </c>
       <c r="C810" t="s">
-        <v>1604</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="811" spans="1:3" x14ac:dyDescent="0.3">
@@ -18051,10 +18059,10 @@
         <v>810</v>
       </c>
       <c r="B811" t="s">
-        <v>1622</v>
+        <v>1618</v>
       </c>
       <c r="C811" t="s">
-        <v>1648</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="812" spans="1:3" x14ac:dyDescent="0.3">
@@ -18062,10 +18070,10 @@
         <v>811</v>
       </c>
       <c r="B812" t="s">
-        <v>1623</v>
+        <v>1619</v>
       </c>
       <c r="C812" t="s">
-        <v>1649</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="813" spans="1:3" x14ac:dyDescent="0.3">
@@ -18073,10 +18081,10 @@
         <v>812</v>
       </c>
       <c r="B813" t="s">
-        <v>1624</v>
+        <v>1620</v>
       </c>
       <c r="C813" t="s">
-        <v>1650</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="814" spans="1:3" x14ac:dyDescent="0.3">
@@ -18084,10 +18092,10 @@
         <v>813</v>
       </c>
       <c r="B814" t="s">
-        <v>1625</v>
+        <v>1621</v>
       </c>
       <c r="C814" t="s">
-        <v>1651</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="815" spans="1:3" x14ac:dyDescent="0.3">
@@ -18095,10 +18103,10 @@
         <v>814</v>
       </c>
       <c r="B815" t="s">
-        <v>1626</v>
+        <v>1622</v>
       </c>
       <c r="C815" t="s">
-        <v>1652</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.3">
@@ -18106,10 +18114,10 @@
         <v>815</v>
       </c>
       <c r="B816" t="s">
-        <v>1627</v>
+        <v>1623</v>
       </c>
       <c r="C816" t="s">
-        <v>1734</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="817" spans="1:3" x14ac:dyDescent="0.3">
@@ -18117,10 +18125,10 @@
         <v>816</v>
       </c>
       <c r="B817" t="s">
-        <v>1628</v>
+        <v>1624</v>
       </c>
       <c r="C817" t="s">
-        <v>1735</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="818" spans="1:3" x14ac:dyDescent="0.3">
@@ -18128,10 +18136,10 @@
         <v>817</v>
       </c>
       <c r="B818" t="s">
-        <v>1629</v>
+        <v>1625</v>
       </c>
       <c r="C818" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="819" spans="1:3" x14ac:dyDescent="0.3">
@@ -18139,10 +18147,10 @@
         <v>818</v>
       </c>
       <c r="B819" t="s">
-        <v>1630</v>
+        <v>1626</v>
       </c>
       <c r="C819" t="s">
-        <v>1653</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="820" spans="1:3" x14ac:dyDescent="0.3">
@@ -18150,10 +18158,10 @@
         <v>819</v>
       </c>
       <c r="B820" t="s">
-        <v>1631</v>
+        <v>1627</v>
       </c>
       <c r="C820" t="s">
-        <v>1654</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="821" spans="1:3" x14ac:dyDescent="0.3">
@@ -18161,10 +18169,10 @@
         <v>820</v>
       </c>
       <c r="B821" t="s">
-        <v>1632</v>
+        <v>1628</v>
       </c>
       <c r="C821" t="s">
-        <v>1655</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="822" spans="1:3" x14ac:dyDescent="0.3">
@@ -18172,10 +18180,10 @@
         <v>821</v>
       </c>
       <c r="B822" t="s">
-        <v>1633</v>
+        <v>1629</v>
       </c>
       <c r="C822" t="s">
-        <v>1656</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="823" spans="1:3" x14ac:dyDescent="0.3">
@@ -18183,10 +18191,10 @@
         <v>822</v>
       </c>
       <c r="B823" t="s">
-        <v>1634</v>
+        <v>1630</v>
       </c>
       <c r="C823" t="s">
-        <v>1657</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="824" spans="1:3" x14ac:dyDescent="0.3">
@@ -18194,10 +18202,10 @@
         <v>823</v>
       </c>
       <c r="B824" t="s">
-        <v>1635</v>
+        <v>1631</v>
       </c>
       <c r="C824" t="s">
-        <v>1658</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="825" spans="1:3" x14ac:dyDescent="0.3">
@@ -18205,10 +18213,10 @@
         <v>824</v>
       </c>
       <c r="B825" t="s">
-        <v>1636</v>
+        <v>1632</v>
       </c>
       <c r="C825" t="s">
-        <v>1659</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="826" spans="1:3" x14ac:dyDescent="0.3">
@@ -18216,10 +18224,10 @@
         <v>825</v>
       </c>
       <c r="B826" t="s">
-        <v>1637</v>
+        <v>1633</v>
       </c>
       <c r="C826" t="s">
-        <v>1660</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.3">
@@ -18227,10 +18235,10 @@
         <v>826</v>
       </c>
       <c r="B827" t="s">
-        <v>1638</v>
+        <v>1634</v>
       </c>
       <c r="C827" t="s">
-        <v>1661</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="828" spans="1:3" x14ac:dyDescent="0.3">
@@ -18238,10 +18246,10 @@
         <v>827</v>
       </c>
       <c r="B828" t="s">
-        <v>1639</v>
+        <v>1635</v>
       </c>
       <c r="C828" t="s">
-        <v>1662</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="829" spans="1:3" x14ac:dyDescent="0.3">
@@ -18249,10 +18257,10 @@
         <v>828</v>
       </c>
       <c r="B829" t="s">
-        <v>1640</v>
+        <v>1636</v>
       </c>
       <c r="C829" t="s">
-        <v>1663</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="830" spans="1:3" x14ac:dyDescent="0.3">
@@ -18260,10 +18268,10 @@
         <v>829</v>
       </c>
       <c r="B830" t="s">
-        <v>1641</v>
+        <v>1637</v>
       </c>
       <c r="C830" t="s">
-        <v>1664</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="831" spans="1:3" x14ac:dyDescent="0.3">
@@ -18271,10 +18279,10 @@
         <v>830</v>
       </c>
       <c r="B831" t="s">
-        <v>1642</v>
+        <v>1638</v>
       </c>
       <c r="C831" t="s">
-        <v>1665</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="832" spans="1:3" x14ac:dyDescent="0.3">
@@ -18282,10 +18290,10 @@
         <v>831</v>
       </c>
       <c r="B832" t="s">
-        <v>1643</v>
+        <v>1639</v>
       </c>
       <c r="C832" t="s">
-        <v>1666</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="833" spans="1:3" x14ac:dyDescent="0.3">
@@ -18293,10 +18301,10 @@
         <v>832</v>
       </c>
       <c r="B833" t="s">
-        <v>1644</v>
+        <v>1640</v>
       </c>
       <c r="C833" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="834" spans="1:3" x14ac:dyDescent="0.3">
@@ -18304,10 +18312,10 @@
         <v>833</v>
       </c>
       <c r="B834" t="s">
-        <v>1645</v>
+        <v>1641</v>
       </c>
       <c r="C834" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="835" spans="1:3" x14ac:dyDescent="0.3">
@@ -18315,10 +18323,10 @@
         <v>834</v>
       </c>
       <c r="B835" t="s">
-        <v>1646</v>
+        <v>1642</v>
       </c>
       <c r="C835" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="836" spans="1:3" x14ac:dyDescent="0.3">
@@ -18326,10 +18334,10 @@
         <v>835</v>
       </c>
       <c r="B836" t="s">
-        <v>1647</v>
+        <v>1643</v>
       </c>
       <c r="C836" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="837" spans="1:3" x14ac:dyDescent="0.3">
@@ -18337,10 +18345,10 @@
         <v>836</v>
       </c>
       <c r="B837" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="C837" t="s">
-        <v>1698</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.3">
@@ -18348,10 +18356,10 @@
         <v>837</v>
       </c>
       <c r="B838" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="C838" t="s">
-        <v>1699</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="839" spans="1:3" x14ac:dyDescent="0.3">
@@ -18359,10 +18367,10 @@
         <v>838</v>
       </c>
       <c r="B839" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="C839" t="s">
-        <v>1700</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="840" spans="1:3" x14ac:dyDescent="0.3">
@@ -18370,10 +18378,10 @@
         <v>839</v>
       </c>
       <c r="B840" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="C840" t="s">
-        <v>1701</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="841" spans="1:3" x14ac:dyDescent="0.3">
@@ -18381,10 +18389,10 @@
         <v>840</v>
       </c>
       <c r="B841" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="C841" t="s">
-        <v>1702</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="842" spans="1:3" x14ac:dyDescent="0.3">
@@ -18392,10 +18400,10 @@
         <v>841</v>
       </c>
       <c r="B842" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="C842" t="s">
-        <v>1733</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="843" spans="1:3" x14ac:dyDescent="0.3">
@@ -18403,7 +18411,7 @@
         <v>842</v>
       </c>
       <c r="B843" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="C843" t="s">
         <v>1049</v>
@@ -18414,10 +18422,10 @@
         <v>843</v>
       </c>
       <c r="B844" t="s">
-        <v>1679</v>
+        <v>1675</v>
       </c>
       <c r="C844" t="s">
-        <v>1720</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="845" spans="1:3" x14ac:dyDescent="0.3">
@@ -18425,10 +18433,10 @@
         <v>844</v>
       </c>
       <c r="B845" t="s">
-        <v>1680</v>
+        <v>1676</v>
       </c>
       <c r="C845" t="s">
-        <v>1703</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="846" spans="1:3" x14ac:dyDescent="0.3">
@@ -18436,10 +18444,10 @@
         <v>845</v>
       </c>
       <c r="B846" t="s">
-        <v>1681</v>
+        <v>1677</v>
       </c>
       <c r="C846" t="s">
-        <v>1704</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="847" spans="1:3" x14ac:dyDescent="0.3">
@@ -18447,10 +18455,10 @@
         <v>846</v>
       </c>
       <c r="B847" t="s">
-        <v>1682</v>
+        <v>1678</v>
       </c>
       <c r="C847" t="s">
-        <v>1705</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="848" spans="1:3" x14ac:dyDescent="0.3">
@@ -18458,10 +18466,10 @@
         <v>847</v>
       </c>
       <c r="B848" t="s">
-        <v>1683</v>
+        <v>1679</v>
       </c>
       <c r="C848" t="s">
-        <v>1706</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.3">
@@ -18469,10 +18477,10 @@
         <v>848</v>
       </c>
       <c r="B849" t="s">
-        <v>1684</v>
+        <v>1680</v>
       </c>
       <c r="C849" t="s">
-        <v>1707</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="850" spans="1:3" x14ac:dyDescent="0.3">
@@ -18480,10 +18488,10 @@
         <v>849</v>
       </c>
       <c r="B850" t="s">
-        <v>1685</v>
+        <v>1681</v>
       </c>
       <c r="C850" t="s">
-        <v>1708</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="851" spans="1:3" x14ac:dyDescent="0.3">
@@ -18491,10 +18499,10 @@
         <v>850</v>
       </c>
       <c r="B851" t="s">
-        <v>1686</v>
+        <v>1682</v>
       </c>
       <c r="C851" t="s">
-        <v>1709</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="852" spans="1:3" x14ac:dyDescent="0.3">
@@ -18502,10 +18510,10 @@
         <v>851</v>
       </c>
       <c r="B852" t="s">
-        <v>1687</v>
+        <v>1683</v>
       </c>
       <c r="C852" t="s">
-        <v>1708</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="853" spans="1:3" x14ac:dyDescent="0.3">
@@ -18513,10 +18521,10 @@
         <v>852</v>
       </c>
       <c r="B853" t="s">
-        <v>1688</v>
+        <v>1684</v>
       </c>
       <c r="C853" t="s">
-        <v>1710</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="854" spans="1:3" x14ac:dyDescent="0.3">
@@ -18524,10 +18532,10 @@
         <v>853</v>
       </c>
       <c r="B854" t="s">
-        <v>1689</v>
+        <v>1685</v>
       </c>
       <c r="C854" t="s">
-        <v>1711</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="855" spans="1:3" x14ac:dyDescent="0.3">
@@ -18535,10 +18543,10 @@
         <v>854</v>
       </c>
       <c r="B855" t="s">
-        <v>1690</v>
+        <v>1686</v>
       </c>
       <c r="C855" t="s">
-        <v>1712</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="856" spans="1:3" x14ac:dyDescent="0.3">
@@ -18546,10 +18554,10 @@
         <v>855</v>
       </c>
       <c r="B856" t="s">
-        <v>1691</v>
+        <v>1687</v>
       </c>
       <c r="C856" t="s">
-        <v>1713</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="857" spans="1:3" x14ac:dyDescent="0.3">
@@ -18557,10 +18565,10 @@
         <v>856</v>
       </c>
       <c r="B857" t="s">
-        <v>1692</v>
+        <v>1688</v>
       </c>
       <c r="C857" t="s">
-        <v>1714</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="858" spans="1:3" x14ac:dyDescent="0.3">
@@ -18568,10 +18576,10 @@
         <v>857</v>
       </c>
       <c r="B858" t="s">
-        <v>1693</v>
+        <v>1689</v>
       </c>
       <c r="C858" t="s">
-        <v>1715</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="859" spans="1:3" x14ac:dyDescent="0.3">
@@ -18579,10 +18587,10 @@
         <v>858</v>
       </c>
       <c r="B859" t="s">
-        <v>1694</v>
+        <v>1690</v>
       </c>
       <c r="C859" t="s">
-        <v>1716</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.3">
@@ -18590,10 +18598,10 @@
         <v>859</v>
       </c>
       <c r="B860" t="s">
-        <v>1695</v>
+        <v>1691</v>
       </c>
       <c r="C860" t="s">
-        <v>1717</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="861" spans="1:3" x14ac:dyDescent="0.3">
@@ -18601,10 +18609,10 @@
         <v>860</v>
       </c>
       <c r="B861" t="s">
-        <v>1696</v>
+        <v>1692</v>
       </c>
       <c r="C861" t="s">
-        <v>1718</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="862" spans="1:3" x14ac:dyDescent="0.3">
@@ -18612,10 +18620,10 @@
         <v>861</v>
       </c>
       <c r="B862" t="s">
-        <v>1697</v>
+        <v>1693</v>
       </c>
       <c r="C862" t="s">
-        <v>1719</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="863" spans="1:3" x14ac:dyDescent="0.3">
@@ -18623,10 +18631,10 @@
         <v>862</v>
       </c>
       <c r="B863" t="s">
-        <v>1721</v>
+        <v>1717</v>
       </c>
       <c r="C863" t="s">
-        <v>1727</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="864" spans="1:3" x14ac:dyDescent="0.3">
@@ -18634,10 +18642,10 @@
         <v>863</v>
       </c>
       <c r="B864" t="s">
-        <v>1722</v>
+        <v>1718</v>
       </c>
       <c r="C864" t="s">
-        <v>1728</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="865" spans="1:3" x14ac:dyDescent="0.3">
@@ -18645,10 +18653,10 @@
         <v>864</v>
       </c>
       <c r="B865" t="s">
-        <v>1723</v>
+        <v>1719</v>
       </c>
       <c r="C865" t="s">
-        <v>1729</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="866" spans="1:3" x14ac:dyDescent="0.3">
@@ -18656,10 +18664,10 @@
         <v>865</v>
       </c>
       <c r="B866" t="s">
-        <v>1724</v>
+        <v>1720</v>
       </c>
       <c r="C866" t="s">
-        <v>1729</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="867" spans="1:3" x14ac:dyDescent="0.3">
@@ -18667,10 +18675,10 @@
         <v>866</v>
       </c>
       <c r="B867" t="s">
+        <v>1722</v>
+      </c>
+      <c r="C867" t="s">
         <v>1726</v>
-      </c>
-      <c r="C867" t="s">
-        <v>1730</v>
       </c>
     </row>
     <row r="868" spans="1:3" x14ac:dyDescent="0.3">
@@ -18678,10 +18686,21 @@
         <v>867</v>
       </c>
       <c r="B868" t="s">
-        <v>1725</v>
+        <v>1721</v>
       </c>
       <c r="C868" t="s">
-        <v>1731</v>
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="869" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A869">
+        <v>868</v>
+      </c>
+      <c r="B869" t="s">
+        <v>1732</v>
+      </c>
+      <c r="C869" t="s">
+        <v>1733</v>
       </c>
     </row>
   </sheetData>

--- a/30_table/01_테스트버전/Table_STR_String.xlsx
+++ b/30_table/01_테스트버전/Table_STR_String.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="1738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1839" uniqueCount="1797">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5824,9 +5824,6 @@
     <t>지하 2층으로 이동하세요</t>
   </si>
   <si>
-    <t>화염을 피해 다음 지역으로 이동하세요</t>
-  </si>
-  <si>
     <t>구울을 피해 다음 지역으로 이동하세요.</t>
   </si>
   <si>
@@ -5943,6 +5940,222 @@
   <si>
     <t>문의 또는 오류 신고</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영혼수집가 라미</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20026_01</t>
+  </si>
+  <si>
+    <t>이 위험한 곳까지 오다니 대단하군요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한가지 부탁을 드려도 될까요?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저는 죽은 자의 영혼을 모으고 있는데,</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좀비의 영혼을 아직 모으지 못했어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>혹시 좀비의 영혼을 가져다 주실 수 있으신가요?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20026_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20026_03</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20026_04</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20026_05</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20027_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>벌써 구해 오신건가요?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정말 대단하군요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이게 좀비의 영혼인가요?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>왠지 쓸쓸한 기운이 느껴지네요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅님 덕분에 이제 이 영혼도 안식을 찾을 수 있겠군요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>감사합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20027_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20027_03</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20027_04</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20027_05</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20027_06</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20028_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>샹그리라를 찾는다구요?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>글쎄요, 저는 잘 모르겠군요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하지만 서큐버스가 무언가를 지키는 것 같더군요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>혹시 거기에 단서가 있을지도…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서큐버스는 좀 더 깊은 곳에 있다고 하더군요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아까 영혼을 모으러 갔던 곳을 지나면 만날 수 있을꺼에요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>위험한 몬스터이니 조심하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20028_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20028_03</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20028_04</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20028_05</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20028_06</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20028_07</t>
+  </si>
+  <si>
+    <t>STR_ITEM_QUEST_02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좀비의 영혼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_ITEM_QUEST_02_DESC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한이 서려있는 좀비의 영혼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_NPC_N_0026</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좀비의 영혼은 아직인가요?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>역시나 어려운 부탁있군요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20029_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20029_02</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_027</t>
+  </si>
+  <si>
+    <t>STR_MAP_S4_027_DESC</t>
+  </si>
+  <si>
+    <t>비밀 서고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제단 앞으로 이동 하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_NPC_N_0030</t>
+  </si>
+  <si>
+    <t>오래된 책</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20030_01</t>
+  </si>
+  <si>
+    <t>마법에 사용되는 듯한 도형과 알 수 없는 문자…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>페이지가 찢어져 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>리바이???</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일단 이 사람에 대해 조사해 보자.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20030_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20030_03</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20030_04</t>
   </si>
 </sst>
 </file>
@@ -9129,7 +9342,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E869"/>
+  <dimension ref="A1:E899"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="33" bestFit="1" customWidth="1"/>
@@ -16137,7 +16350,7 @@
         <v>1297</v>
       </c>
       <c r="C636" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.3">
@@ -17226,7 +17439,7 @@
         <v>1409</v>
       </c>
       <c r="C735" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="736" spans="1:3" x14ac:dyDescent="0.3">
@@ -17237,7 +17450,7 @@
         <v>1410</v>
       </c>
       <c r="C736" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="737" spans="1:3" x14ac:dyDescent="0.3">
@@ -17248,7 +17461,7 @@
         <v>1411</v>
       </c>
       <c r="C737" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="738" spans="1:3" x14ac:dyDescent="0.3">
@@ -17259,7 +17472,7 @@
         <v>1412</v>
       </c>
       <c r="C738" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.3">
@@ -18117,7 +18330,7 @@
         <v>1623</v>
       </c>
       <c r="C816" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="817" spans="1:3" x14ac:dyDescent="0.3">
@@ -18128,7 +18341,7 @@
         <v>1624</v>
       </c>
       <c r="C817" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="818" spans="1:3" x14ac:dyDescent="0.3">
@@ -18337,7 +18550,7 @@
         <v>1643</v>
       </c>
       <c r="C836" t="s">
-        <v>1667</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="837" spans="1:3" x14ac:dyDescent="0.3">
@@ -18345,10 +18558,10 @@
         <v>836</v>
       </c>
       <c r="B837" t="s">
-        <v>1668</v>
+        <v>1783</v>
       </c>
       <c r="C837" t="s">
-        <v>1694</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.3">
@@ -18356,10 +18569,10 @@
         <v>837</v>
       </c>
       <c r="B838" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="C838" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="839" spans="1:3" x14ac:dyDescent="0.3">
@@ -18367,10 +18580,10 @@
         <v>838</v>
       </c>
       <c r="B839" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="C839" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="840" spans="1:3" x14ac:dyDescent="0.3">
@@ -18378,10 +18591,10 @@
         <v>839</v>
       </c>
       <c r="B840" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="C840" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="841" spans="1:3" x14ac:dyDescent="0.3">
@@ -18389,10 +18602,10 @@
         <v>840</v>
       </c>
       <c r="B841" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="C841" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="842" spans="1:3" x14ac:dyDescent="0.3">
@@ -18400,10 +18613,10 @@
         <v>841</v>
       </c>
       <c r="B842" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="C842" t="s">
-        <v>1729</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="843" spans="1:3" x14ac:dyDescent="0.3">
@@ -18411,10 +18624,10 @@
         <v>842</v>
       </c>
       <c r="B843" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="C843" t="s">
-        <v>1049</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="844" spans="1:3" x14ac:dyDescent="0.3">
@@ -18422,10 +18635,10 @@
         <v>843</v>
       </c>
       <c r="B844" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="C844" t="s">
-        <v>1716</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="845" spans="1:3" x14ac:dyDescent="0.3">
@@ -18433,10 +18646,10 @@
         <v>844</v>
       </c>
       <c r="B845" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="C845" t="s">
-        <v>1699</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="846" spans="1:3" x14ac:dyDescent="0.3">
@@ -18444,10 +18657,10 @@
         <v>845</v>
       </c>
       <c r="B846" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="C846" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="847" spans="1:3" x14ac:dyDescent="0.3">
@@ -18455,10 +18668,10 @@
         <v>846</v>
       </c>
       <c r="B847" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="C847" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="848" spans="1:3" x14ac:dyDescent="0.3">
@@ -18466,10 +18679,10 @@
         <v>847</v>
       </c>
       <c r="B848" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="C848" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.3">
@@ -18477,7 +18690,7 @@
         <v>848</v>
       </c>
       <c r="B849" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="C849" t="s">
         <v>1703</v>
@@ -18488,10 +18701,10 @@
         <v>849</v>
       </c>
       <c r="B850" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="C850" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="851" spans="1:3" x14ac:dyDescent="0.3">
@@ -18499,10 +18712,10 @@
         <v>850</v>
       </c>
       <c r="B851" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="C851" t="s">
-        <v>1705</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="852" spans="1:3" x14ac:dyDescent="0.3">
@@ -18510,7 +18723,7 @@
         <v>851</v>
       </c>
       <c r="B852" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="C852" t="s">
         <v>1704</v>
@@ -18521,10 +18734,10 @@
         <v>852</v>
       </c>
       <c r="B853" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="C853" t="s">
-        <v>1706</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="854" spans="1:3" x14ac:dyDescent="0.3">
@@ -18532,10 +18745,10 @@
         <v>853</v>
       </c>
       <c r="B854" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="C854" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="855" spans="1:3" x14ac:dyDescent="0.3">
@@ -18543,10 +18756,10 @@
         <v>854</v>
       </c>
       <c r="B855" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="C855" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="856" spans="1:3" x14ac:dyDescent="0.3">
@@ -18554,10 +18767,10 @@
         <v>855</v>
       </c>
       <c r="B856" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="C856" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="857" spans="1:3" x14ac:dyDescent="0.3">
@@ -18565,10 +18778,10 @@
         <v>856</v>
       </c>
       <c r="B857" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="C857" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="858" spans="1:3" x14ac:dyDescent="0.3">
@@ -18576,10 +18789,10 @@
         <v>857</v>
       </c>
       <c r="B858" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="C858" t="s">
-        <v>1711</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="859" spans="1:3" x14ac:dyDescent="0.3">
@@ -18587,10 +18800,10 @@
         <v>858</v>
       </c>
       <c r="B859" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="C859" t="s">
-        <v>1712</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.3">
@@ -18598,10 +18811,10 @@
         <v>859</v>
       </c>
       <c r="B860" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="C860" t="s">
-        <v>1713</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="861" spans="1:3" x14ac:dyDescent="0.3">
@@ -18609,10 +18822,10 @@
         <v>860</v>
       </c>
       <c r="B861" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="C861" t="s">
-        <v>1714</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="862" spans="1:3" x14ac:dyDescent="0.3">
@@ -18620,10 +18833,10 @@
         <v>861</v>
       </c>
       <c r="B862" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="C862" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="863" spans="1:3" x14ac:dyDescent="0.3">
@@ -18631,10 +18844,10 @@
         <v>862</v>
       </c>
       <c r="B863" t="s">
-        <v>1717</v>
+        <v>1693</v>
       </c>
       <c r="C863" t="s">
-        <v>1723</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="864" spans="1:3" x14ac:dyDescent="0.3">
@@ -18642,10 +18855,10 @@
         <v>863</v>
       </c>
       <c r="B864" t="s">
-        <v>1718</v>
+        <v>1784</v>
       </c>
       <c r="C864" t="s">
-        <v>1724</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="865" spans="1:3" x14ac:dyDescent="0.3">
@@ -18653,10 +18866,10 @@
         <v>864</v>
       </c>
       <c r="B865" t="s">
-        <v>1719</v>
+        <v>1716</v>
       </c>
       <c r="C865" t="s">
-        <v>1725</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="866" spans="1:3" x14ac:dyDescent="0.3">
@@ -18664,10 +18877,10 @@
         <v>865</v>
       </c>
       <c r="B866" t="s">
-        <v>1720</v>
+        <v>1717</v>
       </c>
       <c r="C866" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="867" spans="1:3" x14ac:dyDescent="0.3">
@@ -18675,10 +18888,10 @@
         <v>866</v>
       </c>
       <c r="B867" t="s">
-        <v>1722</v>
+        <v>1718</v>
       </c>
       <c r="C867" t="s">
-        <v>1726</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="868" spans="1:3" x14ac:dyDescent="0.3">
@@ -18686,10 +18899,10 @@
         <v>867</v>
       </c>
       <c r="B868" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="C868" t="s">
-        <v>1727</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="869" spans="1:3" x14ac:dyDescent="0.3">
@@ -18697,10 +18910,340 @@
         <v>868</v>
       </c>
       <c r="B869" t="s">
+        <v>1721</v>
+      </c>
+      <c r="C869" t="s">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="870" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A870">
+        <v>869</v>
+      </c>
+      <c r="B870" t="s">
+        <v>1720</v>
+      </c>
+      <c r="C870" t="s">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="871" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A871">
+        <v>870</v>
+      </c>
+      <c r="B871" t="s">
+        <v>1731</v>
+      </c>
+      <c r="C871" t="s">
         <v>1732</v>
       </c>
-      <c r="C869" t="s">
-        <v>1733</v>
+    </row>
+    <row r="872" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A872">
+        <v>871</v>
+      </c>
+      <c r="B872" t="s">
+        <v>1778</v>
+      </c>
+      <c r="C872" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="873" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A873">
+        <v>872</v>
+      </c>
+      <c r="B873" t="s">
+        <v>1738</v>
+      </c>
+      <c r="C873" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="874" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A874">
+        <v>873</v>
+      </c>
+      <c r="B874" t="s">
+        <v>1744</v>
+      </c>
+      <c r="C874" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="875" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A875">
+        <v>874</v>
+      </c>
+      <c r="B875" t="s">
+        <v>1745</v>
+      </c>
+      <c r="C875" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="876" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A876">
+        <v>875</v>
+      </c>
+      <c r="B876" t="s">
+        <v>1746</v>
+      </c>
+      <c r="C876" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="877" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A877">
+        <v>876</v>
+      </c>
+      <c r="B877" t="s">
+        <v>1747</v>
+      </c>
+      <c r="C877" t="s">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="878" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A878">
+        <v>877</v>
+      </c>
+      <c r="B878" t="s">
+        <v>1748</v>
+      </c>
+      <c r="C878" t="s">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="879" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A879">
+        <v>878</v>
+      </c>
+      <c r="B879" t="s">
+        <v>1755</v>
+      </c>
+      <c r="C879" t="s">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="880" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A880">
+        <v>879</v>
+      </c>
+      <c r="B880" t="s">
+        <v>1756</v>
+      </c>
+      <c r="C880" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="881" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A881">
+        <v>880</v>
+      </c>
+      <c r="B881" t="s">
+        <v>1757</v>
+      </c>
+      <c r="C881" t="s">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="882" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A882">
+        <v>881</v>
+      </c>
+      <c r="B882" t="s">
+        <v>1758</v>
+      </c>
+      <c r="C882" t="s">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="883" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A883">
+        <v>882</v>
+      </c>
+      <c r="B883" t="s">
+        <v>1759</v>
+      </c>
+      <c r="C883" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="884" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A884">
+        <v>883</v>
+      </c>
+      <c r="B884" t="s">
+        <v>1760</v>
+      </c>
+      <c r="C884" t="s">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="885" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A885">
+        <v>884</v>
+      </c>
+      <c r="B885" t="s">
+        <v>1768</v>
+      </c>
+      <c r="C885" t="s">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="886" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A886">
+        <v>885</v>
+      </c>
+      <c r="B886" t="s">
+        <v>1769</v>
+      </c>
+      <c r="C886" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="887" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A887">
+        <v>886</v>
+      </c>
+      <c r="B887" t="s">
+        <v>1770</v>
+      </c>
+      <c r="C887" t="s">
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="888" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A888">
+        <v>887</v>
+      </c>
+      <c r="B888" t="s">
+        <v>1771</v>
+      </c>
+      <c r="C888" t="s">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="889" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A889">
+        <v>888</v>
+      </c>
+      <c r="B889" t="s">
+        <v>1772</v>
+      </c>
+      <c r="C889" t="s">
+        <v>1766</v>
+      </c>
+    </row>
+    <row r="890" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A890">
+        <v>889</v>
+      </c>
+      <c r="B890" t="s">
+        <v>1773</v>
+      </c>
+      <c r="C890" t="s">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="891" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A891">
+        <v>890</v>
+      </c>
+      <c r="B891" t="s">
+        <v>1774</v>
+      </c>
+      <c r="C891" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="892" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A892">
+        <v>891</v>
+      </c>
+      <c r="B892" t="s">
+        <v>1776</v>
+      </c>
+      <c r="C892" t="s">
+        <v>1777</v>
+      </c>
+    </row>
+    <row r="893" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A893">
+        <v>892</v>
+      </c>
+      <c r="B893" t="s">
+        <v>1781</v>
+      </c>
+      <c r="C893" t="s">
+        <v>1779</v>
+      </c>
+    </row>
+    <row r="894" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A894">
+        <v>893</v>
+      </c>
+      <c r="B894" t="s">
+        <v>1782</v>
+      </c>
+      <c r="C894" t="s">
+        <v>1780</v>
+      </c>
+    </row>
+    <row r="895" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A895">
+        <v>894</v>
+      </c>
+      <c r="B895" t="s">
+        <v>1787</v>
+      </c>
+      <c r="C895" t="s">
+        <v>1788</v>
+      </c>
+    </row>
+    <row r="896" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A896">
+        <v>895</v>
+      </c>
+      <c r="B896" t="s">
+        <v>1789</v>
+      </c>
+      <c r="C896" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="897" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A897">
+        <v>896</v>
+      </c>
+      <c r="B897" t="s">
+        <v>1794</v>
+      </c>
+      <c r="C897" t="s">
+        <v>1791</v>
+      </c>
+    </row>
+    <row r="898" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A898">
+        <v>897</v>
+      </c>
+      <c r="B898" t="s">
+        <v>1795</v>
+      </c>
+      <c r="C898" t="s">
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="899" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A899">
+        <v>898</v>
+      </c>
+      <c r="B899" t="s">
+        <v>1796</v>
+      </c>
+      <c r="C899" t="s">
+        <v>1793</v>
       </c>
     </row>
   </sheetData>

--- a/30_table/01_테스트버전/Table_STR_String.xlsx
+++ b/30_table/01_테스트버전/Table_STR_String.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1843" uniqueCount="1804">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1863" uniqueCount="1824">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -6201,6 +6201,77 @@
   </si>
   <si>
     <t>빛나는 철 장화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_TIP_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_TIP_2</t>
+  </si>
+  <si>
+    <t>STR_TIP_3</t>
+  </si>
+  <si>
+    <t>STR_TIP_4</t>
+  </si>
+  <si>
+    <t>STR_TIP_5</t>
+  </si>
+  <si>
+    <t>STR_TIP_6</t>
+  </si>
+  <si>
+    <t>STR_TIP_7</t>
+  </si>
+  <si>
+    <t>STR_TIP_8</t>
+  </si>
+  <si>
+    <t>STR_TIP_9</t>
+  </si>
+  <si>
+    <t>STR_TIP_10</t>
+  </si>
+  <si>
+    <t>게임 팁: 하단 메뉴는 화살표 버튼을 누르거나, 드레그 하면 다음 메뉴를 볼 수 있습니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임 팁: 문의나 오류 신고는 하단 메뉴의 오류 버튼을 눌러 주세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임 팁: 회원 등급이 높으면 구매할 수 있는 상품이 증가합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임 팁: 각성을 하면 캐릭터의 능력치를 높일 수 있습니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임 팁: 환생을 하면 캐릭터의 등급을 낮출 수 있습니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임 팁: 강화를 하면 장비의 능력치를 높일 수 있습니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임 팁: 강화는 +99까지 가능합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임 팁: 강화 시 +4부터는 실패할 수 있습니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임 팁: 가방이 부족하면 가방을 확장해 보세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임 팁: 영웅 슬롯이 부족하면 +버튼을 누르면 확장할 수 있습니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -9388,7 +9459,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E901"/>
+  <dimension ref="A1:E911"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="33" bestFit="1" customWidth="1"/>
@@ -19314,6 +19385,116 @@
         <v>1779</v>
       </c>
     </row>
+    <row r="902" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A902">
+        <v>901</v>
+      </c>
+      <c r="B902" t="s">
+        <v>1804</v>
+      </c>
+      <c r="C902" t="s">
+        <v>1814</v>
+      </c>
+    </row>
+    <row r="903" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A903">
+        <v>902</v>
+      </c>
+      <c r="B903" t="s">
+        <v>1805</v>
+      </c>
+      <c r="C903" t="s">
+        <v>1815</v>
+      </c>
+    </row>
+    <row r="904" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A904">
+        <v>903</v>
+      </c>
+      <c r="B904" t="s">
+        <v>1806</v>
+      </c>
+      <c r="C904" t="s">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="905" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A905">
+        <v>904</v>
+      </c>
+      <c r="B905" t="s">
+        <v>1807</v>
+      </c>
+      <c r="C905" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="906" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A906">
+        <v>905</v>
+      </c>
+      <c r="B906" t="s">
+        <v>1808</v>
+      </c>
+      <c r="C906" t="s">
+        <v>1818</v>
+      </c>
+    </row>
+    <row r="907" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A907">
+        <v>906</v>
+      </c>
+      <c r="B907" t="s">
+        <v>1809</v>
+      </c>
+      <c r="C907" t="s">
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="908" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A908">
+        <v>907</v>
+      </c>
+      <c r="B908" t="s">
+        <v>1810</v>
+      </c>
+      <c r="C908" t="s">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="909" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A909">
+        <v>908</v>
+      </c>
+      <c r="B909" t="s">
+        <v>1811</v>
+      </c>
+      <c r="C909" t="s">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="910" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A910">
+        <v>909</v>
+      </c>
+      <c r="B910" t="s">
+        <v>1812</v>
+      </c>
+      <c r="C910" t="s">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="911" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A911">
+        <v>910</v>
+      </c>
+      <c r="B911" t="s">
+        <v>1813</v>
+      </c>
+      <c r="C911" t="s">
+        <v>1823</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/30_table/01_테스트버전/Table_STR_String.xlsx
+++ b/30_table/01_테스트버전/Table_STR_String.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3795" uniqueCount="1880">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4259" uniqueCount="2092">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -6483,6 +6483,642 @@
   <si>
     <t>STR_MSG_CHA_ENCHANT_1</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_MAP_S5_001</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_002</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_003</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_004</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_005</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_006</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_007</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_008</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_009</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_010</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_011</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_012</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_013</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_014</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_015</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_016</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_017</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_018</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_019</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_020</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_021</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_022</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_023</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_024</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_025</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_026</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_027</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_028</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_029</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_030</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_031</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_032</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_001</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_002</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_003</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_004</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_005</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_006</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_007</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_008</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_009</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_010</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_011</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_012</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_013</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_014</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_015</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_016</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_017</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_018</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_019</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_020</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_021</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_022</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_023</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_024</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_025</t>
+  </si>
+  <si>
+    <t>STR_MAP_S0_001</t>
+  </si>
+  <si>
+    <t>민병대원 마르코</t>
+  </si>
+  <si>
+    <t>고고학자</t>
+  </si>
+  <si>
+    <t>마법 연구소</t>
+  </si>
+  <si>
+    <t>마법사 작클레</t>
+  </si>
+  <si>
+    <t>여관으로</t>
+  </si>
+  <si>
+    <t>여관 주인 줄리아</t>
+  </si>
+  <si>
+    <t>작클레의 호출</t>
+  </si>
+  <si>
+    <t>마법 연구소로</t>
+  </si>
+  <si>
+    <t>리바이의 서의 비밀 1</t>
+  </si>
+  <si>
+    <t>광물 조합으로</t>
+  </si>
+  <si>
+    <t>빈 집으로</t>
+  </si>
+  <si>
+    <t>빈집털이</t>
+  </si>
+  <si>
+    <t>파머의 고민</t>
+  </si>
+  <si>
+    <t>호박 수확</t>
+  </si>
+  <si>
+    <t>파머에게 줄 선물</t>
+  </si>
+  <si>
+    <t>광물 조합</t>
+  </si>
+  <si>
+    <t>광물 조합장 코퍼</t>
+  </si>
+  <si>
+    <t>리바이의 서의 비밀 2</t>
+  </si>
+  <si>
+    <t>귀신 퇴치</t>
+  </si>
+  <si>
+    <t>도둑</t>
+  </si>
+  <si>
+    <t>귀신 퇴치 보고</t>
+  </si>
+  <si>
+    <t>그들이 노리는 것</t>
+  </si>
+  <si>
+    <t>광산 마을 서쪽으로</t>
+  </si>
+  <si>
+    <t>민병대원 산체스</t>
+  </si>
+  <si>
+    <t>황무지로</t>
+  </si>
+  <si>
+    <t>보물 창고로</t>
+  </si>
+  <si>
+    <t>보물 창고</t>
+  </si>
+  <si>
+    <t>얀센의 전언</t>
+  </si>
+  <si>
+    <t>광산 마을 남쪽으로</t>
+  </si>
+  <si>
+    <t>민병대원 카를로스</t>
+  </si>
+  <si>
+    <t>남쪽 숲으로</t>
+  </si>
+  <si>
+    <t>탐사 캠프로</t>
+  </si>
+  <si>
+    <t>황무지 탐사대</t>
+  </si>
+  <si>
+    <t>전갈 퇴치</t>
+  </si>
+  <si>
+    <t>전갈 퇴치 보고</t>
+  </si>
+  <si>
+    <t>유적지의 망령</t>
+  </si>
+  <si>
+    <t>유적지 조사</t>
+  </si>
+  <si>
+    <t>유적지 조사 보고</t>
+  </si>
+  <si>
+    <t>폐광 조사 의뢰</t>
+  </si>
+  <si>
+    <t>폐광 조사</t>
+  </si>
+  <si>
+    <t>폐광 조사 보고</t>
+  </si>
+  <si>
+    <t>지룡 안타라스</t>
+  </si>
+  <si>
+    <t>지룡의 둥지로 1</t>
+  </si>
+  <si>
+    <t>지룡의 둥지로 2</t>
+  </si>
+  <si>
+    <t>지룡 안타라스 퇴치</t>
+  </si>
+  <si>
+    <t>지룡 퇴치 보고</t>
+  </si>
+  <si>
+    <t>고대 유적</t>
+  </si>
+  <si>
+    <t>광산 마을로</t>
+  </si>
+  <si>
+    <t>지룡의 둥지로 3</t>
+  </si>
+  <si>
+    <t>지룡의 둥지로 4</t>
+  </si>
+  <si>
+    <t>안타라스의 보물</t>
+  </si>
+  <si>
+    <t>폐광으로</t>
+  </si>
+  <si>
+    <t>폐광 입구</t>
+  </si>
+  <si>
+    <t>묘지로</t>
+  </si>
+  <si>
+    <t>만든 사람들</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_001_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_002_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_003_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_004_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_005_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_006_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_007_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_008_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_009_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_010_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_011_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_012_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_013_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_014_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_015_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_016_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_017_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_018_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_019_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_020_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_021_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_022_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_023_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_024_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_025_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_026_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_027_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_028_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_029_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_030_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_031_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S5_032_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_001_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_002_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_003_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_004_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_005_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_006_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_007_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_008_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_009_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_010_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_011_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_012_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_013_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_014_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_015_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_016_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_017_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_018_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_019_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_020_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_021_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_022_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_023_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_024_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S6_025_DESC</t>
+  </si>
+  <si>
+    <t>STR_MAP_S0_001_DESC</t>
+  </si>
+  <si>
+    <t>민병대원 마르코와 대화 하세요.</t>
+  </si>
+  <si>
+    <t>민병대원 마르코와 대화 하세요</t>
+  </si>
+  <si>
+    <t>마법 연구소로 이동 하세요</t>
+  </si>
+  <si>
+    <t>작클레와 대화 하세요.</t>
+  </si>
+  <si>
+    <t>광산마을 여관으로 이동 하세요.</t>
+  </si>
+  <si>
+    <t>줄리아와 대화 하세요.</t>
+  </si>
+  <si>
+    <t>줄리아와 대화 하세요</t>
+  </si>
+  <si>
+    <t>마법 연구소로 이동 하세요.</t>
+  </si>
+  <si>
+    <t>다음 지역으로 이동해 보세요</t>
+  </si>
+  <si>
+    <t>상자를 열어 골드주머니를 획득하세요.</t>
+  </si>
+  <si>
+    <t>파머에게 수확한 호박 1개를 전해 주세요.</t>
+  </si>
+  <si>
+    <t>광물 조합으로 들어가세요.</t>
+  </si>
+  <si>
+    <t>광물 조합장 코퍼와 대화 하세요.</t>
+  </si>
+  <si>
+    <t>황무지로 이동 하세요.</t>
+  </si>
+  <si>
+    <t>남쪽 숲으로 이동 하세요.</t>
+  </si>
+  <si>
+    <t>오른쪽에 있는 집으로 들어가세요.</t>
+  </si>
+  <si>
+    <t>파머와 대화 하세요.</t>
+  </si>
+  <si>
+    <t>호박 밭으로 가서 호박을 수확하세요.</t>
+  </si>
+  <si>
+    <t>광물 조합장 코퍼와 대화 하세요</t>
+  </si>
+  <si>
+    <t>묘지로 이동 하세요.</t>
+  </si>
+  <si>
+    <t>귀신을 처치 하세요.</t>
+  </si>
+  <si>
+    <t>광물 조합에서 나오는 도둑을 잡으세요.</t>
+  </si>
+  <si>
+    <t>광산 마을 서쪽으로 이동 하세요.</t>
+  </si>
+  <si>
+    <t>민병대원 산체스와 대화 하세요.</t>
+  </si>
+  <si>
+    <t>보물 창고로 들어 가세요.</t>
+  </si>
+  <si>
+    <t>광산 마을 남쪽으로 이동 하세요.</t>
+  </si>
+  <si>
+    <t>민병대원 카를로스와 대화 하세요.</t>
+  </si>
+  <si>
+    <t>탐사 캠프로 이동 하세요.</t>
+  </si>
+  <si>
+    <t>탐사대장 얀센과 대화 하세요.</t>
+  </si>
+  <si>
+    <t>전갈을 모두 처치 하세요.</t>
+  </si>
+  <si>
+    <t>유적지를 조사해 보세요.</t>
+  </si>
+  <si>
+    <t>탐사대장 얀센에게 점토판 1개를 가져다 주세요.</t>
+  </si>
+  <si>
+    <t>세 곳의 폐광 중 한 곳만 안전한 폐광입니다. 안전한 폐광을 찾으세요.</t>
+  </si>
+  <si>
+    <t>다음 지역으로 이동 하세요.</t>
+  </si>
+  <si>
+    <t>지룡의 둥지로 이동 하세요.</t>
+  </si>
+  <si>
+    <t>지룡 안타라스를 처치 하세요.</t>
+  </si>
+  <si>
+    <t>탐사대장 얀센에게 지룡의 비늘 1개를 가져다 주세요.</t>
+  </si>
+  <si>
+    <t>보물 창고로 이동 하세요.</t>
+  </si>
+  <si>
+    <t>보물 상자를 열어 보세요.</t>
+  </si>
+  <si>
+    <t>폐광으로 들어 가세요.</t>
+  </si>
+  <si>
+    <t>비석 앞으로 이동해 비석을 조사해 보세요.</t>
   </si>
 </sst>
 </file>
@@ -9669,7 +10305,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E939"/>
+  <dimension ref="A1:E1055"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="33" bestFit="1" customWidth="1"/>
@@ -25641,6 +26277,1978 @@
         <v>1874</v>
       </c>
     </row>
+    <row r="940" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A940">
+        <v>939</v>
+      </c>
+      <c r="B940" t="s">
+        <v>1880</v>
+      </c>
+      <c r="C940" t="s">
+        <v>1938</v>
+      </c>
+      <c r="D940" t="s">
+        <v>1938</v>
+      </c>
+      <c r="E940" t="s">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="941" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A941">
+        <v>940</v>
+      </c>
+      <c r="B941" t="s">
+        <v>1881</v>
+      </c>
+      <c r="C941" t="s">
+        <v>1939</v>
+      </c>
+      <c r="D941" t="s">
+        <v>1939</v>
+      </c>
+      <c r="E941" t="s">
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="942" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A942">
+        <v>941</v>
+      </c>
+      <c r="B942" t="s">
+        <v>1882</v>
+      </c>
+      <c r="C942" t="s">
+        <v>1940</v>
+      </c>
+      <c r="D942" t="s">
+        <v>1940</v>
+      </c>
+      <c r="E942" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="943" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A943">
+        <v>942</v>
+      </c>
+      <c r="B943" t="s">
+        <v>1883</v>
+      </c>
+      <c r="C943" t="s">
+        <v>1941</v>
+      </c>
+      <c r="D943" t="s">
+        <v>1941</v>
+      </c>
+      <c r="E943" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="944" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A944">
+        <v>943</v>
+      </c>
+      <c r="B944" t="s">
+        <v>1884</v>
+      </c>
+      <c r="C944" t="s">
+        <v>1942</v>
+      </c>
+      <c r="D944" t="s">
+        <v>1942</v>
+      </c>
+      <c r="E944" t="s">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="945" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A945">
+        <v>944</v>
+      </c>
+      <c r="B945" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C945" t="s">
+        <v>1943</v>
+      </c>
+      <c r="D945" t="s">
+        <v>1943</v>
+      </c>
+      <c r="E945" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="946" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A946">
+        <v>945</v>
+      </c>
+      <c r="B946" t="s">
+        <v>1886</v>
+      </c>
+      <c r="C946" t="s">
+        <v>1944</v>
+      </c>
+      <c r="D946" t="s">
+        <v>1944</v>
+      </c>
+      <c r="E946" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="947" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A947">
+        <v>946</v>
+      </c>
+      <c r="B947" t="s">
+        <v>1887</v>
+      </c>
+      <c r="C947" t="s">
+        <v>1945</v>
+      </c>
+      <c r="D947" t="s">
+        <v>1945</v>
+      </c>
+      <c r="E947" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="948" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A948">
+        <v>947</v>
+      </c>
+      <c r="B948" t="s">
+        <v>1888</v>
+      </c>
+      <c r="C948" t="s">
+        <v>1946</v>
+      </c>
+      <c r="D948" t="s">
+        <v>1946</v>
+      </c>
+      <c r="E948" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="949" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A949">
+        <v>948</v>
+      </c>
+      <c r="B949" t="s">
+        <v>1889</v>
+      </c>
+      <c r="C949" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D949" t="s">
+        <v>1947</v>
+      </c>
+      <c r="E949" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="950" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A950">
+        <v>949</v>
+      </c>
+      <c r="B950" t="s">
+        <v>1890</v>
+      </c>
+      <c r="C950" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D950" t="s">
+        <v>1948</v>
+      </c>
+      <c r="E950" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="951" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A951">
+        <v>950</v>
+      </c>
+      <c r="B951" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C951" t="s">
+        <v>1949</v>
+      </c>
+      <c r="D951" t="s">
+        <v>1949</v>
+      </c>
+      <c r="E951" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="952" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A952">
+        <v>951</v>
+      </c>
+      <c r="B952" t="s">
+        <v>1892</v>
+      </c>
+      <c r="C952" t="s">
+        <v>1950</v>
+      </c>
+      <c r="D952" t="s">
+        <v>1950</v>
+      </c>
+      <c r="E952" t="s">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="953" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A953">
+        <v>952</v>
+      </c>
+      <c r="B953" t="s">
+        <v>1893</v>
+      </c>
+      <c r="C953" t="s">
+        <v>1951</v>
+      </c>
+      <c r="D953" t="s">
+        <v>1951</v>
+      </c>
+      <c r="E953" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="954" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A954">
+        <v>953</v>
+      </c>
+      <c r="B954" t="s">
+        <v>1894</v>
+      </c>
+      <c r="C954" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D954" t="s">
+        <v>1952</v>
+      </c>
+      <c r="E954" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="955" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A955">
+        <v>954</v>
+      </c>
+      <c r="B955" t="s">
+        <v>1895</v>
+      </c>
+      <c r="C955" t="s">
+        <v>1953</v>
+      </c>
+      <c r="D955" t="s">
+        <v>1953</v>
+      </c>
+      <c r="E955" t="s">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="956" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A956">
+        <v>955</v>
+      </c>
+      <c r="B956" t="s">
+        <v>1896</v>
+      </c>
+      <c r="C956" t="s">
+        <v>1954</v>
+      </c>
+      <c r="D956" t="s">
+        <v>1954</v>
+      </c>
+      <c r="E956" t="s">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="957" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A957">
+        <v>956</v>
+      </c>
+      <c r="B957" t="s">
+        <v>1897</v>
+      </c>
+      <c r="C957" t="s">
+        <v>1955</v>
+      </c>
+      <c r="D957" t="s">
+        <v>1955</v>
+      </c>
+      <c r="E957" t="s">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="958" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A958">
+        <v>957</v>
+      </c>
+      <c r="B958" t="s">
+        <v>1898</v>
+      </c>
+      <c r="C958" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D958" t="s">
+        <v>1991</v>
+      </c>
+      <c r="E958" t="s">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="959" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A959">
+        <v>958</v>
+      </c>
+      <c r="B959" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C959" t="s">
+        <v>1956</v>
+      </c>
+      <c r="D959" t="s">
+        <v>1956</v>
+      </c>
+      <c r="E959" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="960" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A960">
+        <v>959</v>
+      </c>
+      <c r="B960" t="s">
+        <v>1900</v>
+      </c>
+      <c r="C960" t="s">
+        <v>1957</v>
+      </c>
+      <c r="D960" t="s">
+        <v>1957</v>
+      </c>
+      <c r="E960" t="s">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="961" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A961">
+        <v>960</v>
+      </c>
+      <c r="B961" t="s">
+        <v>1901</v>
+      </c>
+      <c r="C961" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D961" t="s">
+        <v>1958</v>
+      </c>
+      <c r="E961" t="s">
+        <v>1958</v>
+      </c>
+    </row>
+    <row r="962" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A962">
+        <v>961</v>
+      </c>
+      <c r="B962" t="s">
+        <v>1902</v>
+      </c>
+      <c r="C962" t="s">
+        <v>1959</v>
+      </c>
+      <c r="D962" t="s">
+        <v>1959</v>
+      </c>
+      <c r="E962" t="s">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="963" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A963">
+        <v>962</v>
+      </c>
+      <c r="B963" t="s">
+        <v>1903</v>
+      </c>
+      <c r="C963" t="s">
+        <v>1960</v>
+      </c>
+      <c r="D963" t="s">
+        <v>1960</v>
+      </c>
+      <c r="E963" t="s">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="964" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A964">
+        <v>963</v>
+      </c>
+      <c r="B964" t="s">
+        <v>1904</v>
+      </c>
+      <c r="C964" t="s">
+        <v>1961</v>
+      </c>
+      <c r="D964" t="s">
+        <v>1961</v>
+      </c>
+      <c r="E964" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="965" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A965">
+        <v>964</v>
+      </c>
+      <c r="B965" t="s">
+        <v>1905</v>
+      </c>
+      <c r="C965" t="s">
+        <v>1962</v>
+      </c>
+      <c r="D965" t="s">
+        <v>1962</v>
+      </c>
+      <c r="E965" t="s">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="966" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A966">
+        <v>965</v>
+      </c>
+      <c r="B966" t="s">
+        <v>1906</v>
+      </c>
+      <c r="C966" t="s">
+        <v>1963</v>
+      </c>
+      <c r="D966" t="s">
+        <v>1963</v>
+      </c>
+      <c r="E966" t="s">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="967" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A967">
+        <v>966</v>
+      </c>
+      <c r="B967" t="s">
+        <v>1907</v>
+      </c>
+      <c r="C967" t="s">
+        <v>1964</v>
+      </c>
+      <c r="D967" t="s">
+        <v>1964</v>
+      </c>
+      <c r="E967" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="968" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A968">
+        <v>967</v>
+      </c>
+      <c r="B968" t="s">
+        <v>1908</v>
+      </c>
+      <c r="C968" t="s">
+        <v>1965</v>
+      </c>
+      <c r="D968" t="s">
+        <v>1965</v>
+      </c>
+      <c r="E968" t="s">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="969" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A969">
+        <v>968</v>
+      </c>
+      <c r="B969" t="s">
+        <v>1909</v>
+      </c>
+      <c r="C969" t="s">
+        <v>1966</v>
+      </c>
+      <c r="D969" t="s">
+        <v>1966</v>
+      </c>
+      <c r="E969" t="s">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="970" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A970">
+        <v>969</v>
+      </c>
+      <c r="B970" t="s">
+        <v>1910</v>
+      </c>
+      <c r="C970" t="s">
+        <v>1967</v>
+      </c>
+      <c r="D970" t="s">
+        <v>1967</v>
+      </c>
+      <c r="E970" t="s">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="971" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A971">
+        <v>970</v>
+      </c>
+      <c r="B971" t="s">
+        <v>1911</v>
+      </c>
+      <c r="C971" t="s">
+        <v>1968</v>
+      </c>
+      <c r="D971" t="s">
+        <v>1968</v>
+      </c>
+      <c r="E971" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="972" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A972">
+        <v>971</v>
+      </c>
+      <c r="B972" t="s">
+        <v>1912</v>
+      </c>
+      <c r="C972" t="s">
+        <v>1969</v>
+      </c>
+      <c r="D972" t="s">
+        <v>1969</v>
+      </c>
+      <c r="E972" t="s">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="973" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A973">
+        <v>972</v>
+      </c>
+      <c r="B973" t="s">
+        <v>1913</v>
+      </c>
+      <c r="C973" t="s">
+        <v>1970</v>
+      </c>
+      <c r="D973" t="s">
+        <v>1970</v>
+      </c>
+      <c r="E973" t="s">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="974" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A974">
+        <v>973</v>
+      </c>
+      <c r="B974" t="s">
+        <v>1914</v>
+      </c>
+      <c r="C974" t="s">
+        <v>1971</v>
+      </c>
+      <c r="D974" t="s">
+        <v>1971</v>
+      </c>
+      <c r="E974" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="975" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A975">
+        <v>974</v>
+      </c>
+      <c r="B975" t="s">
+        <v>1915</v>
+      </c>
+      <c r="C975" t="s">
+        <v>1972</v>
+      </c>
+      <c r="D975" t="s">
+        <v>1972</v>
+      </c>
+      <c r="E975" t="s">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="976" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A976">
+        <v>975</v>
+      </c>
+      <c r="B976" t="s">
+        <v>1916</v>
+      </c>
+      <c r="C976" t="s">
+        <v>1973</v>
+      </c>
+      <c r="D976" t="s">
+        <v>1973</v>
+      </c>
+      <c r="E976" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="977" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A977">
+        <v>976</v>
+      </c>
+      <c r="B977" t="s">
+        <v>1917</v>
+      </c>
+      <c r="C977" t="s">
+        <v>1974</v>
+      </c>
+      <c r="D977" t="s">
+        <v>1974</v>
+      </c>
+      <c r="E977" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="978" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A978">
+        <v>977</v>
+      </c>
+      <c r="B978" t="s">
+        <v>1918</v>
+      </c>
+      <c r="C978" t="s">
+        <v>1975</v>
+      </c>
+      <c r="D978" t="s">
+        <v>1975</v>
+      </c>
+      <c r="E978" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="979" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A979">
+        <v>978</v>
+      </c>
+      <c r="B979" t="s">
+        <v>1919</v>
+      </c>
+      <c r="C979" t="s">
+        <v>1976</v>
+      </c>
+      <c r="D979" t="s">
+        <v>1976</v>
+      </c>
+      <c r="E979" t="s">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="980" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A980">
+        <v>979</v>
+      </c>
+      <c r="B980" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C980" t="s">
+        <v>1977</v>
+      </c>
+      <c r="D980" t="s">
+        <v>1977</v>
+      </c>
+      <c r="E980" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="981" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A981">
+        <v>980</v>
+      </c>
+      <c r="B981" t="s">
+        <v>1921</v>
+      </c>
+      <c r="C981" t="s">
+        <v>1978</v>
+      </c>
+      <c r="D981" t="s">
+        <v>1978</v>
+      </c>
+      <c r="E981" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="982" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A982">
+        <v>981</v>
+      </c>
+      <c r="B982" t="s">
+        <v>1922</v>
+      </c>
+      <c r="C982" t="s">
+        <v>1979</v>
+      </c>
+      <c r="D982" t="s">
+        <v>1979</v>
+      </c>
+      <c r="E982" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="983" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A983">
+        <v>982</v>
+      </c>
+      <c r="B983" t="s">
+        <v>1923</v>
+      </c>
+      <c r="C983" t="s">
+        <v>1980</v>
+      </c>
+      <c r="D983" t="s">
+        <v>1980</v>
+      </c>
+      <c r="E983" t="s">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="984" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A984">
+        <v>983</v>
+      </c>
+      <c r="B984" t="s">
+        <v>1924</v>
+      </c>
+      <c r="C984" t="s">
+        <v>1981</v>
+      </c>
+      <c r="D984" t="s">
+        <v>1981</v>
+      </c>
+      <c r="E984" t="s">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="985" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A985">
+        <v>984</v>
+      </c>
+      <c r="B985" t="s">
+        <v>1925</v>
+      </c>
+      <c r="C985" t="s">
+        <v>1982</v>
+      </c>
+      <c r="D985" t="s">
+        <v>1982</v>
+      </c>
+      <c r="E985" t="s">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="986" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A986">
+        <v>985</v>
+      </c>
+      <c r="B986" t="s">
+        <v>1926</v>
+      </c>
+      <c r="C986" t="s">
+        <v>1983</v>
+      </c>
+      <c r="D986" t="s">
+        <v>1983</v>
+      </c>
+      <c r="E986" t="s">
+        <v>1983</v>
+      </c>
+    </row>
+    <row r="987" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A987">
+        <v>986</v>
+      </c>
+      <c r="B987" t="s">
+        <v>1927</v>
+      </c>
+      <c r="C987" t="s">
+        <v>1984</v>
+      </c>
+      <c r="D987" t="s">
+        <v>1984</v>
+      </c>
+      <c r="E987" t="s">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="988" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A988">
+        <v>987</v>
+      </c>
+      <c r="B988" t="s">
+        <v>1928</v>
+      </c>
+      <c r="C988" t="s">
+        <v>1963</v>
+      </c>
+      <c r="D988" t="s">
+        <v>1963</v>
+      </c>
+      <c r="E988" t="s">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="989" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A989">
+        <v>988</v>
+      </c>
+      <c r="B989" t="s">
+        <v>1929</v>
+      </c>
+      <c r="C989" t="s">
+        <v>1964</v>
+      </c>
+      <c r="D989" t="s">
+        <v>1964</v>
+      </c>
+      <c r="E989" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="990" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A990">
+        <v>989</v>
+      </c>
+      <c r="B990" t="s">
+        <v>1930</v>
+      </c>
+      <c r="C990" t="s">
+        <v>1985</v>
+      </c>
+      <c r="D990" t="s">
+        <v>1985</v>
+      </c>
+      <c r="E990" t="s">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="991" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A991">
+        <v>990</v>
+      </c>
+      <c r="B991" t="s">
+        <v>1931</v>
+      </c>
+      <c r="C991" t="s">
+        <v>1986</v>
+      </c>
+      <c r="D991" t="s">
+        <v>1986</v>
+      </c>
+      <c r="E991" t="s">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="992" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A992">
+        <v>991</v>
+      </c>
+      <c r="B992" t="s">
+        <v>1932</v>
+      </c>
+      <c r="C992" t="s">
+        <v>1987</v>
+      </c>
+      <c r="D992" t="s">
+        <v>1987</v>
+      </c>
+      <c r="E992" t="s">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="993" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A993">
+        <v>992</v>
+      </c>
+      <c r="B993" t="s">
+        <v>1933</v>
+      </c>
+      <c r="C993" t="s">
+        <v>1988</v>
+      </c>
+      <c r="D993" t="s">
+        <v>1988</v>
+      </c>
+      <c r="E993" t="s">
+        <v>1988</v>
+      </c>
+    </row>
+    <row r="994" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A994">
+        <v>993</v>
+      </c>
+      <c r="B994" t="s">
+        <v>1934</v>
+      </c>
+      <c r="C994" t="s">
+        <v>1977</v>
+      </c>
+      <c r="D994" t="s">
+        <v>1977</v>
+      </c>
+      <c r="E994" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="995" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A995">
+        <v>994</v>
+      </c>
+      <c r="B995" t="s">
+        <v>1935</v>
+      </c>
+      <c r="C995" t="s">
+        <v>1989</v>
+      </c>
+      <c r="D995" t="s">
+        <v>1989</v>
+      </c>
+      <c r="E995" t="s">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="996" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A996">
+        <v>995</v>
+      </c>
+      <c r="B996" t="s">
+        <v>1936</v>
+      </c>
+      <c r="C996" t="s">
+        <v>1990</v>
+      </c>
+      <c r="D996" t="s">
+        <v>1990</v>
+      </c>
+      <c r="E996" t="s">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="997" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A997">
+        <v>996</v>
+      </c>
+      <c r="B997" t="s">
+        <v>1937</v>
+      </c>
+      <c r="C997" t="s">
+        <v>1992</v>
+      </c>
+      <c r="D997" t="s">
+        <v>1992</v>
+      </c>
+      <c r="E997" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="998" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A998">
+        <v>997</v>
+      </c>
+      <c r="B998" t="s">
+        <v>1993</v>
+      </c>
+      <c r="C998" t="s">
+        <v>2051</v>
+      </c>
+      <c r="D998" t="s">
+        <v>2051</v>
+      </c>
+      <c r="E998" t="s">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="999" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A999">
+        <v>998</v>
+      </c>
+      <c r="B999" t="s">
+        <v>1994</v>
+      </c>
+      <c r="C999" t="s">
+        <v>2052</v>
+      </c>
+      <c r="D999" t="s">
+        <v>2052</v>
+      </c>
+      <c r="E999" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1000">
+        <v>999</v>
+      </c>
+      <c r="B1000" t="s">
+        <v>1995</v>
+      </c>
+      <c r="C1000" t="s">
+        <v>2053</v>
+      </c>
+      <c r="D1000" t="s">
+        <v>2053</v>
+      </c>
+      <c r="E1000" t="s">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1001">
+        <v>1000</v>
+      </c>
+      <c r="B1001" t="s">
+        <v>1996</v>
+      </c>
+      <c r="C1001" t="s">
+        <v>2054</v>
+      </c>
+      <c r="D1001" t="s">
+        <v>2054</v>
+      </c>
+      <c r="E1001" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1002">
+        <v>1001</v>
+      </c>
+      <c r="B1002" t="s">
+        <v>1997</v>
+      </c>
+      <c r="C1002" t="s">
+        <v>2055</v>
+      </c>
+      <c r="D1002" t="s">
+        <v>2055</v>
+      </c>
+      <c r="E1002" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1003">
+        <v>1002</v>
+      </c>
+      <c r="B1003" t="s">
+        <v>1998</v>
+      </c>
+      <c r="C1003" t="s">
+        <v>2056</v>
+      </c>
+      <c r="D1003" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1003" t="s">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1004">
+        <v>1003</v>
+      </c>
+      <c r="B1004" t="s">
+        <v>1999</v>
+      </c>
+      <c r="C1004" t="s">
+        <v>2057</v>
+      </c>
+      <c r="D1004" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E1004" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1005">
+        <v>1004</v>
+      </c>
+      <c r="B1005" t="s">
+        <v>2000</v>
+      </c>
+      <c r="C1005" t="s">
+        <v>2058</v>
+      </c>
+      <c r="D1005" t="s">
+        <v>2058</v>
+      </c>
+      <c r="E1005" t="s">
+        <v>2058</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1006">
+        <v>1005</v>
+      </c>
+      <c r="B1006" t="s">
+        <v>2001</v>
+      </c>
+      <c r="C1006" t="s">
+        <v>2054</v>
+      </c>
+      <c r="D1006" t="s">
+        <v>2054</v>
+      </c>
+      <c r="E1006" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1007">
+        <v>1006</v>
+      </c>
+      <c r="B1007" t="s">
+        <v>2002</v>
+      </c>
+      <c r="C1007" t="s">
+        <v>2059</v>
+      </c>
+      <c r="D1007" t="s">
+        <v>2059</v>
+      </c>
+      <c r="E1007" t="s">
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1008">
+        <v>1007</v>
+      </c>
+      <c r="B1008" t="s">
+        <v>2003</v>
+      </c>
+      <c r="C1008" t="s">
+        <v>2066</v>
+      </c>
+      <c r="D1008" t="s">
+        <v>2066</v>
+      </c>
+      <c r="E1008" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1009">
+        <v>1008</v>
+      </c>
+      <c r="B1009" t="s">
+        <v>2004</v>
+      </c>
+      <c r="C1009" t="s">
+        <v>2060</v>
+      </c>
+      <c r="D1009" t="s">
+        <v>2060</v>
+      </c>
+      <c r="E1009" t="s">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1010">
+        <v>1009</v>
+      </c>
+      <c r="B1010" t="s">
+        <v>2005</v>
+      </c>
+      <c r="C1010" t="s">
+        <v>2067</v>
+      </c>
+      <c r="D1010" t="s">
+        <v>2067</v>
+      </c>
+      <c r="E1010" t="s">
+        <v>2067</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1011">
+        <v>1010</v>
+      </c>
+      <c r="B1011" t="s">
+        <v>2006</v>
+      </c>
+      <c r="C1011" t="s">
+        <v>2068</v>
+      </c>
+      <c r="D1011" t="s">
+        <v>2068</v>
+      </c>
+      <c r="E1011" t="s">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1012">
+        <v>1011</v>
+      </c>
+      <c r="B1012" t="s">
+        <v>2007</v>
+      </c>
+      <c r="C1012" t="s">
+        <v>2061</v>
+      </c>
+      <c r="D1012" t="s">
+        <v>2061</v>
+      </c>
+      <c r="E1012" t="s">
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1013">
+        <v>1012</v>
+      </c>
+      <c r="B1013" t="s">
+        <v>2008</v>
+      </c>
+      <c r="C1013" t="s">
+        <v>2062</v>
+      </c>
+      <c r="D1013" t="s">
+        <v>2062</v>
+      </c>
+      <c r="E1013" t="s">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1014">
+        <v>1013</v>
+      </c>
+      <c r="B1014" t="s">
+        <v>2009</v>
+      </c>
+      <c r="C1014" t="s">
+        <v>2063</v>
+      </c>
+      <c r="D1014" t="s">
+        <v>2063</v>
+      </c>
+      <c r="E1014" t="s">
+        <v>2063</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1015">
+        <v>1014</v>
+      </c>
+      <c r="B1015" t="s">
+        <v>2010</v>
+      </c>
+      <c r="C1015" t="s">
+        <v>2069</v>
+      </c>
+      <c r="D1015" t="s">
+        <v>2069</v>
+      </c>
+      <c r="E1015" t="s">
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1016">
+        <v>1015</v>
+      </c>
+      <c r="B1016" t="s">
+        <v>2011</v>
+      </c>
+      <c r="C1016" t="s">
+        <v>2070</v>
+      </c>
+      <c r="D1016" t="s">
+        <v>2070</v>
+      </c>
+      <c r="E1016" t="s">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1017">
+        <v>1016</v>
+      </c>
+      <c r="B1017" t="s">
+        <v>2012</v>
+      </c>
+      <c r="C1017" t="s">
+        <v>2071</v>
+      </c>
+      <c r="D1017" t="s">
+        <v>2071</v>
+      </c>
+      <c r="E1017" t="s">
+        <v>2071</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1018">
+        <v>1017</v>
+      </c>
+      <c r="B1018" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C1018" t="s">
+        <v>2072</v>
+      </c>
+      <c r="D1018" t="s">
+        <v>2072</v>
+      </c>
+      <c r="E1018" t="s">
+        <v>2072</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1019">
+        <v>1018</v>
+      </c>
+      <c r="B1019" t="s">
+        <v>2014</v>
+      </c>
+      <c r="C1019" t="s">
+        <v>2063</v>
+      </c>
+      <c r="D1019" t="s">
+        <v>2063</v>
+      </c>
+      <c r="E1019" t="s">
+        <v>2063</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1020">
+        <v>1019</v>
+      </c>
+      <c r="B1020" t="s">
+        <v>2015</v>
+      </c>
+      <c r="C1020" t="s">
+        <v>2063</v>
+      </c>
+      <c r="D1020" t="s">
+        <v>2063</v>
+      </c>
+      <c r="E1020" t="s">
+        <v>2063</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1021">
+        <v>1020</v>
+      </c>
+      <c r="B1021" t="s">
+        <v>2016</v>
+      </c>
+      <c r="C1021" t="s">
+        <v>2073</v>
+      </c>
+      <c r="D1021" t="s">
+        <v>2073</v>
+      </c>
+      <c r="E1021" t="s">
+        <v>2073</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1022">
+        <v>1021</v>
+      </c>
+      <c r="B1022" t="s">
+        <v>2017</v>
+      </c>
+      <c r="C1022" t="s">
+        <v>2074</v>
+      </c>
+      <c r="D1022" t="s">
+        <v>2074</v>
+      </c>
+      <c r="E1022" t="s">
+        <v>2074</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1023">
+        <v>1022</v>
+      </c>
+      <c r="B1023" t="s">
+        <v>2018</v>
+      </c>
+      <c r="C1023" t="s">
+        <v>2064</v>
+      </c>
+      <c r="D1023" t="s">
+        <v>2064</v>
+      </c>
+      <c r="E1023" t="s">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1024">
+        <v>1023</v>
+      </c>
+      <c r="B1024" t="s">
+        <v>2019</v>
+      </c>
+      <c r="C1024" t="s">
+        <v>2075</v>
+      </c>
+      <c r="D1024" t="s">
+        <v>2075</v>
+      </c>
+      <c r="E1024" t="s">
+        <v>2075</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1025">
+        <v>1024</v>
+      </c>
+      <c r="B1025" t="s">
+        <v>2020</v>
+      </c>
+      <c r="C1025" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D1025" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E1025" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1026">
+        <v>1025</v>
+      </c>
+      <c r="B1026" t="s">
+        <v>2021</v>
+      </c>
+      <c r="C1026" t="s">
+        <v>2054</v>
+      </c>
+      <c r="D1026" t="s">
+        <v>2054</v>
+      </c>
+      <c r="E1026" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1027">
+        <v>1026</v>
+      </c>
+      <c r="B1027" t="s">
+        <v>2022</v>
+      </c>
+      <c r="C1027" t="s">
+        <v>2076</v>
+      </c>
+      <c r="D1027" t="s">
+        <v>2076</v>
+      </c>
+      <c r="E1027" t="s">
+        <v>2076</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1028">
+        <v>1027</v>
+      </c>
+      <c r="B1028" t="s">
+        <v>2023</v>
+      </c>
+      <c r="C1028" t="s">
+        <v>2077</v>
+      </c>
+      <c r="D1028" t="s">
+        <v>2077</v>
+      </c>
+      <c r="E1028" t="s">
+        <v>2077</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1029">
+        <v>1028</v>
+      </c>
+      <c r="B1029" t="s">
+        <v>2024</v>
+      </c>
+      <c r="C1029" t="s">
+        <v>2065</v>
+      </c>
+      <c r="D1029" t="s">
+        <v>2065</v>
+      </c>
+      <c r="E1029" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1030">
+        <v>1029</v>
+      </c>
+      <c r="B1030" t="s">
+        <v>2025</v>
+      </c>
+      <c r="C1030" t="s">
+        <v>2078</v>
+      </c>
+      <c r="D1030" t="s">
+        <v>2078</v>
+      </c>
+      <c r="E1030" t="s">
+        <v>2078</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1031">
+        <v>1030</v>
+      </c>
+      <c r="B1031" t="s">
+        <v>2026</v>
+      </c>
+      <c r="C1031" t="s">
+        <v>2079</v>
+      </c>
+      <c r="D1031" t="s">
+        <v>2079</v>
+      </c>
+      <c r="E1031" t="s">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1032">
+        <v>1031</v>
+      </c>
+      <c r="B1032" t="s">
+        <v>2027</v>
+      </c>
+      <c r="C1032" t="s">
+        <v>2080</v>
+      </c>
+      <c r="D1032" t="s">
+        <v>2080</v>
+      </c>
+      <c r="E1032" t="s">
+        <v>2080</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1033">
+        <v>1032</v>
+      </c>
+      <c r="B1033" t="s">
+        <v>2028</v>
+      </c>
+      <c r="C1033" t="s">
+        <v>2079</v>
+      </c>
+      <c r="D1033" t="s">
+        <v>2079</v>
+      </c>
+      <c r="E1033" t="s">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1034">
+        <v>1033</v>
+      </c>
+      <c r="B1034" t="s">
+        <v>2029</v>
+      </c>
+      <c r="C1034" t="s">
+        <v>2079</v>
+      </c>
+      <c r="D1034" t="s">
+        <v>2079</v>
+      </c>
+      <c r="E1034" t="s">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1035">
+        <v>1034</v>
+      </c>
+      <c r="B1035" t="s">
+        <v>2030</v>
+      </c>
+      <c r="C1035" t="s">
+        <v>2081</v>
+      </c>
+      <c r="D1035" t="s">
+        <v>2081</v>
+      </c>
+      <c r="E1035" t="s">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1036">
+        <v>1035</v>
+      </c>
+      <c r="B1036" t="s">
+        <v>2031</v>
+      </c>
+      <c r="C1036" t="s">
+        <v>2082</v>
+      </c>
+      <c r="D1036" t="s">
+        <v>2082</v>
+      </c>
+      <c r="E1036" t="s">
+        <v>2082</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1037">
+        <v>1036</v>
+      </c>
+      <c r="B1037" t="s">
+        <v>2032</v>
+      </c>
+      <c r="C1037" t="s">
+        <v>2079</v>
+      </c>
+      <c r="D1037" t="s">
+        <v>2079</v>
+      </c>
+      <c r="E1037" t="s">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1038">
+        <v>1037</v>
+      </c>
+      <c r="B1038" t="s">
+        <v>2033</v>
+      </c>
+      <c r="C1038" t="s">
+        <v>2083</v>
+      </c>
+      <c r="D1038" t="s">
+        <v>2083</v>
+      </c>
+      <c r="E1038" t="s">
+        <v>2083</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1039">
+        <v>1038</v>
+      </c>
+      <c r="B1039" t="s">
+        <v>2034</v>
+      </c>
+      <c r="C1039" t="s">
+        <v>2079</v>
+      </c>
+      <c r="D1039" t="s">
+        <v>2079</v>
+      </c>
+      <c r="E1039" t="s">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1040">
+        <v>1039</v>
+      </c>
+      <c r="B1040" t="s">
+        <v>2035</v>
+      </c>
+      <c r="C1040" t="s">
+        <v>2079</v>
+      </c>
+      <c r="D1040" t="s">
+        <v>2079</v>
+      </c>
+      <c r="E1040" t="s">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1041">
+        <v>1040</v>
+      </c>
+      <c r="B1041" t="s">
+        <v>2036</v>
+      </c>
+      <c r="C1041" t="s">
+        <v>2084</v>
+      </c>
+      <c r="D1041" t="s">
+        <v>2084</v>
+      </c>
+      <c r="E1041" t="s">
+        <v>2084</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1042">
+        <v>1041</v>
+      </c>
+      <c r="B1042" t="s">
+        <v>2037</v>
+      </c>
+      <c r="C1042" t="s">
+        <v>2085</v>
+      </c>
+      <c r="D1042" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E1042" t="s">
+        <v>2085</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1043">
+        <v>1042</v>
+      </c>
+      <c r="B1043" t="s">
+        <v>2038</v>
+      </c>
+      <c r="C1043" t="s">
+        <v>2086</v>
+      </c>
+      <c r="D1043" t="s">
+        <v>2086</v>
+      </c>
+      <c r="E1043" t="s">
+        <v>2086</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1044">
+        <v>1043</v>
+      </c>
+      <c r="B1044" t="s">
+        <v>2039</v>
+      </c>
+      <c r="C1044" t="s">
+        <v>2087</v>
+      </c>
+      <c r="D1044" t="s">
+        <v>2087</v>
+      </c>
+      <c r="E1044" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1045">
+        <v>1044</v>
+      </c>
+      <c r="B1045" t="s">
+        <v>2040</v>
+      </c>
+      <c r="C1045" t="s">
+        <v>2079</v>
+      </c>
+      <c r="D1045" t="s">
+        <v>2079</v>
+      </c>
+      <c r="E1045" t="s">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1046">
+        <v>1045</v>
+      </c>
+      <c r="B1046" t="s">
+        <v>2041</v>
+      </c>
+      <c r="C1046" t="s">
+        <v>2088</v>
+      </c>
+      <c r="D1046" t="s">
+        <v>2088</v>
+      </c>
+      <c r="E1046" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1047">
+        <v>1046</v>
+      </c>
+      <c r="B1047" t="s">
+        <v>2042</v>
+      </c>
+      <c r="C1047" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D1047" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E1047" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1048">
+        <v>1047</v>
+      </c>
+      <c r="B1048" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C1048" t="s">
+        <v>2079</v>
+      </c>
+      <c r="D1048" t="s">
+        <v>2079</v>
+      </c>
+      <c r="E1048" t="s">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1049">
+        <v>1048</v>
+      </c>
+      <c r="B1049" t="s">
+        <v>2044</v>
+      </c>
+      <c r="C1049" t="s">
+        <v>2084</v>
+      </c>
+      <c r="D1049" t="s">
+        <v>2084</v>
+      </c>
+      <c r="E1049" t="s">
+        <v>2084</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1050">
+        <v>1049</v>
+      </c>
+      <c r="B1050" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1050" t="s">
+        <v>2085</v>
+      </c>
+      <c r="D1050" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E1050" t="s">
+        <v>2085</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1051">
+        <v>1050</v>
+      </c>
+      <c r="B1051" t="s">
+        <v>2046</v>
+      </c>
+      <c r="C1051" t="s">
+        <v>2089</v>
+      </c>
+      <c r="D1051" t="s">
+        <v>2089</v>
+      </c>
+      <c r="E1051" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1052">
+        <v>1051</v>
+      </c>
+      <c r="B1052" t="s">
+        <v>2047</v>
+      </c>
+      <c r="C1052" t="s">
+        <v>2079</v>
+      </c>
+      <c r="D1052" t="s">
+        <v>2079</v>
+      </c>
+      <c r="E1052" t="s">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1053">
+        <v>1052</v>
+      </c>
+      <c r="B1053" t="s">
+        <v>2048</v>
+      </c>
+      <c r="C1053" t="s">
+        <v>2084</v>
+      </c>
+      <c r="D1053" t="s">
+        <v>2084</v>
+      </c>
+      <c r="E1053" t="s">
+        <v>2084</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1054">
+        <v>1053</v>
+      </c>
+      <c r="B1054" t="s">
+        <v>2049</v>
+      </c>
+      <c r="C1054" t="s">
+        <v>2090</v>
+      </c>
+      <c r="D1054" t="s">
+        <v>2090</v>
+      </c>
+      <c r="E1054" t="s">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1055">
+        <v>1054</v>
+      </c>
+      <c r="B1055" t="s">
+        <v>2050</v>
+      </c>
+      <c r="C1055" t="s">
+        <v>2091</v>
+      </c>
+      <c r="D1055" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1055" t="s">
+        <v>2091</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/30_table/01_테스트버전/Table_STR_String.xlsx
+++ b/30_table/01_테스트버전/Table_STR_String.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4615" uniqueCount="2268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4655" uniqueCount="2288">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5424,10 +5424,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>개발실</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>생각보다 어렵지 않아요.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -7743,6 +7739,72 @@
   </si>
   <si>
     <t>묘지의 망령이 가지고 다니는 낫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_NPC_N_0051</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20051_01</t>
+  </si>
+  <si>
+    <t>[b][31bbf5]만든 사람들[-][/b]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20051_02</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20051_03</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20051_04</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20051_05</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20051_06</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20051_07</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20051_08</t>
+  </si>
+  <si>
+    <t>STR_STORY_NPC_20051_09</t>
+  </si>
+  <si>
+    <t>[b][31bbf5]제작[-][/b]\n\n메테오라 게임 스튜디오</t>
+  </si>
+  <si>
+    <t>[b][31bbf5]디렉터[-][/b]\n\n변동언</t>
+  </si>
+  <si>
+    <t>[b][31bbf5]게임기획[-][/b]\n\n변동언</t>
+  </si>
+  <si>
+    <t>[b][31bbf5]프로그래밍[-][/b]\n\n변동언</t>
+  </si>
+  <si>
+    <t>[b][31bbf5]그래픽[-][/b]\n\n변동언</t>
+  </si>
+  <si>
+    <t>[b][31bbf5]음악[-][/b]\n\n변동언</t>
+  </si>
+  <si>
+    <t>[b][31bbf5]테스트[-][/b]\n\n변동언</t>
+  </si>
+  <si>
+    <t>[b][31bbf5]감사한 사람들[-][/b]\n\n게기모, 유니티 개발자 그룹, 인디라 게임 개발자 모임</t>
+  </si>
+  <si>
+    <t>개발자 크레딧</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메테오라</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -10942,7 +11004,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1144"/>
+  <dimension ref="A1:E1154"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="33" bestFit="1" customWidth="1"/>
@@ -11112,13 +11174,13 @@
         <v>467</v>
       </c>
       <c r="C10" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="D10" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="E10" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -11163,13 +11225,13 @@
         <v>470</v>
       </c>
       <c r="C13" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="D13" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="E13" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -11214,13 +11276,13 @@
         <v>516</v>
       </c>
       <c r="C16" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="D16" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="E16" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -11265,13 +11327,13 @@
         <v>519</v>
       </c>
       <c r="C19" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="D19" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="E19" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -11316,13 +11378,13 @@
         <v>522</v>
       </c>
       <c r="C22" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="D22" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="E22" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -11367,13 +11429,13 @@
         <v>525</v>
       </c>
       <c r="C25" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="D25" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="E25" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -11418,13 +11480,13 @@
         <v>528</v>
       </c>
       <c r="C28" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="D28" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="E28" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -11469,13 +11531,13 @@
         <v>531</v>
       </c>
       <c r="C31" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="D31" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="E31" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -11588,13 +11650,13 @@
         <v>534</v>
       </c>
       <c r="C38" s="29" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="D38" s="29" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="E38" s="29" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -11605,13 +11667,13 @@
         <v>535</v>
       </c>
       <c r="C39" s="29" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="E39" s="29" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -11622,13 +11684,13 @@
         <v>536</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="E40" s="29" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -11639,13 +11701,13 @@
         <v>537</v>
       </c>
       <c r="C41" s="29" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="E41" s="29" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -11656,13 +11718,13 @@
         <v>538</v>
       </c>
       <c r="C42" s="29" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
       <c r="E42" s="29" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -11690,13 +11752,13 @@
         <v>540</v>
       </c>
       <c r="C44" s="29" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="E44" s="29" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -11758,13 +11820,13 @@
         <v>476</v>
       </c>
       <c r="C48" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="D48" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="E48" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
@@ -11809,13 +11871,13 @@
         <v>543</v>
       </c>
       <c r="C51" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="D51" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="E51" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
@@ -11860,13 +11922,13 @@
         <v>546</v>
       </c>
       <c r="C54" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="D54" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="E54" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
@@ -11911,13 +11973,13 @@
         <v>549</v>
       </c>
       <c r="C57" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="D57" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="E57" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
@@ -12268,13 +12330,13 @@
         <v>566</v>
       </c>
       <c r="C78" s="29" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="D78" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="E78" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
@@ -13288,13 +13350,13 @@
         <v>600</v>
       </c>
       <c r="C138" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
       <c r="D138" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
       <c r="E138" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
@@ -13305,13 +13367,13 @@
         <v>601</v>
       </c>
       <c r="C139" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="D139" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="E139" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
@@ -13322,13 +13384,13 @@
         <v>602</v>
       </c>
       <c r="C140" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="D140" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="E140" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
@@ -13339,7 +13401,7 @@
         <v>603</v>
       </c>
       <c r="C141" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="D141" t="s">
         <v>790</v>
@@ -13356,13 +13418,13 @@
         <v>604</v>
       </c>
       <c r="C142" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="D142" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="E142" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
@@ -13373,13 +13435,13 @@
         <v>605</v>
       </c>
       <c r="C143" t="s">
-        <v>2092</v>
+        <v>2091</v>
       </c>
       <c r="D143" t="s">
-        <v>2092</v>
+        <v>2091</v>
       </c>
       <c r="E143" t="s">
-        <v>2092</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
@@ -13390,13 +13452,13 @@
         <v>606</v>
       </c>
       <c r="C144" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
       <c r="D144" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
       <c r="E144" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
@@ -14019,13 +14081,13 @@
         <v>632</v>
       </c>
       <c r="C181" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="D181" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="E181" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.3">
@@ -14393,13 +14455,13 @@
         <v>55</v>
       </c>
       <c r="C203" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="D203" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="E203" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.3">
@@ -14410,13 +14472,13 @@
         <v>56</v>
       </c>
       <c r="C204" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="D204" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="E204" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.3">
@@ -14427,13 +14489,13 @@
         <v>57</v>
       </c>
       <c r="C205" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="D205" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="E205" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.3">
@@ -14444,13 +14506,13 @@
         <v>58</v>
       </c>
       <c r="C206" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="D206" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="E206" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.3">
@@ -15430,13 +15492,13 @@
         <v>374</v>
       </c>
       <c r="C264" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="D264" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="E264" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.3">
@@ -17246,7 +17308,7 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="C371" t="s">
         <v>1316</v>
@@ -17739,16 +17801,16 @@
         <v>399</v>
       </c>
       <c r="B400" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C400" t="s">
         <v>2074</v>
       </c>
-      <c r="C400" t="s">
-        <v>2075</v>
-      </c>
       <c r="D400" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="E400" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.3">
@@ -18708,16 +18770,16 @@
         <v>456</v>
       </c>
       <c r="B457" t="s">
+        <v>1846</v>
+      </c>
+      <c r="C457" t="s">
         <v>1847</v>
       </c>
-      <c r="C457" t="s">
-        <v>1848</v>
-      </c>
       <c r="D457" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="E457" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.3">
@@ -18946,16 +19008,16 @@
         <v>470</v>
       </c>
       <c r="B471" t="s">
+        <v>1844</v>
+      </c>
+      <c r="C471" t="s">
         <v>1845</v>
       </c>
-      <c r="C471" t="s">
-        <v>1846</v>
-      </c>
       <c r="D471" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="E471" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.3">
@@ -19286,7 +19348,7 @@
         <v>490</v>
       </c>
       <c r="B491" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="C491" t="s">
         <v>336</v>
@@ -19320,7 +19382,7 @@
         <v>492</v>
       </c>
       <c r="B493" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="C493" t="s">
         <v>338</v>
@@ -19337,16 +19399,16 @@
         <v>493</v>
       </c>
       <c r="B494" t="s">
+        <v>1858</v>
+      </c>
+      <c r="C494" t="s">
         <v>1859</v>
       </c>
-      <c r="C494" t="s">
-        <v>1860</v>
-      </c>
       <c r="D494" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="E494" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.3">
@@ -20734,13 +20796,13 @@
         <v>868</v>
       </c>
       <c r="C576" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="D576" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="E576" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="577" spans="1:5" x14ac:dyDescent="0.3">
@@ -20751,13 +20813,13 @@
         <v>869</v>
       </c>
       <c r="C577" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="D577" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="E577" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="578" spans="1:5" x14ac:dyDescent="0.3">
@@ -20836,13 +20898,13 @@
         <v>878</v>
       </c>
       <c r="C582" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="D582" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="E582" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="583" spans="1:5" x14ac:dyDescent="0.3">
@@ -21040,13 +21102,13 @@
         <v>905</v>
       </c>
       <c r="C594" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="D594" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="E594" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.3">
@@ -21074,13 +21136,13 @@
         <v>907</v>
       </c>
       <c r="C596" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="D596" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="E596" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="597" spans="1:5" x14ac:dyDescent="0.3">
@@ -21091,13 +21153,13 @@
         <v>908</v>
       </c>
       <c r="C597" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="D597" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="E597" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="598" spans="1:5" x14ac:dyDescent="0.3">
@@ -21227,13 +21289,13 @@
         <v>919</v>
       </c>
       <c r="C605" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="D605" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="E605" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="606" spans="1:5" x14ac:dyDescent="0.3">
@@ -21669,13 +21731,13 @@
         <v>1254</v>
       </c>
       <c r="C631" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="D631" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="E631" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="632" spans="1:5" x14ac:dyDescent="0.3">
@@ -21686,13 +21748,13 @@
         <v>1255</v>
       </c>
       <c r="C632" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="D632" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="E632" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="633" spans="1:5" x14ac:dyDescent="0.3">
@@ -21703,13 +21765,13 @@
         <v>1256</v>
       </c>
       <c r="C633" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="D633" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="E633" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="634" spans="1:5" x14ac:dyDescent="0.3">
@@ -21720,13 +21782,13 @@
         <v>1257</v>
       </c>
       <c r="C634" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="D634" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="E634" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="635" spans="1:5" x14ac:dyDescent="0.3">
@@ -21737,13 +21799,13 @@
         <v>1258</v>
       </c>
       <c r="C635" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="D635" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="E635" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="636" spans="1:5" x14ac:dyDescent="0.3">
@@ -21754,13 +21816,13 @@
         <v>1259</v>
       </c>
       <c r="C636" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="D636" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="E636" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="637" spans="1:5" x14ac:dyDescent="0.3">
@@ -21771,13 +21833,13 @@
         <v>1260</v>
       </c>
       <c r="C637" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="D637" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="E637" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="638" spans="1:5" x14ac:dyDescent="0.3">
@@ -21822,13 +21884,13 @@
         <v>1263</v>
       </c>
       <c r="C640" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="D640" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="E640" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="641" spans="1:5" x14ac:dyDescent="0.3">
@@ -22315,13 +22377,13 @@
         <v>1572</v>
       </c>
       <c r="C669" t="s">
-        <v>1573</v>
+        <v>2287</v>
       </c>
       <c r="D669" t="s">
-        <v>1573</v>
+        <v>2287</v>
       </c>
       <c r="E669" t="s">
-        <v>1573</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="670" spans="1:5" x14ac:dyDescent="0.3">
@@ -23505,13 +23567,13 @@
         <v>1374</v>
       </c>
       <c r="C739" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="D739" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="E739" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="740" spans="1:5" x14ac:dyDescent="0.3">
@@ -23522,13 +23584,13 @@
         <v>1375</v>
       </c>
       <c r="C740" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="D740" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="E740" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="741" spans="1:5" x14ac:dyDescent="0.3">
@@ -23539,13 +23601,13 @@
         <v>1376</v>
       </c>
       <c r="C741" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="D741" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="E741" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="742" spans="1:5" x14ac:dyDescent="0.3">
@@ -23556,13 +23618,13 @@
         <v>1377</v>
       </c>
       <c r="C742" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="D742" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="E742" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="743" spans="1:5" x14ac:dyDescent="0.3">
@@ -24559,13 +24621,13 @@
         <v>1543</v>
       </c>
       <c r="C801" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="D801" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="E801" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="802" spans="1:5" x14ac:dyDescent="0.3">
@@ -24576,13 +24638,13 @@
         <v>1544</v>
       </c>
       <c r="C802" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="D802" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="E802" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="803" spans="1:5" x14ac:dyDescent="0.3">
@@ -24794,16 +24856,16 @@
         <v>814</v>
       </c>
       <c r="B815" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="C815" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="D815" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="E815" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="816" spans="1:5" x14ac:dyDescent="0.3">
@@ -24811,16 +24873,16 @@
         <v>815</v>
       </c>
       <c r="B816" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="C816" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="D816" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="E816" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="817" spans="1:5" x14ac:dyDescent="0.3">
@@ -24828,16 +24890,16 @@
         <v>816</v>
       </c>
       <c r="B817" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="C817" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="D817" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="E817" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="818" spans="1:5" x14ac:dyDescent="0.3">
@@ -24845,16 +24907,16 @@
         <v>817</v>
       </c>
       <c r="B818" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="C818" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="D818" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="E818" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="819" spans="1:5" x14ac:dyDescent="0.3">
@@ -24862,16 +24924,16 @@
         <v>818</v>
       </c>
       <c r="B819" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="C819" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="D819" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="E819" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="820" spans="1:5" x14ac:dyDescent="0.3">
@@ -24879,16 +24941,16 @@
         <v>819</v>
       </c>
       <c r="B820" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="C820" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="D820" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="E820" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="821" spans="1:5" x14ac:dyDescent="0.3">
@@ -24896,16 +24958,16 @@
         <v>820</v>
       </c>
       <c r="B821" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="C821" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="D821" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="E821" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="822" spans="1:5" x14ac:dyDescent="0.3">
@@ -24913,16 +24975,16 @@
         <v>821</v>
       </c>
       <c r="B822" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="C822" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="D822" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="E822" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="823" spans="1:5" x14ac:dyDescent="0.3">
@@ -24930,16 +24992,16 @@
         <v>822</v>
       </c>
       <c r="B823" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="C823" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="D823" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="E823" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="824" spans="1:5" x14ac:dyDescent="0.3">
@@ -24947,16 +25009,16 @@
         <v>823</v>
       </c>
       <c r="B824" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="C824" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="D824" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="E824" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="825" spans="1:5" x14ac:dyDescent="0.3">
@@ -24964,16 +25026,16 @@
         <v>824</v>
       </c>
       <c r="B825" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="C825" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="D825" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="E825" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="826" spans="1:5" x14ac:dyDescent="0.3">
@@ -24981,16 +25043,16 @@
         <v>825</v>
       </c>
       <c r="B826" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="C826" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="D826" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="E826" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="827" spans="1:5" x14ac:dyDescent="0.3">
@@ -24998,16 +25060,16 @@
         <v>826</v>
       </c>
       <c r="B827" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="C827" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="D827" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="E827" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="828" spans="1:5" x14ac:dyDescent="0.3">
@@ -25015,16 +25077,16 @@
         <v>827</v>
       </c>
       <c r="B828" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="C828" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="D828" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="E828" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="829" spans="1:5" x14ac:dyDescent="0.3">
@@ -25032,16 +25094,16 @@
         <v>828</v>
       </c>
       <c r="B829" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="C829" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="D829" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="E829" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="830" spans="1:5" x14ac:dyDescent="0.3">
@@ -25049,16 +25111,16 @@
         <v>829</v>
       </c>
       <c r="B830" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="C830" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="D830" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="E830" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="831" spans="1:5" x14ac:dyDescent="0.3">
@@ -25066,16 +25128,16 @@
         <v>830</v>
       </c>
       <c r="B831" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="C831" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="D831" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="E831" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="832" spans="1:5" x14ac:dyDescent="0.3">
@@ -25083,16 +25145,16 @@
         <v>831</v>
       </c>
       <c r="B832" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="C832" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="D832" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="E832" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="833" spans="1:5" x14ac:dyDescent="0.3">
@@ -25100,16 +25162,16 @@
         <v>832</v>
       </c>
       <c r="B833" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="C833" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="D833" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="E833" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="834" spans="1:5" x14ac:dyDescent="0.3">
@@ -25117,16 +25179,16 @@
         <v>833</v>
       </c>
       <c r="B834" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="C834" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="D834" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="E834" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="835" spans="1:5" x14ac:dyDescent="0.3">
@@ -25134,16 +25196,16 @@
         <v>834</v>
       </c>
       <c r="B835" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="C835" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="D835" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="E835" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="836" spans="1:5" x14ac:dyDescent="0.3">
@@ -25151,16 +25213,16 @@
         <v>835</v>
       </c>
       <c r="B836" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="C836" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="D836" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="E836" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="837" spans="1:5" x14ac:dyDescent="0.3">
@@ -25168,16 +25230,16 @@
         <v>836</v>
       </c>
       <c r="B837" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="C837" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="D837" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="E837" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="838" spans="1:5" x14ac:dyDescent="0.3">
@@ -25185,16 +25247,16 @@
         <v>837</v>
       </c>
       <c r="B838" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="C838" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="D838" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="E838" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="839" spans="1:5" x14ac:dyDescent="0.3">
@@ -25202,16 +25264,16 @@
         <v>838</v>
       </c>
       <c r="B839" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="C839" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="D839" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="E839" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="840" spans="1:5" x14ac:dyDescent="0.3">
@@ -25219,16 +25281,16 @@
         <v>839</v>
       </c>
       <c r="B840" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="C840" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="D840" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="E840" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="841" spans="1:5" x14ac:dyDescent="0.3">
@@ -25236,16 +25298,16 @@
         <v>840</v>
       </c>
       <c r="B841" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="C841" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="D841" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="E841" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="842" spans="1:5" x14ac:dyDescent="0.3">
@@ -25253,16 +25315,16 @@
         <v>841</v>
       </c>
       <c r="B842" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="C842" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="D842" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="E842" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="843" spans="1:5" x14ac:dyDescent="0.3">
@@ -25270,16 +25332,16 @@
         <v>842</v>
       </c>
       <c r="B843" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="C843" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="D843" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="E843" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="844" spans="1:5" x14ac:dyDescent="0.3">
@@ -25287,16 +25349,16 @@
         <v>843</v>
       </c>
       <c r="B844" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="C844" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="D844" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="E844" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="845" spans="1:5" x14ac:dyDescent="0.3">
@@ -25304,16 +25366,16 @@
         <v>844</v>
       </c>
       <c r="B845" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="C845" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="D845" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="E845" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="846" spans="1:5" x14ac:dyDescent="0.3">
@@ -25321,16 +25383,16 @@
         <v>845</v>
       </c>
       <c r="B846" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="C846" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="D846" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="E846" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="847" spans="1:5" x14ac:dyDescent="0.3">
@@ -25338,16 +25400,16 @@
         <v>846</v>
       </c>
       <c r="B847" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="C847" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="D847" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="E847" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="848" spans="1:5" x14ac:dyDescent="0.3">
@@ -25355,7 +25417,7 @@
         <v>847</v>
       </c>
       <c r="B848" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="C848" t="s">
         <v>1016</v>
@@ -25372,16 +25434,16 @@
         <v>848</v>
       </c>
       <c r="B849" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="C849" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="D849" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="E849" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="850" spans="1:5" x14ac:dyDescent="0.3">
@@ -25389,16 +25451,16 @@
         <v>849</v>
       </c>
       <c r="B850" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="C850" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="D850" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="E850" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="851" spans="1:5" x14ac:dyDescent="0.3">
@@ -25406,16 +25468,16 @@
         <v>850</v>
       </c>
       <c r="B851" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="C851" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="D851" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="E851" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="852" spans="1:5" x14ac:dyDescent="0.3">
@@ -25423,16 +25485,16 @@
         <v>851</v>
       </c>
       <c r="B852" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="C852" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="D852" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="E852" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="853" spans="1:5" x14ac:dyDescent="0.3">
@@ -25440,16 +25502,16 @@
         <v>852</v>
       </c>
       <c r="B853" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="C853" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="D853" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="E853" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="854" spans="1:5" x14ac:dyDescent="0.3">
@@ -25457,16 +25519,16 @@
         <v>853</v>
       </c>
       <c r="B854" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="C854" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="D854" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="E854" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="855" spans="1:5" x14ac:dyDescent="0.3">
@@ -25474,16 +25536,16 @@
         <v>854</v>
       </c>
       <c r="B855" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="C855" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="D855" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="E855" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="856" spans="1:5" x14ac:dyDescent="0.3">
@@ -25491,16 +25553,16 @@
         <v>855</v>
       </c>
       <c r="B856" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="C856" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="D856" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="E856" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="857" spans="1:5" x14ac:dyDescent="0.3">
@@ -25508,16 +25570,16 @@
         <v>856</v>
       </c>
       <c r="B857" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="C857" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="D857" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="E857" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="858" spans="1:5" x14ac:dyDescent="0.3">
@@ -25525,16 +25587,16 @@
         <v>857</v>
       </c>
       <c r="B858" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="C858" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="D858" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="E858" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="859" spans="1:5" x14ac:dyDescent="0.3">
@@ -25542,16 +25604,16 @@
         <v>858</v>
       </c>
       <c r="B859" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="C859" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="D859" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="E859" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="860" spans="1:5" x14ac:dyDescent="0.3">
@@ -25559,16 +25621,16 @@
         <v>859</v>
       </c>
       <c r="B860" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="C860" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="D860" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="E860" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="861" spans="1:5" x14ac:dyDescent="0.3">
@@ -25576,16 +25638,16 @@
         <v>860</v>
       </c>
       <c r="B861" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="C861" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="D861" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="E861" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="862" spans="1:5" x14ac:dyDescent="0.3">
@@ -25593,16 +25655,16 @@
         <v>861</v>
       </c>
       <c r="B862" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="C862" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="D862" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="E862" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="863" spans="1:5" x14ac:dyDescent="0.3">
@@ -25610,16 +25672,16 @@
         <v>862</v>
       </c>
       <c r="B863" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="C863" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="D863" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="E863" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="864" spans="1:5" x14ac:dyDescent="0.3">
@@ -25627,16 +25689,16 @@
         <v>863</v>
       </c>
       <c r="B864" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="C864" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="D864" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="E864" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="865" spans="1:5" x14ac:dyDescent="0.3">
@@ -25644,16 +25706,16 @@
         <v>864</v>
       </c>
       <c r="B865" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="C865" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="D865" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="E865" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="866" spans="1:5" x14ac:dyDescent="0.3">
@@ -25661,16 +25723,16 @@
         <v>865</v>
       </c>
       <c r="B866" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="C866" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="D866" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="E866" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="867" spans="1:5" x14ac:dyDescent="0.3">
@@ -25678,16 +25740,16 @@
         <v>866</v>
       </c>
       <c r="B867" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="C867" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="D867" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="E867" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="868" spans="1:5" x14ac:dyDescent="0.3">
@@ -25695,16 +25757,16 @@
         <v>867</v>
       </c>
       <c r="B868" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="C868" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="D868" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="E868" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="869" spans="1:5" x14ac:dyDescent="0.3">
@@ -25712,16 +25774,16 @@
         <v>868</v>
       </c>
       <c r="B869" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="C869" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="D869" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="E869" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="870" spans="1:5" x14ac:dyDescent="0.3">
@@ -25729,16 +25791,16 @@
         <v>869</v>
       </c>
       <c r="B870" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="C870" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="D870" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="E870" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="871" spans="1:5" x14ac:dyDescent="0.3">
@@ -25746,10 +25808,10 @@
         <v>870</v>
       </c>
       <c r="B871" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="C871" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="D871" t="s">
         <v>1051</v>
@@ -25763,10 +25825,10 @@
         <v>871</v>
       </c>
       <c r="B872" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="C872" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="D872" t="s">
         <v>1051</v>
@@ -25780,16 +25842,16 @@
         <v>872</v>
       </c>
       <c r="B873" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="C873" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="D873" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="E873" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="874" spans="1:5" x14ac:dyDescent="0.3">
@@ -25797,16 +25859,16 @@
         <v>873</v>
       </c>
       <c r="B874" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="C874" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="D874" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="E874" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="875" spans="1:5" x14ac:dyDescent="0.3">
@@ -25814,16 +25876,16 @@
         <v>874</v>
       </c>
       <c r="B875" t="s">
+        <v>1685</v>
+      </c>
+      <c r="C875" t="s">
         <v>1686</v>
       </c>
-      <c r="C875" t="s">
-        <v>1687</v>
-      </c>
       <c r="D875" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="E875" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="876" spans="1:5" x14ac:dyDescent="0.3">
@@ -25831,16 +25893,16 @@
         <v>875</v>
       </c>
       <c r="B876" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="C876" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="D876" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="E876" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="877" spans="1:5" x14ac:dyDescent="0.3">
@@ -25848,16 +25910,16 @@
         <v>876</v>
       </c>
       <c r="B877" t="s">
+        <v>1692</v>
+      </c>
+      <c r="C877" t="s">
         <v>1693</v>
       </c>
-      <c r="C877" t="s">
-        <v>1694</v>
-      </c>
       <c r="D877" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="E877" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="878" spans="1:5" x14ac:dyDescent="0.3">
@@ -25865,16 +25927,16 @@
         <v>877</v>
       </c>
       <c r="B878" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="C878" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="D878" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="E878" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="879" spans="1:5" x14ac:dyDescent="0.3">
@@ -25882,16 +25944,16 @@
         <v>878</v>
       </c>
       <c r="B879" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C879" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="D879" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="E879" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="880" spans="1:5" x14ac:dyDescent="0.3">
@@ -25899,16 +25961,16 @@
         <v>879</v>
       </c>
       <c r="B880" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="C880" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="D880" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="E880" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="881" spans="1:5" x14ac:dyDescent="0.3">
@@ -25916,16 +25978,16 @@
         <v>880</v>
       </c>
       <c r="B881" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="C881" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="D881" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="E881" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="882" spans="1:5" x14ac:dyDescent="0.3">
@@ -25933,16 +25995,16 @@
         <v>881</v>
       </c>
       <c r="B882" t="s">
+        <v>1702</v>
+      </c>
+      <c r="C882" t="s">
         <v>1703</v>
       </c>
-      <c r="C882" t="s">
-        <v>1704</v>
-      </c>
       <c r="D882" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="E882" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="883" spans="1:5" x14ac:dyDescent="0.3">
@@ -25950,16 +26012,16 @@
         <v>882</v>
       </c>
       <c r="B883" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="C883" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="D883" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="E883" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="884" spans="1:5" x14ac:dyDescent="0.3">
@@ -25967,16 +26029,16 @@
         <v>883</v>
       </c>
       <c r="B884" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="C884" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="D884" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="E884" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="885" spans="1:5" x14ac:dyDescent="0.3">
@@ -25984,16 +26046,16 @@
         <v>884</v>
       </c>
       <c r="B885" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="C885" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="D885" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="E885" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="886" spans="1:5" x14ac:dyDescent="0.3">
@@ -26001,16 +26063,16 @@
         <v>885</v>
       </c>
       <c r="B886" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="C886" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="D886" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E886" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="887" spans="1:5" x14ac:dyDescent="0.3">
@@ -26018,16 +26080,16 @@
         <v>886</v>
       </c>
       <c r="B887" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="C887" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="D887" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="E887" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="888" spans="1:5" x14ac:dyDescent="0.3">
@@ -26035,16 +26097,16 @@
         <v>887</v>
       </c>
       <c r="B888" t="s">
+        <v>1714</v>
+      </c>
+      <c r="C888" t="s">
         <v>1715</v>
       </c>
-      <c r="C888" t="s">
-        <v>1716</v>
-      </c>
       <c r="D888" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="E888" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="889" spans="1:5" x14ac:dyDescent="0.3">
@@ -26052,16 +26114,16 @@
         <v>888</v>
       </c>
       <c r="B889" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="C889" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="D889" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="E889" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="890" spans="1:5" x14ac:dyDescent="0.3">
@@ -26069,16 +26131,16 @@
         <v>889</v>
       </c>
       <c r="B890" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="C890" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="D890" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="E890" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="891" spans="1:5" x14ac:dyDescent="0.3">
@@ -26086,16 +26148,16 @@
         <v>890</v>
       </c>
       <c r="B891" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="C891" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="D891" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="E891" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="892" spans="1:5" x14ac:dyDescent="0.3">
@@ -26103,16 +26165,16 @@
         <v>891</v>
       </c>
       <c r="B892" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="C892" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="D892" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="E892" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="893" spans="1:5" x14ac:dyDescent="0.3">
@@ -26120,16 +26182,16 @@
         <v>892</v>
       </c>
       <c r="B893" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="C893" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="D893" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="E893" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="894" spans="1:5" x14ac:dyDescent="0.3">
@@ -26137,16 +26199,16 @@
         <v>893</v>
       </c>
       <c r="B894" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="C894" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="D894" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="E894" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="895" spans="1:5" x14ac:dyDescent="0.3">
@@ -26154,16 +26216,16 @@
         <v>894</v>
       </c>
       <c r="B895" t="s">
+        <v>1728</v>
+      </c>
+      <c r="C895" t="s">
         <v>1729</v>
       </c>
-      <c r="C895" t="s">
-        <v>1730</v>
-      </c>
       <c r="D895" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="E895" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="896" spans="1:5" x14ac:dyDescent="0.3">
@@ -26171,16 +26233,16 @@
         <v>895</v>
       </c>
       <c r="B896" t="s">
+        <v>1730</v>
+      </c>
+      <c r="C896" t="s">
         <v>1731</v>
       </c>
-      <c r="C896" t="s">
-        <v>1732</v>
-      </c>
       <c r="D896" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="E896" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="897" spans="1:5" x14ac:dyDescent="0.3">
@@ -26188,16 +26250,16 @@
         <v>896</v>
       </c>
       <c r="B897" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="C897" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="D897" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="E897" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="898" spans="1:5" x14ac:dyDescent="0.3">
@@ -26205,16 +26267,16 @@
         <v>897</v>
       </c>
       <c r="B898" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="C898" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="D898" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="E898" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="899" spans="1:5" x14ac:dyDescent="0.3">
@@ -26222,16 +26284,16 @@
         <v>898</v>
       </c>
       <c r="B899" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="C899" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="D899" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="E899" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="900" spans="1:5" x14ac:dyDescent="0.3">
@@ -26239,16 +26301,16 @@
         <v>899</v>
       </c>
       <c r="B900" t="s">
+        <v>1741</v>
+      </c>
+      <c r="C900" t="s">
         <v>1742</v>
       </c>
-      <c r="C900" t="s">
-        <v>1743</v>
-      </c>
       <c r="D900" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="E900" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="901" spans="1:5" x14ac:dyDescent="0.3">
@@ -26256,16 +26318,16 @@
         <v>900</v>
       </c>
       <c r="B901" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="C901" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="D901" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="E901" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="902" spans="1:5" x14ac:dyDescent="0.3">
@@ -26273,16 +26335,16 @@
         <v>901</v>
       </c>
       <c r="B902" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="C902" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="D902" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="E902" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="903" spans="1:5" x14ac:dyDescent="0.3">
@@ -26290,16 +26352,16 @@
         <v>902</v>
       </c>
       <c r="B903" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="C903" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="D903" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="E903" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="904" spans="1:5" x14ac:dyDescent="0.3">
@@ -26307,16 +26369,16 @@
         <v>903</v>
       </c>
       <c r="B904" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="C904" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="D904" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="E904" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="905" spans="1:5" x14ac:dyDescent="0.3">
@@ -26324,16 +26386,16 @@
         <v>904</v>
       </c>
       <c r="B905" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="C905" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="D905" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="E905" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="906" spans="1:5" x14ac:dyDescent="0.3">
@@ -26341,16 +26403,16 @@
         <v>905</v>
       </c>
       <c r="B906" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="C906" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="D906" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="E906" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="907" spans="1:5" x14ac:dyDescent="0.3">
@@ -26358,16 +26420,16 @@
         <v>906</v>
       </c>
       <c r="B907" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="C907" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="D907" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="E907" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="908" spans="1:5" x14ac:dyDescent="0.3">
@@ -26375,16 +26437,16 @@
         <v>907</v>
       </c>
       <c r="B908" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="C908" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="D908" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="E908" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="909" spans="1:5" x14ac:dyDescent="0.3">
@@ -26392,16 +26454,16 @@
         <v>908</v>
       </c>
       <c r="B909" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="C909" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="D909" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="E909" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="910" spans="1:5" x14ac:dyDescent="0.3">
@@ -26409,16 +26471,16 @@
         <v>909</v>
       </c>
       <c r="B910" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="C910" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="D910" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="E910" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="911" spans="1:5" x14ac:dyDescent="0.3">
@@ -26426,16 +26488,16 @@
         <v>910</v>
       </c>
       <c r="B911" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="C911" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="D911" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="E911" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="912" spans="1:5" x14ac:dyDescent="0.3">
@@ -26443,16 +26505,16 @@
         <v>911</v>
       </c>
       <c r="B912" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="C912" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="D912" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="E912" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="913" spans="1:5" x14ac:dyDescent="0.3">
@@ -26460,16 +26522,16 @@
         <v>912</v>
       </c>
       <c r="B913" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="C913" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="D913" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="E913" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="914" spans="1:5" x14ac:dyDescent="0.3">
@@ -26477,16 +26539,16 @@
         <v>913</v>
       </c>
       <c r="B914" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="C914" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="D914" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="E914" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="915" spans="1:5" x14ac:dyDescent="0.3">
@@ -26494,16 +26556,16 @@
         <v>914</v>
       </c>
       <c r="B915" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="C915" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="D915" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="E915" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="916" spans="1:5" x14ac:dyDescent="0.3">
@@ -26511,16 +26573,16 @@
         <v>915</v>
       </c>
       <c r="B916" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="C916" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="D916" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="E916" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="917" spans="1:5" x14ac:dyDescent="0.3">
@@ -26528,16 +26590,16 @@
         <v>916</v>
       </c>
       <c r="B917" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="C917" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="D917" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="E917" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="918" spans="1:5" x14ac:dyDescent="0.3">
@@ -26545,16 +26607,16 @@
         <v>917</v>
       </c>
       <c r="B918" t="s">
+        <v>1804</v>
+      </c>
+      <c r="C918" t="s">
         <v>1805</v>
       </c>
-      <c r="C918" t="s">
-        <v>1806</v>
-      </c>
       <c r="D918" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="E918" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="919" spans="1:5" x14ac:dyDescent="0.3">
@@ -26562,16 +26624,16 @@
         <v>918</v>
       </c>
       <c r="B919" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="C919" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="D919" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="E919" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="920" spans="1:5" x14ac:dyDescent="0.3">
@@ -26579,16 +26641,16 @@
         <v>919</v>
       </c>
       <c r="B920" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="C920" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="D920" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="E920" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="921" spans="1:5" x14ac:dyDescent="0.3">
@@ -26596,16 +26658,16 @@
         <v>920</v>
       </c>
       <c r="B921" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="C921" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="D921" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="E921" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="922" spans="1:5" x14ac:dyDescent="0.3">
@@ -26613,16 +26675,16 @@
         <v>921</v>
       </c>
       <c r="B922" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="C922" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="D922" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="E922" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="923" spans="1:5" x14ac:dyDescent="0.3">
@@ -26630,16 +26692,16 @@
         <v>922</v>
       </c>
       <c r="B923" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="C923" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="D923" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="E923" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="924" spans="1:5" x14ac:dyDescent="0.3">
@@ -26647,16 +26709,16 @@
         <v>923</v>
       </c>
       <c r="B924" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="C924" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="D924" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="E924" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="925" spans="1:5" x14ac:dyDescent="0.3">
@@ -26664,16 +26726,16 @@
         <v>924</v>
       </c>
       <c r="B925" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="C925" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="D925" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="E925" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="926" spans="1:5" x14ac:dyDescent="0.3">
@@ -26681,16 +26743,16 @@
         <v>925</v>
       </c>
       <c r="B926" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="C926" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="D926" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="E926" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="927" spans="1:5" x14ac:dyDescent="0.3">
@@ -26698,16 +26760,16 @@
         <v>926</v>
       </c>
       <c r="B927" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="C927" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="D927" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="E927" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="928" spans="1:5" x14ac:dyDescent="0.3">
@@ -26715,16 +26777,16 @@
         <v>927</v>
       </c>
       <c r="B928" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="C928" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="D928" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="E928" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="929" spans="1:5" x14ac:dyDescent="0.3">
@@ -26732,16 +26794,16 @@
         <v>928</v>
       </c>
       <c r="B929" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="C929" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="D929" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="E929" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="930" spans="1:5" x14ac:dyDescent="0.3">
@@ -26749,16 +26811,16 @@
         <v>929</v>
       </c>
       <c r="B930" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="C930" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="D930" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="E930" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="931" spans="1:5" x14ac:dyDescent="0.3">
@@ -26766,16 +26828,16 @@
         <v>930</v>
       </c>
       <c r="B931" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="C931" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="D931" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="E931" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="932" spans="1:5" x14ac:dyDescent="0.3">
@@ -26783,16 +26845,16 @@
         <v>931</v>
       </c>
       <c r="B932" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="C932" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="D932" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="E932" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="933" spans="1:5" x14ac:dyDescent="0.3">
@@ -26800,16 +26862,16 @@
         <v>932</v>
       </c>
       <c r="B933" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C933" t="s">
         <v>1851</v>
       </c>
-      <c r="C933" t="s">
-        <v>1852</v>
-      </c>
       <c r="D933" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="E933" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="934" spans="1:5" x14ac:dyDescent="0.3">
@@ -26817,16 +26879,16 @@
         <v>933</v>
       </c>
       <c r="B934" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C934" t="s">
         <v>1837</v>
       </c>
-      <c r="C934" t="s">
-        <v>1838</v>
-      </c>
       <c r="D934" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="E934" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="935" spans="1:5" x14ac:dyDescent="0.3">
@@ -26834,16 +26896,16 @@
         <v>934</v>
       </c>
       <c r="B935" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C935" t="s">
         <v>1839</v>
       </c>
-      <c r="C935" t="s">
-        <v>1840</v>
-      </c>
       <c r="D935" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="E935" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="936" spans="1:5" x14ac:dyDescent="0.3">
@@ -26851,16 +26913,16 @@
         <v>935</v>
       </c>
       <c r="B936" t="s">
+        <v>1840</v>
+      </c>
+      <c r="C936" t="s">
         <v>1841</v>
       </c>
-      <c r="C936" t="s">
-        <v>1842</v>
-      </c>
       <c r="D936" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="E936" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="937" spans="1:5" x14ac:dyDescent="0.3">
@@ -26868,16 +26930,16 @@
         <v>936</v>
       </c>
       <c r="B937" t="s">
+        <v>1842</v>
+      </c>
+      <c r="C937" t="s">
         <v>1843</v>
       </c>
-      <c r="C937" t="s">
-        <v>1844</v>
-      </c>
       <c r="D937" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="E937" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="938" spans="1:5" x14ac:dyDescent="0.3">
@@ -26885,16 +26947,16 @@
         <v>937</v>
       </c>
       <c r="B938" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C938" t="s">
         <v>1849</v>
       </c>
-      <c r="C938" t="s">
-        <v>1850</v>
-      </c>
       <c r="D938" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="E938" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="939" spans="1:5" x14ac:dyDescent="0.3">
@@ -26902,16 +26964,16 @@
         <v>938</v>
       </c>
       <c r="B939" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="C939" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="D939" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="E939" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="940" spans="1:5" x14ac:dyDescent="0.3">
@@ -26919,16 +26981,16 @@
         <v>939</v>
       </c>
       <c r="B940" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="C940" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="D940" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="E940" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="941" spans="1:5" x14ac:dyDescent="0.3">
@@ -26936,16 +26998,16 @@
         <v>940</v>
       </c>
       <c r="B941" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="C941" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="D941" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="E941" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="942" spans="1:5" x14ac:dyDescent="0.3">
@@ -26953,16 +27015,16 @@
         <v>941</v>
       </c>
       <c r="B942" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="C942" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="D942" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="E942" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="943" spans="1:5" x14ac:dyDescent="0.3">
@@ -26970,16 +27032,16 @@
         <v>942</v>
       </c>
       <c r="B943" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="C943" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="D943" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="E943" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="944" spans="1:5" x14ac:dyDescent="0.3">
@@ -26987,16 +27049,16 @@
         <v>943</v>
       </c>
       <c r="B944" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="C944" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="D944" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="E944" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="945" spans="1:5" x14ac:dyDescent="0.3">
@@ -27004,16 +27066,16 @@
         <v>944</v>
       </c>
       <c r="B945" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="C945" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="D945" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="E945" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="946" spans="1:5" x14ac:dyDescent="0.3">
@@ -27021,16 +27083,16 @@
         <v>945</v>
       </c>
       <c r="B946" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="C946" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="D946" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="E946" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="947" spans="1:5" x14ac:dyDescent="0.3">
@@ -27038,16 +27100,16 @@
         <v>946</v>
       </c>
       <c r="B947" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="C947" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="D947" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="E947" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="948" spans="1:5" x14ac:dyDescent="0.3">
@@ -27055,16 +27117,16 @@
         <v>947</v>
       </c>
       <c r="B948" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="C948" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="D948" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="E948" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="949" spans="1:5" x14ac:dyDescent="0.3">
@@ -27072,16 +27134,16 @@
         <v>948</v>
       </c>
       <c r="B949" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="C949" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="D949" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="E949" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="950" spans="1:5" x14ac:dyDescent="0.3">
@@ -27089,16 +27151,16 @@
         <v>949</v>
       </c>
       <c r="B950" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="C950" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="D950" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="E950" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="951" spans="1:5" x14ac:dyDescent="0.3">
@@ -27106,16 +27168,16 @@
         <v>950</v>
       </c>
       <c r="B951" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="C951" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="D951" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="E951" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="952" spans="1:5" x14ac:dyDescent="0.3">
@@ -27123,16 +27185,16 @@
         <v>951</v>
       </c>
       <c r="B952" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="C952" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="D952" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="E952" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="953" spans="1:5" x14ac:dyDescent="0.3">
@@ -27140,16 +27202,16 @@
         <v>952</v>
       </c>
       <c r="B953" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="C953" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="D953" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="E953" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="954" spans="1:5" x14ac:dyDescent="0.3">
@@ -27157,16 +27219,16 @@
         <v>953</v>
       </c>
       <c r="B954" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="C954" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="D954" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="E954" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="955" spans="1:5" x14ac:dyDescent="0.3">
@@ -27174,16 +27236,16 @@
         <v>954</v>
       </c>
       <c r="B955" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="C955" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="D955" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="E955" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="956" spans="1:5" x14ac:dyDescent="0.3">
@@ -27191,16 +27253,16 @@
         <v>955</v>
       </c>
       <c r="B956" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="C956" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="D956" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="E956" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="957" spans="1:5" x14ac:dyDescent="0.3">
@@ -27208,16 +27270,16 @@
         <v>956</v>
       </c>
       <c r="B957" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="C957" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="D957" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="E957" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="958" spans="1:5" x14ac:dyDescent="0.3">
@@ -27225,16 +27287,16 @@
         <v>957</v>
       </c>
       <c r="B958" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="C958" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="D958" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="E958" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="959" spans="1:5" x14ac:dyDescent="0.3">
@@ -27242,16 +27304,16 @@
         <v>958</v>
       </c>
       <c r="B959" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="C959" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="D959" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="E959" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="960" spans="1:5" x14ac:dyDescent="0.3">
@@ -27259,16 +27321,16 @@
         <v>959</v>
       </c>
       <c r="B960" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="C960" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="D960" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="E960" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="961" spans="1:5" x14ac:dyDescent="0.3">
@@ -27276,16 +27338,16 @@
         <v>960</v>
       </c>
       <c r="B961" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="C961" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="D961" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="E961" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="962" spans="1:5" x14ac:dyDescent="0.3">
@@ -27293,16 +27355,16 @@
         <v>961</v>
       </c>
       <c r="B962" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="C962" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="D962" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="E962" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="963" spans="1:5" x14ac:dyDescent="0.3">
@@ -27310,16 +27372,16 @@
         <v>962</v>
       </c>
       <c r="B963" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="C963" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="D963" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="E963" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="964" spans="1:5" x14ac:dyDescent="0.3">
@@ -27327,16 +27389,16 @@
         <v>963</v>
       </c>
       <c r="B964" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="C964" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="D964" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="E964" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="965" spans="1:5" x14ac:dyDescent="0.3">
@@ -27344,16 +27406,16 @@
         <v>964</v>
       </c>
       <c r="B965" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="C965" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="D965" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="E965" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="966" spans="1:5" x14ac:dyDescent="0.3">
@@ -27361,16 +27423,16 @@
         <v>965</v>
       </c>
       <c r="B966" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="C966" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="D966" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="E966" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="967" spans="1:5" x14ac:dyDescent="0.3">
@@ -27378,16 +27440,16 @@
         <v>966</v>
       </c>
       <c r="B967" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="C967" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="D967" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="E967" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="968" spans="1:5" x14ac:dyDescent="0.3">
@@ -27395,16 +27457,16 @@
         <v>967</v>
       </c>
       <c r="B968" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="C968" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="D968" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="E968" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="969" spans="1:5" x14ac:dyDescent="0.3">
@@ -27412,16 +27474,16 @@
         <v>968</v>
       </c>
       <c r="B969" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="C969" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="D969" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="E969" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="970" spans="1:5" x14ac:dyDescent="0.3">
@@ -27429,16 +27491,16 @@
         <v>969</v>
       </c>
       <c r="B970" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="C970" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="D970" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="E970" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="971" spans="1:5" x14ac:dyDescent="0.3">
@@ -27446,16 +27508,16 @@
         <v>970</v>
       </c>
       <c r="B971" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="C971" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="D971" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="E971" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="972" spans="1:5" x14ac:dyDescent="0.3">
@@ -27463,16 +27525,16 @@
         <v>971</v>
       </c>
       <c r="B972" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="C972" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="D972" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="E972" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="973" spans="1:5" x14ac:dyDescent="0.3">
@@ -27480,16 +27542,16 @@
         <v>972</v>
       </c>
       <c r="B973" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C973" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="D973" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="E973" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="974" spans="1:5" x14ac:dyDescent="0.3">
@@ -27497,16 +27559,16 @@
         <v>973</v>
       </c>
       <c r="B974" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="C974" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="D974" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="E974" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="975" spans="1:5" x14ac:dyDescent="0.3">
@@ -27514,16 +27576,16 @@
         <v>974</v>
       </c>
       <c r="B975" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="C975" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="D975" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="E975" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="976" spans="1:5" x14ac:dyDescent="0.3">
@@ -27531,16 +27593,16 @@
         <v>975</v>
       </c>
       <c r="B976" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="C976" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="D976" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="E976" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="977" spans="1:5" x14ac:dyDescent="0.3">
@@ -27548,16 +27610,16 @@
         <v>976</v>
       </c>
       <c r="B977" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="C977" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="D977" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="E977" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="978" spans="1:5" x14ac:dyDescent="0.3">
@@ -27565,16 +27627,16 @@
         <v>977</v>
       </c>
       <c r="B978" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="C978" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="D978" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="E978" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="979" spans="1:5" x14ac:dyDescent="0.3">
@@ -27582,16 +27644,16 @@
         <v>978</v>
       </c>
       <c r="B979" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="C979" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="D979" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="E979" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="980" spans="1:5" x14ac:dyDescent="0.3">
@@ -27599,16 +27661,16 @@
         <v>979</v>
       </c>
       <c r="B980" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="C980" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="D980" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="E980" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="981" spans="1:5" x14ac:dyDescent="0.3">
@@ -27616,16 +27678,16 @@
         <v>980</v>
       </c>
       <c r="B981" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="C981" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="D981" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="E981" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="982" spans="1:5" x14ac:dyDescent="0.3">
@@ -27633,16 +27695,16 @@
         <v>981</v>
       </c>
       <c r="B982" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="C982" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="D982" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="E982" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="983" spans="1:5" x14ac:dyDescent="0.3">
@@ -27650,16 +27712,16 @@
         <v>982</v>
       </c>
       <c r="B983" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="C983" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="D983" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="E983" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="984" spans="1:5" x14ac:dyDescent="0.3">
@@ -27667,16 +27729,16 @@
         <v>983</v>
       </c>
       <c r="B984" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="C984" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="D984" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="E984" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="985" spans="1:5" x14ac:dyDescent="0.3">
@@ -27684,16 +27746,16 @@
         <v>984</v>
       </c>
       <c r="B985" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="C985" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="D985" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="E985" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="986" spans="1:5" x14ac:dyDescent="0.3">
@@ -27701,16 +27763,16 @@
         <v>985</v>
       </c>
       <c r="B986" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="C986" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="D986" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="E986" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="987" spans="1:5" x14ac:dyDescent="0.3">
@@ -27718,16 +27780,16 @@
         <v>986</v>
       </c>
       <c r="B987" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="C987" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="D987" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="E987" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="988" spans="1:5" x14ac:dyDescent="0.3">
@@ -27735,16 +27797,16 @@
         <v>987</v>
       </c>
       <c r="B988" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="C988" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="D988" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="E988" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="989" spans="1:5" x14ac:dyDescent="0.3">
@@ -27752,16 +27814,16 @@
         <v>988</v>
       </c>
       <c r="B989" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="C989" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="D989" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="E989" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="990" spans="1:5" x14ac:dyDescent="0.3">
@@ -27769,16 +27831,16 @@
         <v>989</v>
       </c>
       <c r="B990" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="C990" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="D990" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="E990" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="991" spans="1:5" x14ac:dyDescent="0.3">
@@ -27786,16 +27848,16 @@
         <v>990</v>
       </c>
       <c r="B991" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="C991" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="D991" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="E991" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="992" spans="1:5" x14ac:dyDescent="0.3">
@@ -27803,16 +27865,16 @@
         <v>991</v>
       </c>
       <c r="B992" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="C992" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="D992" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="E992" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="993" spans="1:5" x14ac:dyDescent="0.3">
@@ -27820,16 +27882,16 @@
         <v>992</v>
       </c>
       <c r="B993" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="C993" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="D993" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="E993" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="994" spans="1:5" x14ac:dyDescent="0.3">
@@ -27837,16 +27899,16 @@
         <v>993</v>
       </c>
       <c r="B994" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="C994" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="D994" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="E994" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="995" spans="1:5" x14ac:dyDescent="0.3">
@@ -27854,16 +27916,16 @@
         <v>994</v>
       </c>
       <c r="B995" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="C995" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="D995" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="E995" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="996" spans="1:5" x14ac:dyDescent="0.3">
@@ -27871,16 +27933,16 @@
         <v>995</v>
       </c>
       <c r="B996" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="C996" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="D996" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="E996" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="997" spans="1:5" x14ac:dyDescent="0.3">
@@ -27888,16 +27950,16 @@
         <v>996</v>
       </c>
       <c r="B997" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="C997" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="D997" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="E997" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="998" spans="1:5" x14ac:dyDescent="0.3">
@@ -27905,16 +27967,16 @@
         <v>997</v>
       </c>
       <c r="B998" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="C998" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="D998" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="E998" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="999" spans="1:5" x14ac:dyDescent="0.3">
@@ -27922,16 +27984,16 @@
         <v>998</v>
       </c>
       <c r="B999" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="C999" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="D999" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="E999" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="1000" spans="1:5" x14ac:dyDescent="0.3">
@@ -27939,16 +28001,16 @@
         <v>999</v>
       </c>
       <c r="B1000" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="C1000" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="D1000" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="E1000" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="1001" spans="1:5" x14ac:dyDescent="0.3">
@@ -27956,16 +28018,16 @@
         <v>1000</v>
       </c>
       <c r="B1001" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="C1001" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="D1001" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="E1001" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="1002" spans="1:5" x14ac:dyDescent="0.3">
@@ -27973,16 +28035,16 @@
         <v>1001</v>
       </c>
       <c r="B1002" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="C1002" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="D1002" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="E1002" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="1003" spans="1:5" x14ac:dyDescent="0.3">
@@ -27990,16 +28052,16 @@
         <v>1002</v>
       </c>
       <c r="B1003" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="C1003" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="D1003" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="E1003" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1004" spans="1:5" x14ac:dyDescent="0.3">
@@ -28007,16 +28069,16 @@
         <v>1003</v>
       </c>
       <c r="B1004" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="C1004" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="D1004" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="E1004" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="1005" spans="1:5" x14ac:dyDescent="0.3">
@@ -28024,16 +28086,16 @@
         <v>1004</v>
       </c>
       <c r="B1005" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="C1005" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="D1005" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="E1005" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="1006" spans="1:5" x14ac:dyDescent="0.3">
@@ -28041,16 +28103,16 @@
         <v>1005</v>
       </c>
       <c r="B1006" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="C1006" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="D1006" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="E1006" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="1007" spans="1:5" x14ac:dyDescent="0.3">
@@ -28058,16 +28120,16 @@
         <v>1006</v>
       </c>
       <c r="B1007" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="C1007" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="D1007" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="E1007" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="1008" spans="1:5" x14ac:dyDescent="0.3">
@@ -28075,16 +28137,16 @@
         <v>1007</v>
       </c>
       <c r="B1008" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="C1008" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="D1008" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="E1008" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="1009" spans="1:5" x14ac:dyDescent="0.3">
@@ -28092,16 +28154,16 @@
         <v>1008</v>
       </c>
       <c r="B1009" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="C1009" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="D1009" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="E1009" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="1010" spans="1:5" x14ac:dyDescent="0.3">
@@ -28109,16 +28171,16 @@
         <v>1009</v>
       </c>
       <c r="B1010" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="C1010" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="D1010" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="E1010" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="1011" spans="1:5" x14ac:dyDescent="0.3">
@@ -28126,16 +28188,16 @@
         <v>1010</v>
       </c>
       <c r="B1011" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="C1011" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="D1011" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="E1011" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="1012" spans="1:5" x14ac:dyDescent="0.3">
@@ -28143,16 +28205,16 @@
         <v>1011</v>
       </c>
       <c r="B1012" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="C1012" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="D1012" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="E1012" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="1013" spans="1:5" x14ac:dyDescent="0.3">
@@ -28160,16 +28222,16 @@
         <v>1012</v>
       </c>
       <c r="B1013" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="C1013" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="D1013" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="E1013" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="1014" spans="1:5" x14ac:dyDescent="0.3">
@@ -28177,16 +28239,16 @@
         <v>1013</v>
       </c>
       <c r="B1014" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="C1014" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="D1014" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="E1014" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="1015" spans="1:5" x14ac:dyDescent="0.3">
@@ -28194,16 +28256,16 @@
         <v>1014</v>
       </c>
       <c r="B1015" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="C1015" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="D1015" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="E1015" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="1016" spans="1:5" x14ac:dyDescent="0.3">
@@ -28211,16 +28273,16 @@
         <v>1015</v>
       </c>
       <c r="B1016" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="C1016" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="D1016" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="E1016" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="1017" spans="1:5" x14ac:dyDescent="0.3">
@@ -28228,16 +28290,16 @@
         <v>1016</v>
       </c>
       <c r="B1017" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="C1017" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="D1017" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="E1017" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="1018" spans="1:5" x14ac:dyDescent="0.3">
@@ -28245,16 +28307,16 @@
         <v>1017</v>
       </c>
       <c r="B1018" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="C1018" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="D1018" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="E1018" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="1019" spans="1:5" x14ac:dyDescent="0.3">
@@ -28262,16 +28324,16 @@
         <v>1018</v>
       </c>
       <c r="B1019" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="C1019" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="D1019" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="E1019" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="1020" spans="1:5" x14ac:dyDescent="0.3">
@@ -28279,16 +28341,16 @@
         <v>1019</v>
       </c>
       <c r="B1020" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="C1020" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="D1020" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="E1020" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="1021" spans="1:5" x14ac:dyDescent="0.3">
@@ -28296,16 +28358,16 @@
         <v>1020</v>
       </c>
       <c r="B1021" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="C1021" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="D1021" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="E1021" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="1022" spans="1:5" x14ac:dyDescent="0.3">
@@ -28313,16 +28375,16 @@
         <v>1021</v>
       </c>
       <c r="B1022" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="C1022" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="D1022" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="E1022" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="1023" spans="1:5" x14ac:dyDescent="0.3">
@@ -28330,16 +28392,16 @@
         <v>1022</v>
       </c>
       <c r="B1023" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="C1023" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="D1023" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="E1023" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="1024" spans="1:5" x14ac:dyDescent="0.3">
@@ -28347,16 +28409,16 @@
         <v>1023</v>
       </c>
       <c r="B1024" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="C1024" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="D1024" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="E1024" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="1025" spans="1:5" x14ac:dyDescent="0.3">
@@ -28364,16 +28426,16 @@
         <v>1024</v>
       </c>
       <c r="B1025" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C1025" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="D1025" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E1025" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="1026" spans="1:5" x14ac:dyDescent="0.3">
@@ -28381,7 +28443,7 @@
         <v>1025</v>
       </c>
       <c r="B1026" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="C1026" t="s">
         <v>1016</v>
@@ -28398,16 +28460,16 @@
         <v>1026</v>
       </c>
       <c r="B1027" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="C1027" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="D1027" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="E1027" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="1028" spans="1:5" x14ac:dyDescent="0.3">
@@ -28415,16 +28477,16 @@
         <v>1027</v>
       </c>
       <c r="B1028" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="C1028" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="D1028" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="E1028" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="1029" spans="1:5" x14ac:dyDescent="0.3">
@@ -28432,16 +28494,16 @@
         <v>1028</v>
       </c>
       <c r="B1029" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="C1029" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="D1029" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E1029" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="1030" spans="1:5" x14ac:dyDescent="0.3">
@@ -28449,16 +28511,16 @@
         <v>1029</v>
       </c>
       <c r="B1030" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="C1030" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="D1030" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="E1030" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="1031" spans="1:5" x14ac:dyDescent="0.3">
@@ -28466,16 +28528,16 @@
         <v>1030</v>
       </c>
       <c r="B1031" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="C1031" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="D1031" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E1031" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="1032" spans="1:5" x14ac:dyDescent="0.3">
@@ -28483,16 +28545,16 @@
         <v>1031</v>
       </c>
       <c r="B1032" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="C1032" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="D1032" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="E1032" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="1033" spans="1:5" x14ac:dyDescent="0.3">
@@ -28500,16 +28562,16 @@
         <v>1032</v>
       </c>
       <c r="B1033" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="C1033" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="D1033" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="E1033" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="1034" spans="1:5" x14ac:dyDescent="0.3">
@@ -28517,16 +28579,16 @@
         <v>1033</v>
       </c>
       <c r="B1034" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="C1034" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="D1034" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="E1034" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="1035" spans="1:5" x14ac:dyDescent="0.3">
@@ -28534,16 +28596,16 @@
         <v>1034</v>
       </c>
       <c r="B1035" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="C1035" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="D1035" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="E1035" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="1036" spans="1:5" x14ac:dyDescent="0.3">
@@ -28551,16 +28613,16 @@
         <v>1035</v>
       </c>
       <c r="B1036" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="C1036" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="D1036" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="E1036" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="1037" spans="1:5" x14ac:dyDescent="0.3">
@@ -28568,16 +28630,16 @@
         <v>1036</v>
       </c>
       <c r="B1037" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="C1037" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="D1037" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="E1037" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="1038" spans="1:5" x14ac:dyDescent="0.3">
@@ -28585,16 +28647,16 @@
         <v>1037</v>
       </c>
       <c r="B1038" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="C1038" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="D1038" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="E1038" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="1039" spans="1:5" x14ac:dyDescent="0.3">
@@ -28602,16 +28664,16 @@
         <v>1038</v>
       </c>
       <c r="B1039" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="C1039" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="D1039" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="E1039" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="1040" spans="1:5" x14ac:dyDescent="0.3">
@@ -28619,16 +28681,16 @@
         <v>1039</v>
       </c>
       <c r="B1040" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="C1040" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="D1040" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="E1040" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="1041" spans="1:5" x14ac:dyDescent="0.3">
@@ -28636,16 +28698,16 @@
         <v>1040</v>
       </c>
       <c r="B1041" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="C1041" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="D1041" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="E1041" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="1042" spans="1:5" x14ac:dyDescent="0.3">
@@ -28653,16 +28715,16 @@
         <v>1041</v>
       </c>
       <c r="B1042" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C1042" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="D1042" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="E1042" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="1043" spans="1:5" x14ac:dyDescent="0.3">
@@ -28670,16 +28732,16 @@
         <v>1042</v>
       </c>
       <c r="B1043" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C1043" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="D1043" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="E1043" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="1044" spans="1:5" x14ac:dyDescent="0.3">
@@ -28687,16 +28749,16 @@
         <v>1043</v>
       </c>
       <c r="B1044" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C1044" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="D1044" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="E1044" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1045" spans="1:5" x14ac:dyDescent="0.3">
@@ -28704,16 +28766,16 @@
         <v>1044</v>
       </c>
       <c r="B1045" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C1045" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="D1045" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="E1045" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="1046" spans="1:5" x14ac:dyDescent="0.3">
@@ -28721,16 +28783,16 @@
         <v>1045</v>
       </c>
       <c r="B1046" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C1046" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="D1046" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="E1046" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="1047" spans="1:5" x14ac:dyDescent="0.3">
@@ -28738,16 +28800,16 @@
         <v>1046</v>
       </c>
       <c r="B1047" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C1047" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="D1047" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="E1047" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="1048" spans="1:5" x14ac:dyDescent="0.3">
@@ -28755,7 +28817,7 @@
         <v>1047</v>
       </c>
       <c r="B1048" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C1048" t="s">
         <v>1016</v>
@@ -28772,16 +28834,16 @@
         <v>1048</v>
       </c>
       <c r="B1049" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C1049" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="D1049" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="E1049" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="1050" spans="1:5" x14ac:dyDescent="0.3">
@@ -28789,16 +28851,16 @@
         <v>1049</v>
       </c>
       <c r="B1050" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C1050" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="D1050" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="E1050" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="1051" spans="1:5" x14ac:dyDescent="0.3">
@@ -28806,16 +28868,16 @@
         <v>1050</v>
       </c>
       <c r="B1051" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C1051" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="D1051" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="E1051" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="1052" spans="1:5" x14ac:dyDescent="0.3">
@@ -28823,16 +28885,16 @@
         <v>1051</v>
       </c>
       <c r="B1052" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C1052" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="D1052" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="E1052" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="1053" spans="1:5" x14ac:dyDescent="0.3">
@@ -28840,16 +28902,16 @@
         <v>1052</v>
       </c>
       <c r="B1053" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="C1053" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="D1053" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="E1053" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="1054" spans="1:5" x14ac:dyDescent="0.3">
@@ -28857,16 +28919,16 @@
         <v>1053</v>
       </c>
       <c r="B1054" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="C1054" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="D1054" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="E1054" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="1055" spans="1:5" x14ac:dyDescent="0.3">
@@ -28874,16 +28936,16 @@
         <v>1054</v>
       </c>
       <c r="B1055" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C1055" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="D1055" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="E1055" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="1056" spans="1:5" x14ac:dyDescent="0.3">
@@ -28891,16 +28953,16 @@
         <v>1055</v>
       </c>
       <c r="B1056" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="C1056" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="D1056" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="E1056" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1057" spans="1:5" x14ac:dyDescent="0.3">
@@ -28908,16 +28970,16 @@
         <v>1056</v>
       </c>
       <c r="B1057" s="28" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="C1057" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="D1057" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="E1057" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="1058" spans="1:5" x14ac:dyDescent="0.3">
@@ -28925,16 +28987,16 @@
         <v>1057</v>
       </c>
       <c r="B1058" s="28" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
       <c r="C1058" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="D1058" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="E1058" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="1059" spans="1:5" x14ac:dyDescent="0.3">
@@ -28942,16 +29004,16 @@
         <v>1058</v>
       </c>
       <c r="B1059" s="28" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="C1059" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="D1059" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="E1059" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="1060" spans="1:5" x14ac:dyDescent="0.3">
@@ -28959,16 +29021,16 @@
         <v>1059</v>
       </c>
       <c r="B1060" s="28" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="C1060" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="D1060" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="E1060" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="1061" spans="1:5" x14ac:dyDescent="0.3">
@@ -28976,16 +29038,16 @@
         <v>1060</v>
       </c>
       <c r="B1061" s="28" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
       <c r="C1061" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="D1061" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="E1061" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="1062" spans="1:5" x14ac:dyDescent="0.3">
@@ -28993,16 +29055,16 @@
         <v>1061</v>
       </c>
       <c r="B1062" s="28" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
       <c r="C1062" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="D1062" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="E1062" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="1063" spans="1:5" x14ac:dyDescent="0.3">
@@ -29010,16 +29072,16 @@
         <v>1062</v>
       </c>
       <c r="B1063" s="28" t="s">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="C1063" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="D1063" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="E1063" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="1064" spans="1:5" x14ac:dyDescent="0.3">
@@ -29027,16 +29089,16 @@
         <v>1063</v>
       </c>
       <c r="B1064" s="28" t="s">
+        <v>2101</v>
+      </c>
+      <c r="C1064" t="s">
         <v>2102</v>
       </c>
-      <c r="C1064" t="s">
-        <v>2103</v>
-      </c>
       <c r="D1064" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="E1064" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="1065" spans="1:5" x14ac:dyDescent="0.3">
@@ -29044,16 +29106,16 @@
         <v>1064</v>
       </c>
       <c r="B1065" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="C1065" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="D1065" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="E1065" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="1066" spans="1:5" x14ac:dyDescent="0.3">
@@ -29061,16 +29123,16 @@
         <v>1065</v>
       </c>
       <c r="B1066" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="C1066" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="D1066" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="E1066" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="1067" spans="1:5" x14ac:dyDescent="0.3">
@@ -29078,16 +29140,16 @@
         <v>1066</v>
       </c>
       <c r="B1067" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="C1067" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
       <c r="D1067" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
       <c r="E1067" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="1068" spans="1:5" x14ac:dyDescent="0.3">
@@ -29095,16 +29157,16 @@
         <v>1067</v>
       </c>
       <c r="B1068" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
       <c r="C1068" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="D1068" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="E1068" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="1069" spans="1:5" x14ac:dyDescent="0.3">
@@ -29112,16 +29174,16 @@
         <v>1068</v>
       </c>
       <c r="B1069" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="C1069" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="D1069" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="E1069" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="1070" spans="1:5" x14ac:dyDescent="0.3">
@@ -29129,16 +29191,16 @@
         <v>1069</v>
       </c>
       <c r="B1070" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="C1070" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="D1070" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="E1070" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="1071" spans="1:5" x14ac:dyDescent="0.3">
@@ -29146,16 +29208,16 @@
         <v>1070</v>
       </c>
       <c r="B1071" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="C1071" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="D1071" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="E1071" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="1072" spans="1:5" x14ac:dyDescent="0.3">
@@ -29163,16 +29225,16 @@
         <v>1071</v>
       </c>
       <c r="B1072" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="C1072" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="D1072" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="E1072" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="1073" spans="1:5" x14ac:dyDescent="0.3">
@@ -29180,16 +29242,16 @@
         <v>1072</v>
       </c>
       <c r="B1073" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="C1073" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="D1073" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="E1073" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="1074" spans="1:5" x14ac:dyDescent="0.3">
@@ -29197,16 +29259,16 @@
         <v>1073</v>
       </c>
       <c r="B1074" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="C1074" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="D1074" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="E1074" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="1075" spans="1:5" x14ac:dyDescent="0.3">
@@ -29214,16 +29276,16 @@
         <v>1074</v>
       </c>
       <c r="B1075" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="C1075" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="D1075" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="E1075" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="1076" spans="1:5" x14ac:dyDescent="0.3">
@@ -29231,16 +29293,16 @@
         <v>1075</v>
       </c>
       <c r="B1076" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="C1076" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="D1076" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="E1076" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="1077" spans="1:5" x14ac:dyDescent="0.3">
@@ -29248,16 +29310,16 @@
         <v>1076</v>
       </c>
       <c r="B1077" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="C1077" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="D1077" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="E1077" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="1078" spans="1:5" x14ac:dyDescent="0.3">
@@ -29265,16 +29327,16 @@
         <v>1077</v>
       </c>
       <c r="B1078" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="C1078" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="D1078" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="E1078" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="1079" spans="1:5" x14ac:dyDescent="0.3">
@@ -29282,16 +29344,16 @@
         <v>1078</v>
       </c>
       <c r="B1079" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="C1079" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="D1079" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="E1079" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1080" spans="1:5" x14ac:dyDescent="0.3">
@@ -29299,16 +29361,16 @@
         <v>1079</v>
       </c>
       <c r="B1080" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="C1080" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="D1080" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="E1080" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="1081" spans="1:5" x14ac:dyDescent="0.3">
@@ -29316,16 +29378,16 @@
         <v>1080</v>
       </c>
       <c r="B1081" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="C1081" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="D1081" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="E1081" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="1082" spans="1:5" x14ac:dyDescent="0.3">
@@ -29333,16 +29395,16 @@
         <v>1081</v>
       </c>
       <c r="B1082" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="C1082" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
       <c r="D1082" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
       <c r="E1082" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="1083" spans="1:5" x14ac:dyDescent="0.3">
@@ -29350,16 +29412,16 @@
         <v>1082</v>
       </c>
       <c r="B1083" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="C1083" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="D1083" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="E1083" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="1084" spans="1:5" x14ac:dyDescent="0.3">
@@ -29367,16 +29429,16 @@
         <v>1083</v>
       </c>
       <c r="B1084" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="C1084" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="D1084" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="E1084" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="1085" spans="1:5" x14ac:dyDescent="0.3">
@@ -29384,16 +29446,16 @@
         <v>1084</v>
       </c>
       <c r="B1085" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="C1085" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="D1085" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="E1085" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="1086" spans="1:5" x14ac:dyDescent="0.3">
@@ -29401,16 +29463,16 @@
         <v>1085</v>
       </c>
       <c r="B1086" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="C1086" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="D1086" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="E1086" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="1087" spans="1:5" x14ac:dyDescent="0.3">
@@ -29418,16 +29480,16 @@
         <v>1086</v>
       </c>
       <c r="B1087" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="C1087" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="D1087" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="E1087" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="1088" spans="1:5" x14ac:dyDescent="0.3">
@@ -29435,16 +29497,16 @@
         <v>1087</v>
       </c>
       <c r="B1088" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="C1088" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="D1088" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="E1088" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="1089" spans="1:5" x14ac:dyDescent="0.3">
@@ -29452,16 +29514,16 @@
         <v>1088</v>
       </c>
       <c r="B1089" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="C1089" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="D1089" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="E1089" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="1090" spans="1:5" x14ac:dyDescent="0.3">
@@ -29469,16 +29531,16 @@
         <v>1089</v>
       </c>
       <c r="B1090" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
       <c r="C1090" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="D1090" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="E1090" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="1091" spans="1:5" x14ac:dyDescent="0.3">
@@ -29486,16 +29548,16 @@
         <v>1090</v>
       </c>
       <c r="B1091" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="C1091" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="D1091" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="E1091" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="1092" spans="1:5" x14ac:dyDescent="0.3">
@@ -29503,16 +29565,16 @@
         <v>1091</v>
       </c>
       <c r="B1092" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="C1092" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
       <c r="D1092" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
       <c r="E1092" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="1093" spans="1:5" x14ac:dyDescent="0.3">
@@ -29520,16 +29582,16 @@
         <v>1092</v>
       </c>
       <c r="B1093" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="C1093" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
       <c r="D1093" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
       <c r="E1093" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="1094" spans="1:5" x14ac:dyDescent="0.3">
@@ -29537,16 +29599,16 @@
         <v>1093</v>
       </c>
       <c r="B1094" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="C1094" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
       <c r="D1094" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
       <c r="E1094" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="1095" spans="1:5" x14ac:dyDescent="0.3">
@@ -29554,16 +29616,16 @@
         <v>1094</v>
       </c>
       <c r="B1095" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
       <c r="C1095" t="s">
-        <v>2179</v>
+        <v>2178</v>
       </c>
       <c r="D1095" t="s">
-        <v>2179</v>
+        <v>2178</v>
       </c>
       <c r="E1095" t="s">
-        <v>2179</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="1096" spans="1:5" x14ac:dyDescent="0.3">
@@ -29571,16 +29633,16 @@
         <v>1095</v>
       </c>
       <c r="B1096" t="s">
-        <v>2184</v>
+        <v>2183</v>
       </c>
       <c r="C1096" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="D1096" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="E1096" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="1097" spans="1:5" x14ac:dyDescent="0.3">
@@ -29588,16 +29650,16 @@
         <v>1096</v>
       </c>
       <c r="B1097" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="C1097" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="D1097" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="E1097" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="1098" spans="1:5" x14ac:dyDescent="0.3">
@@ -29605,16 +29667,16 @@
         <v>1097</v>
       </c>
       <c r="B1098" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
       <c r="C1098" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="D1098" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="E1098" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="1099" spans="1:5" x14ac:dyDescent="0.3">
@@ -29622,16 +29684,16 @@
         <v>1098</v>
       </c>
       <c r="B1099" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
       <c r="C1099" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
       <c r="D1099" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
       <c r="E1099" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="1100" spans="1:5" x14ac:dyDescent="0.3">
@@ -29639,16 +29701,16 @@
         <v>1099</v>
       </c>
       <c r="B1100" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="C1100" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="D1100" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="E1100" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="1101" spans="1:5" x14ac:dyDescent="0.3">
@@ -29656,16 +29718,16 @@
         <v>1100</v>
       </c>
       <c r="B1101" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="C1101" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="D1101" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="E1101" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="1102" spans="1:5" x14ac:dyDescent="0.3">
@@ -29673,16 +29735,16 @@
         <v>1101</v>
       </c>
       <c r="B1102" t="s">
-        <v>2230</v>
+        <v>2229</v>
       </c>
       <c r="C1102" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="D1102" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="E1102" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="1103" spans="1:5" x14ac:dyDescent="0.3">
@@ -29690,16 +29752,16 @@
         <v>1102</v>
       </c>
       <c r="B1103" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="C1103" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
       <c r="D1103" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
       <c r="E1103" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
     </row>
     <row r="1104" spans="1:5" x14ac:dyDescent="0.3">
@@ -29707,16 +29769,16 @@
         <v>1103</v>
       </c>
       <c r="B1104" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="C1104" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
       <c r="D1104" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
       <c r="E1104" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="1105" spans="1:5" x14ac:dyDescent="0.3">
@@ -29724,16 +29786,16 @@
         <v>1104</v>
       </c>
       <c r="B1105" t="s">
-        <v>2231</v>
+        <v>2230</v>
       </c>
       <c r="C1105" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
       <c r="D1105" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
       <c r="E1105" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="1106" spans="1:5" x14ac:dyDescent="0.3">
@@ -29741,16 +29803,16 @@
         <v>1105</v>
       </c>
       <c r="B1106" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="C1106" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
       <c r="D1106" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
       <c r="E1106" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="1107" spans="1:5" x14ac:dyDescent="0.3">
@@ -29758,16 +29820,16 @@
         <v>1106</v>
       </c>
       <c r="B1107" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
       <c r="C1107" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="D1107" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="E1107" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="1108" spans="1:5" x14ac:dyDescent="0.3">
@@ -29775,16 +29837,16 @@
         <v>1107</v>
       </c>
       <c r="B1108" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="C1108" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
       <c r="D1108" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
       <c r="E1108" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="1109" spans="1:5" x14ac:dyDescent="0.3">
@@ -29792,16 +29854,16 @@
         <v>1108</v>
       </c>
       <c r="B1109" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
       <c r="C1109" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="D1109" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="E1109" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="1110" spans="1:5" x14ac:dyDescent="0.3">
@@ -29809,16 +29871,16 @@
         <v>1109</v>
       </c>
       <c r="B1110" t="s">
-        <v>2198</v>
+        <v>2197</v>
       </c>
       <c r="C1110" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="D1110" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="E1110" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="1111" spans="1:5" x14ac:dyDescent="0.3">
@@ -29826,16 +29888,16 @@
         <v>1110</v>
       </c>
       <c r="B1111" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
       <c r="C1111" t="s">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="D1111" t="s">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="E1111" t="s">
-        <v>2203</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="1112" spans="1:5" x14ac:dyDescent="0.3">
@@ -29843,16 +29905,16 @@
         <v>1111</v>
       </c>
       <c r="B1112" t="s">
-        <v>2235</v>
+        <v>2234</v>
       </c>
       <c r="C1112" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="D1112" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="E1112" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="1113" spans="1:5" x14ac:dyDescent="0.3">
@@ -29860,16 +29922,16 @@
         <v>1112</v>
       </c>
       <c r="B1113" t="s">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="C1113" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
       <c r="D1113" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
       <c r="E1113" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="1114" spans="1:5" x14ac:dyDescent="0.3">
@@ -29877,16 +29939,16 @@
         <v>1113</v>
       </c>
       <c r="B1114" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="C1114" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="D1114" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="E1114" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="1115" spans="1:5" x14ac:dyDescent="0.3">
@@ -29894,16 +29956,16 @@
         <v>1114</v>
       </c>
       <c r="B1115" t="s">
-        <v>2207</v>
+        <v>2206</v>
       </c>
       <c r="C1115" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
       <c r="D1115" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
       <c r="E1115" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="1116" spans="1:5" x14ac:dyDescent="0.3">
@@ -29911,16 +29973,16 @@
         <v>1115</v>
       </c>
       <c r="B1116" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="C1116" t="s">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="D1116" t="s">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="E1116" t="s">
-        <v>2211</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="1117" spans="1:5" x14ac:dyDescent="0.3">
@@ -29928,16 +29990,16 @@
         <v>1116</v>
       </c>
       <c r="B1117" t="s">
-        <v>2210</v>
+        <v>2209</v>
       </c>
       <c r="C1117" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="D1117" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="E1117" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="1118" spans="1:5" x14ac:dyDescent="0.3">
@@ -29945,16 +30007,16 @@
         <v>1117</v>
       </c>
       <c r="B1118" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="C1118" t="s">
-        <v>2214</v>
+        <v>2213</v>
       </c>
       <c r="D1118" t="s">
-        <v>2214</v>
+        <v>2213</v>
       </c>
       <c r="E1118" t="s">
-        <v>2214</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="1119" spans="1:5" x14ac:dyDescent="0.3">
@@ -29962,16 +30024,16 @@
         <v>1118</v>
       </c>
       <c r="B1119" t="s">
-        <v>2213</v>
+        <v>2212</v>
       </c>
       <c r="C1119" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="D1119" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="E1119" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="1120" spans="1:5" x14ac:dyDescent="0.3">
@@ -29979,16 +30041,16 @@
         <v>1119</v>
       </c>
       <c r="B1120" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="C1120" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="D1120" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="E1120" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="1121" spans="1:5" x14ac:dyDescent="0.3">
@@ -29996,16 +30058,16 @@
         <v>1120</v>
       </c>
       <c r="B1121" t="s">
-        <v>2216</v>
+        <v>2215</v>
       </c>
       <c r="C1121" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
       <c r="D1121" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
       <c r="E1121" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="1122" spans="1:5" x14ac:dyDescent="0.3">
@@ -30013,16 +30075,16 @@
         <v>1121</v>
       </c>
       <c r="B1122" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="C1122" t="s">
-        <v>2219</v>
+        <v>2218</v>
       </c>
       <c r="D1122" t="s">
-        <v>2219</v>
+        <v>2218</v>
       </c>
       <c r="E1122" t="s">
-        <v>2219</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="1123" spans="1:5" x14ac:dyDescent="0.3">
@@ -30030,16 +30092,16 @@
         <v>1122</v>
       </c>
       <c r="B1123" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
       <c r="C1123" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="D1123" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="E1123" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="1124" spans="1:5" x14ac:dyDescent="0.3">
@@ -30047,16 +30109,16 @@
         <v>1123</v>
       </c>
       <c r="B1124" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="C1124" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
       <c r="D1124" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
       <c r="E1124" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="1125" spans="1:5" x14ac:dyDescent="0.3">
@@ -30064,16 +30126,16 @@
         <v>1124</v>
       </c>
       <c r="B1125" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
       <c r="C1125" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="D1125" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="E1125" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="1126" spans="1:5" x14ac:dyDescent="0.3">
@@ -30081,16 +30143,16 @@
         <v>1125</v>
       </c>
       <c r="B1126" t="s">
-        <v>2222</v>
+        <v>2221</v>
       </c>
       <c r="C1126" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="D1126" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="E1126" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="1127" spans="1:5" x14ac:dyDescent="0.3">
@@ -30098,16 +30160,16 @@
         <v>1126</v>
       </c>
       <c r="B1127" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="C1127" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="D1127" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="E1127" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="1128" spans="1:5" x14ac:dyDescent="0.3">
@@ -30115,16 +30177,16 @@
         <v>1127</v>
       </c>
       <c r="B1128" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="C1128" t="s">
-        <v>2228</v>
+        <v>2227</v>
       </c>
       <c r="D1128" t="s">
-        <v>2228</v>
+        <v>2227</v>
       </c>
       <c r="E1128" t="s">
-        <v>2228</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="1129" spans="1:5" x14ac:dyDescent="0.3">
@@ -30132,16 +30194,16 @@
         <v>1128</v>
       </c>
       <c r="B1129" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="C1129" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="D1129" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="E1129" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="1130" spans="1:5" x14ac:dyDescent="0.3">
@@ -30149,16 +30211,16 @@
         <v>1129</v>
       </c>
       <c r="B1130" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
       <c r="C1130" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
       <c r="D1130" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
       <c r="E1130" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="1131" spans="1:5" x14ac:dyDescent="0.3">
@@ -30166,16 +30228,16 @@
         <v>1130</v>
       </c>
       <c r="B1131" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="C1131" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
       <c r="D1131" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
       <c r="E1131" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="1132" spans="1:5" x14ac:dyDescent="0.3">
@@ -30183,16 +30245,16 @@
         <v>1131</v>
       </c>
       <c r="B1132" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="C1132" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="D1132" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="E1132" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="1133" spans="1:5" x14ac:dyDescent="0.3">
@@ -30200,16 +30262,16 @@
         <v>1132</v>
       </c>
       <c r="B1133" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="C1133" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
       <c r="D1133" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
       <c r="E1133" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="1134" spans="1:5" x14ac:dyDescent="0.3">
@@ -30217,16 +30279,16 @@
         <v>1133</v>
       </c>
       <c r="B1134" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="C1134" t="s">
-        <v>2245</v>
+        <v>2244</v>
       </c>
       <c r="D1134" t="s">
-        <v>2245</v>
+        <v>2244</v>
       </c>
       <c r="E1134" t="s">
-        <v>2245</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="1135" spans="1:5" x14ac:dyDescent="0.3">
@@ -30234,16 +30296,16 @@
         <v>1134</v>
       </c>
       <c r="B1135" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="C1135" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
       <c r="D1135" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
       <c r="E1135" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="1136" spans="1:5" x14ac:dyDescent="0.3">
@@ -30251,16 +30313,16 @@
         <v>1135</v>
       </c>
       <c r="B1136" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="C1136" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
       <c r="D1136" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
       <c r="E1136" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="1137" spans="1:5" x14ac:dyDescent="0.3">
@@ -30268,16 +30330,16 @@
         <v>1136</v>
       </c>
       <c r="B1137" t="s">
-        <v>2255</v>
+        <v>2254</v>
       </c>
       <c r="C1137" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="D1137" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="E1137" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="1138" spans="1:5" x14ac:dyDescent="0.3">
@@ -30285,16 +30347,16 @@
         <v>1137</v>
       </c>
       <c r="B1138" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
       <c r="C1138" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="D1138" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="E1138" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1139" spans="1:5" x14ac:dyDescent="0.3">
@@ -30302,16 +30364,16 @@
         <v>1138</v>
       </c>
       <c r="B1139" t="s">
-        <v>2257</v>
+        <v>2256</v>
       </c>
       <c r="C1139" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="D1139" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="E1139" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="1140" spans="1:5" x14ac:dyDescent="0.3">
@@ -30319,16 +30381,16 @@
         <v>1139</v>
       </c>
       <c r="B1140" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
       <c r="C1140" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="D1140" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="E1140" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="1141" spans="1:5" x14ac:dyDescent="0.3">
@@ -30336,16 +30398,16 @@
         <v>1140</v>
       </c>
       <c r="B1141" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="C1141" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="D1141" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="E1141" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="1142" spans="1:5" x14ac:dyDescent="0.3">
@@ -30353,16 +30415,16 @@
         <v>1141</v>
       </c>
       <c r="B1142" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="C1142" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="D1142" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="E1142" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="1143" spans="1:5" x14ac:dyDescent="0.3">
@@ -30370,16 +30432,16 @@
         <v>1142</v>
       </c>
       <c r="B1143" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="C1143" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="D1143" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="E1143" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="1144" spans="1:5" x14ac:dyDescent="0.3">
@@ -30387,16 +30449,186 @@
         <v>1143</v>
       </c>
       <c r="B1144" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="C1144" t="s">
+        <v>2266</v>
+      </c>
+      <c r="D1144" t="s">
+        <v>2266</v>
+      </c>
+      <c r="E1144" t="s">
+        <v>2266</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1145">
+        <v>1144</v>
+      </c>
+      <c r="B1145" t="s">
         <v>2267</v>
       </c>
-      <c r="D1144" t="s">
-        <v>2267</v>
-      </c>
-      <c r="E1144" t="s">
-        <v>2267</v>
+      <c r="C1145" t="s">
+        <v>2286</v>
+      </c>
+      <c r="D1145" t="s">
+        <v>2286</v>
+      </c>
+      <c r="E1145" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1146">
+        <v>1145</v>
+      </c>
+      <c r="B1146" t="s">
+        <v>2268</v>
+      </c>
+      <c r="C1146" t="s">
+        <v>2269</v>
+      </c>
+      <c r="D1146" t="s">
+        <v>2269</v>
+      </c>
+      <c r="E1146" t="s">
+        <v>2269</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1147">
+        <v>1146</v>
+      </c>
+      <c r="B1147" t="s">
+        <v>2270</v>
+      </c>
+      <c r="C1147" s="24" t="s">
+        <v>2278</v>
+      </c>
+      <c r="D1147" s="24" t="s">
+        <v>2278</v>
+      </c>
+      <c r="E1147" s="24" t="s">
+        <v>2278</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1148">
+        <v>1147</v>
+      </c>
+      <c r="B1148" t="s">
+        <v>2271</v>
+      </c>
+      <c r="C1148" s="24" t="s">
+        <v>2279</v>
+      </c>
+      <c r="D1148" s="24" t="s">
+        <v>2279</v>
+      </c>
+      <c r="E1148" s="24" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1149">
+        <v>1148</v>
+      </c>
+      <c r="B1149" t="s">
+        <v>2272</v>
+      </c>
+      <c r="C1149" s="24" t="s">
+        <v>2280</v>
+      </c>
+      <c r="D1149" s="24" t="s">
+        <v>2280</v>
+      </c>
+      <c r="E1149" s="24" t="s">
+        <v>2280</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1150">
+        <v>1149</v>
+      </c>
+      <c r="B1150" t="s">
+        <v>2273</v>
+      </c>
+      <c r="C1150" s="24" t="s">
+        <v>2281</v>
+      </c>
+      <c r="D1150" s="24" t="s">
+        <v>2281</v>
+      </c>
+      <c r="E1150" s="24" t="s">
+        <v>2281</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1151">
+        <v>1150</v>
+      </c>
+      <c r="B1151" t="s">
+        <v>2274</v>
+      </c>
+      <c r="C1151" s="24" t="s">
+        <v>2282</v>
+      </c>
+      <c r="D1151" s="24" t="s">
+        <v>2282</v>
+      </c>
+      <c r="E1151" s="24" t="s">
+        <v>2282</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1152">
+        <v>1151</v>
+      </c>
+      <c r="B1152" t="s">
+        <v>2275</v>
+      </c>
+      <c r="C1152" s="24" t="s">
+        <v>2283</v>
+      </c>
+      <c r="D1152" s="24" t="s">
+        <v>2283</v>
+      </c>
+      <c r="E1152" s="24" t="s">
+        <v>2283</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1153">
+        <v>1152</v>
+      </c>
+      <c r="B1153" t="s">
+        <v>2276</v>
+      </c>
+      <c r="C1153" s="24" t="s">
+        <v>2284</v>
+      </c>
+      <c r="D1153" s="24" t="s">
+        <v>2284</v>
+      </c>
+      <c r="E1153" s="24" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1154">
+        <v>1153</v>
+      </c>
+      <c r="B1154" t="s">
+        <v>2277</v>
+      </c>
+      <c r="C1154" s="24" t="s">
+        <v>2285</v>
+      </c>
+      <c r="D1154" s="24" t="s">
+        <v>2285</v>
+      </c>
+      <c r="E1154" s="24" t="s">
+        <v>2285</v>
       </c>
     </row>
   </sheetData>
